--- a/CORDEX_Cmor_variables.xlsx
+++ b/CORDEX_Cmor_variables.xlsx
@@ -2012,7 +2012,7 @@
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; daily maximum of the hourly precipitation</t>
+          <t>not produced by CORDEX_Cmor; header ready; daily maximum of the hourly precipitation</t>
         </is>
       </c>
     </row>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="N56" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; vertical integral</t>
+          <t>not produced by CORDEX_Cmor; header ready; vertical integral</t>
         </is>
       </c>
     </row>
@@ -4068,7 +4068,7 @@
       </c>
       <c r="N57" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; vertical integral (2-moment microphysics with hail)</t>
+          <t>not produced by CORDEX_Cmor; header ready; vertical integral (2-moment microphysics with hail)</t>
         </is>
       </c>
     </row>
@@ -8780,7 +8780,7 @@
       </c>
       <c r="N127" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; no gust diagnostic in the WRF output</t>
+          <t>not produced by CORDEX_Cmor; header ready; no gust diagnostic in the WRF output</t>
         </is>
       </c>
     </row>
@@ -9480,7 +9480,7 @@
       </c>
       <c r="N138" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; derived (e.g. wrf-python cape_2d)</t>
+          <t>not produced by CORDEX_Cmor; header ready; derived (e.g. wrf-python cape_2d)</t>
         </is>
       </c>
     </row>
@@ -9544,7 +9544,7 @@
       </c>
       <c r="N139" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; derived (lifted index at 500 hPa)</t>
+          <t>not produced by CORDEX_Cmor; header ready; derived (lifted index at 500 hPa)</t>
         </is>
       </c>
     </row>
@@ -9608,7 +9608,7 @@
       </c>
       <c r="N140" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; derived (e.g. wrf-python cape_2d)</t>
+          <t>not produced by CORDEX_Cmor; header ready; derived (e.g. wrf-python cape_2d)</t>
         </is>
       </c>
     </row>
@@ -9664,7 +9664,7 @@
       </c>
       <c r="N141" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; daily maximum of cape</t>
+          <t>not produced by CORDEX_Cmor; header ready; daily maximum of cape</t>
         </is>
       </c>
     </row>
@@ -9720,7 +9720,7 @@
       </c>
       <c r="N142" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; daily maximum of li</t>
+          <t>not produced by CORDEX_Cmor; header ready; daily maximum of li</t>
         </is>
       </c>
     </row>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="N143" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; daily maximum of cin</t>
+          <t>not produced by CORDEX_Cmor; header ready; daily maximum of cin</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10236,7 @@
       </c>
       <c r="N150" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor</t>
+          <t>not produced by CORDEX_Cmor; header ready; commented lines with all the pressure levels in config/varsets*.sh; missing unless p_top &lt; 20 hPa</t>
         </is>
       </c>
     </row>
@@ -10304,7 +10304,7 @@
       </c>
       <c r="N151" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; above the model top with p_top = 2000 Pa</t>
+          <t>not produced by CORDEX_Cmor; header ready; commented lines with all the pressure levels in config/varsets*.sh; missing unless p_top &lt; 10 hPa</t>
         </is>
       </c>
     </row>
@@ -10712,7 +10712,7 @@
       </c>
       <c r="N157" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor</t>
+          <t>not produced by CORDEX_Cmor; header ready; commented lines with all the pressure levels in config/varsets*.sh; missing unless p_top &lt; 20 hPa</t>
         </is>
       </c>
     </row>
@@ -10780,7 +10780,7 @@
       </c>
       <c r="N158" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; above the model top with p_top = 2000 Pa</t>
+          <t>not produced by CORDEX_Cmor; header ready; commented lines with all the pressure levels in config/varsets*.sh; missing unless p_top &lt; 10 hPa</t>
         </is>
       </c>
     </row>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="N164" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor</t>
+          <t>not produced by CORDEX_Cmor; header ready; commented lines with all the pressure levels in config/varsets*.sh; missing unless p_top &lt; 20 hPa</t>
         </is>
       </c>
     </row>
@@ -11256,7 +11256,7 @@
       </c>
       <c r="N165" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; above the model top with p_top = 2000 Pa</t>
+          <t>not produced by CORDEX_Cmor; header ready; commented lines with all the pressure levels in config/varsets*.sh; missing unless p_top &lt; 10 hPa</t>
         </is>
       </c>
     </row>
@@ -11664,7 +11664,7 @@
       </c>
       <c r="N171" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor</t>
+          <t>not produced by CORDEX_Cmor; header ready; commented lines with all the pressure levels in config/varsets*.sh; missing unless p_top &lt; 20 hPa</t>
         </is>
       </c>
     </row>
@@ -11732,7 +11732,7 @@
       </c>
       <c r="N172" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; above the model top with p_top = 2000 Pa</t>
+          <t>not produced by CORDEX_Cmor; header ready; commented lines with all the pressure levels in config/varsets*.sh; missing unless p_top &lt; 10 hPa</t>
         </is>
       </c>
     </row>
@@ -12140,7 +12140,7 @@
       </c>
       <c r="N178" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor</t>
+          <t>not produced by CORDEX_Cmor; header ready; commented lines with all the pressure levels in config/varsets*.sh; missing unless p_top &lt; 20 hPa</t>
         </is>
       </c>
     </row>
@@ -12208,7 +12208,7 @@
       </c>
       <c r="N179" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; above the model top with p_top = 2000 Pa</t>
+          <t>not produced by CORDEX_Cmor; header ready; commented lines with all the pressure levels in config/varsets*.sh; missing unless p_top &lt; 10 hPa</t>
         </is>
       </c>
     </row>
@@ -12616,7 +12616,7 @@
       </c>
       <c r="N185" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor</t>
+          <t>not produced by CORDEX_Cmor; header ready; commented lines with all the pressure levels in config/varsets*.sh; missing unless p_top &lt; 20 hPa</t>
         </is>
       </c>
     </row>
@@ -12684,7 +12684,7 @@
       </c>
       <c r="N186" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; above the model top with p_top = 2000 Pa</t>
+          <t>not produced by CORDEX_Cmor; header ready; commented lines with all the pressure levels in config/varsets*.sh; missing unless p_top &lt; 10 hPa</t>
         </is>
       </c>
     </row>
@@ -13428,7 +13428,7 @@
       </c>
       <c r="N198" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; root layers per vegetation class (NROOT of VEGPARM.TBL)</t>
+          <t>not produced by CORDEX_Cmor; header ready; root layers per vegetation class (NROOT of VEGPARM.TBL)</t>
         </is>
       </c>
     </row>
@@ -13572,7 +13572,7 @@
       </c>
       <c r="N201" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; not available from WRF (external dataset)</t>
+          <t>not produced by CORDEX_Cmor; header ready; not available from WRF (external dataset)</t>
         </is>
       </c>
     </row>
@@ -13620,7 +13620,7 @@
       </c>
       <c r="N202" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; geo_em; DX*DY/(MAPFAC_MX*MAPFAC_MY) with the DX/DY attributes</t>
+          <t>not produced by CORDEX_Cmor; header ready; geo_em; DX*DY/(MAPFAC_MX*MAPFAC_MY) with the DX/DY attributes</t>
         </is>
       </c>
     </row>
@@ -13684,7 +13684,7 @@
       </c>
       <c r="N203" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor</t>
+          <t>not produced by CORDEX_Cmor; header ready</t>
         </is>
       </c>
     </row>
@@ -14000,7 +14000,7 @@
       </c>
       <c r="N208" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; not in the WRF history output</t>
+          <t>not produced by CORDEX_Cmor; header ready; not in the WRF history output</t>
         </is>
       </c>
     </row>
@@ -14624,7 +14624,7 @@
       </c>
       <c r="N218" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; geo_em; DX*DY/(MAPFAC_MX*MAPFAC_MY) with the DX/DY attributes</t>
+          <t>not produced by CORDEX_Cmor; header ready; geo_em; DX*DY/(MAPFAC_MX*MAPFAC_MY) with the DX/DY attributes</t>
         </is>
       </c>
     </row>
@@ -15072,7 +15072,7 @@
       </c>
       <c r="N226" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; model levels</t>
+          <t>not produced by CORDEX_Cmor; header ready; model levels</t>
         </is>
       </c>
     </row>
@@ -17900,7 +17900,7 @@
       </c>
       <c r="N277" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; no canopy albedo in the WRF output</t>
+          <t>not produced by CORDEX_Cmor; header ready; no canopy albedo in the WRF output</t>
         </is>
       </c>
     </row>
@@ -18100,7 +18100,7 @@
       </c>
       <c r="N281" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; Noah-MP with dynamic vegetation (opt_dveg)</t>
+          <t>not produced by CORDEX_Cmor; header ready; Noah-MP with dynamic vegetation (opt_dveg)</t>
         </is>
       </c>
     </row>
@@ -18316,7 +18316,7 @@
       </c>
       <c r="N285" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; no land-use tiles in WRF: grid-cell value only</t>
+          <t>not produced by CORDEX_Cmor; header ready; no land-use tiles in WRF: grid-cell value only</t>
         </is>
       </c>
     </row>
@@ -18372,7 +18372,7 @@
       </c>
       <c r="N286" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; no land-use tiles in WRF: grid-cell value only</t>
+          <t>not produced by CORDEX_Cmor; header ready; no land-use tiles in WRF: grid-cell value only</t>
         </is>
       </c>
     </row>
@@ -18428,7 +18428,7 @@
       </c>
       <c r="N287" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; no land-use tiles in WRF (Noah-MP Q2MV/Q2MB: vegetated/bare parts)</t>
+          <t>not produced by CORDEX_Cmor; header ready; no land-use tiles in WRF (Noah-MP Q2MV/Q2MB: vegetated/bare parts)</t>
         </is>
       </c>
     </row>
@@ -18484,7 +18484,7 @@
       </c>
       <c r="N288" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; Noah-MP canopy water</t>
+          <t>not produced by CORDEX_Cmor; header ready; Noah-MP canopy water</t>
         </is>
       </c>
     </row>
@@ -18540,7 +18540,7 @@
       </c>
       <c r="N289" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; Noah-MP irrigation (opt_irr); no land-use tiles</t>
+          <t>not produced by CORDEX_Cmor; header ready; Noah-MP irrigation (opt_irr); no land-use tiles</t>
         </is>
       </c>
     </row>
@@ -18596,7 +18596,7 @@
       </c>
       <c r="N290" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; no land-use tiles in WRF: grid-cell value only</t>
+          <t>not produced by CORDEX_Cmor; header ready; no land-use tiles in WRF: grid-cell value only</t>
         </is>
       </c>
     </row>
@@ -18644,7 +18644,7 @@
       </c>
       <c r="N291" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; one value per land-use class (needs a 3-D fx writer)</t>
+          <t>not produced by CORDEX_Cmor; header ready; one value per land-use class (needs a 3-D fx writer)</t>
         </is>
       </c>
     </row>
@@ -18695,12 +18695,12 @@
       </c>
       <c r="M292" s="4" t="inlineStr">
         <is>
-          <t>SFROFF UDROFF</t>
+          <t>RUNSF RUNSB</t>
         </is>
       </c>
       <c r="N292" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; no land-use tiles in WRF: grid-cell value only</t>
+          <t>not produced by CORDEX_Cmor; header ready; no land-use tiles in WRF: grid-cell value only</t>
         </is>
       </c>
     </row>
@@ -18756,7 +18756,7 @@
       </c>
       <c r="N293" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; no land-use tiles in WRF: grid-cell value only</t>
+          <t>not produced by CORDEX_Cmor; header ready; no land-use tiles in WRF: grid-cell value only</t>
         </is>
       </c>
     </row>
@@ -18812,7 +18812,7 @@
       </c>
       <c r="N294" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; no land-use tiles in WRF: grid-cell value only</t>
+          <t>not produced by CORDEX_Cmor; header ready; no land-use tiles in WRF: grid-cell value only</t>
         </is>
       </c>
     </row>
@@ -18868,7 +18868,7 @@
       </c>
       <c r="N295" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; Noah-MP with dynamic vegetation (opt_dveg)</t>
+          <t>not produced by CORDEX_Cmor; header ready; Noah-MP with dynamic vegetation (opt_dveg)</t>
         </is>
       </c>
     </row>
@@ -18916,7 +18916,7 @@
       </c>
       <c r="N296" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; no pasture class in the WRF land-use tables</t>
+          <t>not produced by CORDEX_Cmor; header ready; no pasture class in the WRF land-use tables</t>
         </is>
       </c>
     </row>
@@ -18964,7 +18964,7 @@
       </c>
       <c r="N297" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; urban + land ice classes; LUCAS name resdiualFrac</t>
+          <t>not produced by CORDEX_Cmor; header ready; urban + land ice classes; LUCAS name resdiualFrac</t>
         </is>
       </c>
     </row>
@@ -19020,7 +19020,7 @@
       </c>
       <c r="N298" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; no land-use tiles in WRF: grid-cell value only</t>
+          <t>not produced by CORDEX_Cmor; header ready; no land-use tiles in WRF: grid-cell value only</t>
         </is>
       </c>
     </row>
@@ -19076,7 +19076,7 @@
       </c>
       <c r="N299" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor</t>
+          <t>not produced by CORDEX_Cmor; header ready</t>
         </is>
       </c>
     </row>
@@ -19132,7 +19132,7 @@
       </c>
       <c r="N300" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; no land-use tiles in WRF: grid-cell value only</t>
+          <t>not produced by CORDEX_Cmor; header ready; no land-use tiles in WRF: grid-cell value only</t>
         </is>
       </c>
     </row>
@@ -19236,7 +19236,7 @@
       </c>
       <c r="N302" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; SNOW/1000; no land-use tiles in WRF</t>
+          <t>not produced by CORDEX_Cmor; header ready; SNOW/1000; no land-use tiles in WRF</t>
         </is>
       </c>
     </row>
@@ -19292,7 +19292,7 @@
       </c>
       <c r="N303" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; no land-use tiles in WRF (Noah-MP T2MV/T2MB: vegetated/bare parts)</t>
+          <t>not produced by CORDEX_Cmor; header ready; no land-use tiles in WRF (Noah-MP T2MV/T2MB: vegetated/bare parts)</t>
         </is>
       </c>
     </row>
@@ -19348,7 +19348,7 @@
       </c>
       <c r="N304" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; Noah-MP vegetation temperature</t>
+          <t>not produced by CORDEX_Cmor; header ready; Noah-MP vegetation temperature</t>
         </is>
       </c>
     </row>
@@ -19404,7 +19404,7 @@
       </c>
       <c r="N305" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; Noah-MP bare ground temperature</t>
+          <t>not produced by CORDEX_Cmor; header ready; Noah-MP bare ground temperature</t>
         </is>
       </c>
     </row>
@@ -19556,7 +19556,7 @@
       </c>
       <c r="N308" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; MODIS class 4 (deciduous broadleaf forest)</t>
+          <t>not produced by CORDEX_Cmor; header ready; MODIS class 4 (deciduous broadleaf forest)</t>
         </is>
       </c>
     </row>
@@ -19604,7 +19604,7 @@
       </c>
       <c r="N309" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; MODIS class 2 (evergreen broadleaf forest)</t>
+          <t>not produced by CORDEX_Cmor; header ready; MODIS class 2 (evergreen broadleaf forest)</t>
         </is>
       </c>
     </row>
@@ -19652,7 +19652,7 @@
       </c>
       <c r="N310" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; MODIS class 3 (deciduous needleleaf forest)</t>
+          <t>not produced by CORDEX_Cmor; header ready; MODIS class 3 (deciduous needleleaf forest)</t>
         </is>
       </c>
     </row>
@@ -19764,7 +19764,7 @@
       </c>
       <c r="N312" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; no land-use tiles in WRF: grid-cell value only</t>
+          <t>not produced by CORDEX_Cmor; header ready; no land-use tiles in WRF: grid-cell value only</t>
         </is>
       </c>
     </row>
@@ -19868,7 +19868,7 @@
       </c>
       <c r="N314" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; derived (e.g. wrf-python cape_2d); LUCAS name CAPE</t>
+          <t>not produced by CORDEX_Cmor; header ready; derived (e.g. wrf-python cape_2d); LUCAS name CAPE</t>
         </is>
       </c>
     </row>
@@ -19924,7 +19924,7 @@
       </c>
       <c r="N315" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; derived (e.g. wrf-python cape_2d); LUCAS name CIN</t>
+          <t>not produced by CORDEX_Cmor; header ready; derived (e.g. wrf-python cape_2d); LUCAS name CIN</t>
         </is>
       </c>
     </row>
@@ -19980,7 +19980,7 @@
       </c>
       <c r="N316" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; relative vorticity on pressure levels</t>
+          <t>not produced by CORDEX_Cmor; header ready; relative vorticity on pressure levels</t>
         </is>
       </c>
     </row>
@@ -20036,7 +20036,7 @@
       </c>
       <c r="N317" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; omega = -rho g w on pressure levels</t>
+          <t>not produced by CORDEX_Cmor; header ready; omega = -rho g w on pressure levels</t>
         </is>
       </c>
     </row>
@@ -20084,7 +20084,7 @@
       </c>
       <c r="N318" s="4" t="inlineStr">
         <is>
-          <t>not produced by CORDEX_Cmor; Noah-MP soil layer thickness</t>
+          <t>not produced by CORDEX_Cmor; header ready; Noah-MP soil layer thickness</t>
         </is>
       </c>
     </row>

--- a/CORDEX_Cmor_variables.xlsx
+++ b/CORDEX_Cmor_variables.xlsx
@@ -19985,58 +19985,58 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="4" t="inlineStr">
+      <c r="A317" t="inlineStr">
         <is>
           <t>wap</t>
         </is>
       </c>
-      <c r="B317" s="4" t="inlineStr">
+      <c r="B317" t="inlineStr">
         <is>
           <t>FPS-LUCAS</t>
         </is>
       </c>
-      <c r="C317" s="4" t="inlineStr">
+      <c r="C317" t="inlineStr">
         <is>
           <t>TIER 1</t>
         </is>
       </c>
-      <c r="D317" s="4" t="inlineStr">
+      <c r="D317" t="inlineStr">
         <is>
           <t>Pa s-1</t>
         </is>
       </c>
-      <c r="E317" s="5" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F317" s="5" t="inlineStr"/>
-      <c r="G317" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="H317" s="5" t="inlineStr"/>
-      <c r="I317" s="5" t="inlineStr"/>
-      <c r="J317" s="5" t="inlineStr"/>
-      <c r="K317" s="4" t="inlineStr">
+      <c r="E317" s="3" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F317" s="3" t="inlineStr"/>
+      <c r="G317" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H317" s="3" t="inlineStr"/>
+      <c r="I317" s="3" t="inlineStr"/>
+      <c r="J317" s="3" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
         <is>
           <t>omega</t>
         </is>
       </c>
-      <c r="L317" s="4" t="inlineStr">
+      <c r="L317" t="inlineStr">
         <is>
           <t>lagrangian_tendency_of_air_pressure</t>
         </is>
       </c>
-      <c r="M317" s="4" t="inlineStr">
-        <is>
-          <t>W P PB T QVAPOR</t>
-        </is>
-      </c>
-      <c r="N317" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; omega = -rho g w on pressure levels</t>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>W T QVAPOR P PB</t>
+        </is>
+      </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_plev_wap (plev_wap varset), as wap&lt;p&gt; on each pressure level (1000 to 30 hPa); omega = -rho g w; written every 6 h</t>
         </is>
       </c>
     </row>

--- a/CORDEX_Cmor_variables.xlsx
+++ b/CORDEX_Cmor_variables.xlsx
@@ -17259,7 +17259,7 @@
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_wap (plev_wap varset), as wap&lt;p&gt; on each pressure level (1000 to 30 hPa); omega = -rho g w; written every 6 h</t>
+          <t>CORDEX_Cmor: RCM_plev_wap (plev_wap varset), as wap&lt;p&gt; on each pressure level (1000 to 30 hPa); omega = -rho g w; every wp_step hours (grid ini)</t>
         </is>
       </c>
     </row>

--- a/CORDEX_Cmor_variables.xlsx
+++ b/CORDEX_Cmor_variables.xlsx
@@ -1522,11 +1522,7 @@
       <c r="F17" s="3" t="inlineStr"/>
       <c r="G17" s="3" t="inlineStr"/>
       <c r="H17" s="3" t="inlineStr"/>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>x¹</t>
-        </is>
-      </c>
+      <c r="I17" s="3" t="inlineStr"/>
       <c r="J17" s="3" t="inlineStr"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
@@ -1579,11 +1575,7 @@
       <c r="F18" s="3" t="inlineStr"/>
       <c r="G18" s="3" t="inlineStr"/>
       <c r="H18" s="3" t="inlineStr"/>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>x¹</t>
-        </is>
-      </c>
+      <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="3" t="inlineStr"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
@@ -4029,132 +4021,132 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="A56" t="inlineStr">
         <is>
           <t>clgvi</t>
         </is>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>CORDEX-CMIP6</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>TIER 1</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>kg m-2</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F56" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G56" s="5" t="inlineStr"/>
-      <c r="H56" s="5" t="inlineStr"/>
-      <c r="I56" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J56" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="K56" s="5" t="inlineStr"/>
-      <c r="L56" s="4" t="inlineStr">
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr"/>
+      <c r="H56" s="3" t="inlineStr"/>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
         <is>
           <t>Vertical integral of mass content of graupel</t>
         </is>
       </c>
-      <c r="M56" s="4" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>atmosphere_mass_content_of_graupel</t>
         </is>
       </c>
-      <c r="N56" s="4" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>QGRAUP P PB PSFC</t>
         </is>
       </c>
-      <c r="O56" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; vertical integral</t>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_sfc_clgvi (wpth4 varset)</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="A57" t="inlineStr">
         <is>
           <t>clhvi</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>CORDEX-CMIP6</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>TIER 1</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>kg m-2</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G57" s="5" t="inlineStr"/>
-      <c r="H57" s="5" t="inlineStr"/>
-      <c r="I57" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J57" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="K57" s="5" t="inlineStr"/>
-      <c r="L57" s="4" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr"/>
+      <c r="H57" s="3" t="inlineStr"/>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
         <is>
           <t>Vertical integral of mass content of hail</t>
         </is>
       </c>
-      <c r="M57" s="4" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>atmosphere_mass_content_of_hail</t>
         </is>
       </c>
-      <c r="N57" s="4" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>QHAIL P PB PSFC</t>
         </is>
       </c>
-      <c r="O57" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; vertical integral (2-moment microphysics with hail)</t>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_sfc_clhvi (wpth4 varset); needs a microphysics with hail (QHAIL)</t>
         </is>
       </c>
     </row>
@@ -8944,59 +8936,59 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="4" t="inlineStr">
+      <c r="A127" t="inlineStr">
         <is>
           <t>wsgsmax</t>
         </is>
       </c>
-      <c r="B127" s="4" t="inlineStr">
+      <c r="B127" t="inlineStr">
         <is>
           <t>CORDEX-CMIP6</t>
         </is>
       </c>
-      <c r="C127" s="4" t="inlineStr">
+      <c r="C127" t="inlineStr">
         <is>
           <t>TIER 2</t>
         </is>
       </c>
-      <c r="D127" s="4" t="inlineStr">
+      <c r="D127" t="inlineStr">
         <is>
           <t>m s-1</t>
         </is>
       </c>
-      <c r="E127" s="5" t="inlineStr"/>
-      <c r="F127" s="5" t="inlineStr"/>
-      <c r="G127" s="5" t="inlineStr"/>
-      <c r="H127" s="5" t="inlineStr"/>
-      <c r="I127" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J127" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="K127" s="5" t="inlineStr"/>
-      <c r="L127" s="4" t="inlineStr">
+      <c r="E127" s="3" t="inlineStr"/>
+      <c r="F127" s="3" t="inlineStr"/>
+      <c r="G127" s="3" t="inlineStr"/>
+      <c r="H127" s="3" t="inlineStr"/>
+      <c r="I127" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K127" s="3" t="inlineStr"/>
+      <c r="L127" t="inlineStr">
         <is>
           <t>Daily Maximum Near-Surface Wind Speed of Gust</t>
         </is>
       </c>
-      <c r="M127" s="4" t="inlineStr">
+      <c r="M127" t="inlineStr">
         <is>
           <t>wind_speed_of_gust</t>
         </is>
       </c>
-      <c r="N127" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O127" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; no gust diagnostic in the WRF output</t>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>U10 V10 U V PH PHB HGT PBLH (b01: also T QVAPOR QCLOUD TKE_PBL)</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_sfc_wsgsmax (gust varset), UPP formula, or RCM_sfc_wsgsmax_b01, Brasseur 2001 as CDXWRF; daily maximum of the hourly gust</t>
         </is>
       </c>
     </row>
@@ -13597,11 +13589,7 @@
       <c r="F196" s="3" t="inlineStr"/>
       <c r="G196" s="3" t="inlineStr"/>
       <c r="H196" s="3" t="inlineStr"/>
-      <c r="I196" s="3" t="inlineStr">
-        <is>
-          <t>x¹</t>
-        </is>
-      </c>
+      <c r="I196" s="3" t="inlineStr"/>
       <c r="J196" s="3" t="inlineStr"/>
       <c r="K196" s="3" t="inlineStr">
         <is>
@@ -13923,11 +13911,7 @@
       <c r="F202" s="5" t="inlineStr"/>
       <c r="G202" s="5" t="inlineStr"/>
       <c r="H202" s="5" t="inlineStr"/>
-      <c r="I202" s="5" t="inlineStr">
-        <is>
-          <t>x¹</t>
-        </is>
-      </c>
+      <c r="I202" s="5" t="inlineStr"/>
       <c r="J202" s="5" t="inlineStr"/>
       <c r="K202" s="5" t="inlineStr">
         <is>
@@ -13956,67 +13940,67 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="4" t="inlineStr">
+      <c r="A203" t="inlineStr">
         <is>
           <t>hfso</t>
         </is>
       </c>
-      <c r="B203" s="4" t="inlineStr">
+      <c r="B203" t="inlineStr">
         <is>
           <t>CORDEX-CMIP6</t>
         </is>
       </c>
-      <c r="C203" s="4" t="inlineStr">
+      <c r="C203" t="inlineStr">
         <is>
           <t>TIER 2</t>
         </is>
       </c>
-      <c r="D203" s="4" t="inlineStr">
+      <c r="D203" t="inlineStr">
         <is>
           <t>W m-2</t>
         </is>
       </c>
-      <c r="E203" s="5" t="inlineStr">
+      <c r="E203" s="3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="F203" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G203" s="5" t="inlineStr"/>
-      <c r="H203" s="5" t="inlineStr"/>
-      <c r="I203" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J203" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="K203" s="5" t="inlineStr"/>
-      <c r="L203" s="4" t="inlineStr">
+      <c r="F203" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G203" s="3" t="inlineStr"/>
+      <c r="H203" s="3" t="inlineStr"/>
+      <c r="I203" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J203" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K203" s="3" t="inlineStr"/>
+      <c r="L203" t="inlineStr">
         <is>
           <t>Surface Downward Ground Heat Flux</t>
         </is>
       </c>
-      <c r="M203" s="4" t="inlineStr">
+      <c r="M203" t="inlineStr">
         <is>
           <t>surface_downward_ground_heat_flux</t>
         </is>
       </c>
-      <c r="N203" s="4" t="inlineStr">
+      <c r="N203" t="inlineStr">
         <is>
           <t>GRDFLX</t>
         </is>
       </c>
-      <c r="O203" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready</t>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_sfc_hfso (out2 varset); hourly mean of GRDFLX (positive into the soil)</t>
         </is>
       </c>
     </row>

--- a/CORDEX_Cmor_variables.xlsx
+++ b/CORDEX_Cmor_variables.xlsx
@@ -8983,7 +8983,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>U10 V10 U V PH PHB HGT PBLH (b01: also T QVAPOR QCLOUD TKE_PBL)</t>
+          <t>U10 V10 U V PH PHB HGT PBLH (b01: also T QVAPOR QCLOUD QKE)</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">

--- a/CORDEX_Cmor_variables.xlsx
+++ b/CORDEX_Cmor_variables.xlsx
@@ -8983,12 +8983,12 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>U10 V10 U V PH PHB HGT PBLH (b01: also T QVAPOR QCLOUD QKE)</t>
+          <t>U10 V10 U V PH PHB HGT PBLH T QVAPOR QCLOUD QKE</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_wsgsmax (gust varset), UPP formula, or RCM_sfc_wsgsmax_b01, Brasseur 2001 as CDXWRF; daily maximum of the hourly gust</t>
+          <t>CORDEX_Cmor: RCM_sfc_wsgsmax (gust varset); Brasseur 2001 as CDXWRF if QKE is in wrfout (T QVAPOR QCLOUD QKE), else UPP formula (U10 V10); daily maximum of the hourly gust</t>
         </is>
       </c>
     </row>

--- a/CORDEX_Cmor_variables.xlsx
+++ b/CORDEX_Cmor_variables.xlsx
@@ -13675,55 +13675,51 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="4" t="inlineStr">
+      <c r="A198" t="inlineStr">
         <is>
           <t>rootd</t>
         </is>
       </c>
-      <c r="B198" s="4" t="inlineStr">
+      <c r="B198" t="inlineStr">
         <is>
           <t>CORDEX-CMIP6</t>
         </is>
       </c>
-      <c r="C198" s="4" t="inlineStr">
+      <c r="C198" t="inlineStr">
         <is>
           <t>TIER 2</t>
         </is>
       </c>
-      <c r="D198" s="4" t="inlineStr">
+      <c r="D198" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="E198" s="5" t="inlineStr"/>
-      <c r="F198" s="5" t="inlineStr"/>
-      <c r="G198" s="5" t="inlineStr"/>
-      <c r="H198" s="5" t="inlineStr"/>
-      <c r="I198" s="5" t="inlineStr"/>
-      <c r="J198" s="5" t="inlineStr"/>
-      <c r="K198" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="L198" s="4" t="inlineStr">
+      <c r="E198" s="3" t="inlineStr"/>
+      <c r="F198" s="3" t="inlineStr"/>
+      <c r="G198" s="3" t="inlineStr"/>
+      <c r="H198" s="3" t="inlineStr"/>
+      <c r="I198" s="3" t="inlineStr"/>
+      <c r="J198" s="3" t="inlineStr"/>
+      <c r="K198" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
         <is>
           <t>Maximum Root Depth</t>
         </is>
       </c>
-      <c r="M198" s="4" t="inlineStr">
+      <c r="M198" t="inlineStr">
         <is>
           <t>root_depth</t>
         </is>
       </c>
-      <c r="N198" s="4" t="inlineStr">
-        <is>
-          <t>LU_INDEX ZS DZS</t>
-        </is>
-      </c>
-      <c r="O198" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; root layers per vegetation class (NROOT of VEGPARM.TBL)</t>
+      <c r="N198" t="inlineStr"/>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_fx_rootd (fx varset); sum of the top NROOT soil layers (VEGPARM.TBL NROOT of the dominant class, LU_INDEX of geo_em)</t>
         </is>
       </c>
     </row>
@@ -13887,55 +13883,55 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="4" t="inlineStr">
+      <c r="A202" t="inlineStr">
         <is>
           <t>areacella</t>
         </is>
       </c>
-      <c r="B202" s="4" t="inlineStr">
+      <c r="B202" t="inlineStr">
         <is>
           <t>CORDEX-CMIP6, FPS-LUCAS</t>
         </is>
       </c>
-      <c r="C202" s="4" t="inlineStr">
+      <c r="C202" t="inlineStr">
         <is>
           <t>TIER 2; LUCAS CORE</t>
         </is>
       </c>
-      <c r="D202" s="4" t="inlineStr">
+      <c r="D202" t="inlineStr">
         <is>
           <t>m2</t>
         </is>
       </c>
-      <c r="E202" s="5" t="inlineStr"/>
-      <c r="F202" s="5" t="inlineStr"/>
-      <c r="G202" s="5" t="inlineStr"/>
-      <c r="H202" s="5" t="inlineStr"/>
-      <c r="I202" s="5" t="inlineStr"/>
-      <c r="J202" s="5" t="inlineStr"/>
-      <c r="K202" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="L202" s="4" t="inlineStr">
+      <c r="E202" s="3" t="inlineStr"/>
+      <c r="F202" s="3" t="inlineStr"/>
+      <c r="G202" s="3" t="inlineStr"/>
+      <c r="H202" s="3" t="inlineStr"/>
+      <c r="I202" s="3" t="inlineStr"/>
+      <c r="J202" s="3" t="inlineStr"/>
+      <c r="K202" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
         <is>
           <t>Atmosphere Grid-Cell Area</t>
         </is>
       </c>
-      <c r="M202" s="4" t="inlineStr">
+      <c r="M202" t="inlineStr">
         <is>
           <t>cell_area</t>
         </is>
       </c>
-      <c r="N202" s="4" t="inlineStr">
-        <is>
-          <t>MAPFAC_MX MAPFAC_MY</t>
-        </is>
-      </c>
-      <c r="O202" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; geo_em; DX*DY/(MAPFAC_MX*MAPFAC_MY) with the DX/DY attributes</t>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>MAPFAC_MX MAPFAC_MY MAPFAC_M</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_fx_areacella (fx varset); DX*DY/(MAPFAC_MX*MAPFAC_MY) of the geo_em file</t>
         </is>
       </c>
     </row>

--- a/CORDEX_Cmor_variables.xlsx
+++ b/CORDEX_Cmor_variables.xlsx
@@ -13716,10 +13716,14 @@
           <t>root_depth</t>
         </is>
       </c>
-      <c r="N198" t="inlineStr"/>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>LU_INDEX LANDMASK</t>
+        </is>
+      </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_fx_rootd (fx varset); sum of the top NROOT soil layers (VEGPARM.TBL NROOT of the dominant class, LU_INDEX of geo_em)</t>
+          <t>CORDEX_Cmor: RCM_fx_rootd (fx varset); from geo_em; sum of the top NROOT soil layers (VEGPARM.TBL NROOT of the dominant class, LU_INDEX of geo_em)</t>
         </is>
       </c>
     </row>

--- a/CORDEX_Cmor_variables.xlsx
+++ b/CORDEX_Cmor_variables.xlsx
@@ -9639,368 +9639,368 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="4" t="inlineStr">
+      <c r="A138" t="inlineStr">
         <is>
           <t>cape</t>
         </is>
       </c>
-      <c r="B138" s="4" t="inlineStr">
+      <c r="B138" t="inlineStr">
         <is>
           <t>CORDEX-CMIP6, FPS-LUCAS</t>
         </is>
       </c>
-      <c r="C138" s="4" t="inlineStr">
+      <c r="C138" t="inlineStr">
         <is>
           <t>TIER 2; LUCAS TIER 1</t>
         </is>
       </c>
-      <c r="D138" s="4" t="inlineStr">
+      <c r="D138" t="inlineStr">
         <is>
           <t>J kg-1</t>
         </is>
       </c>
-      <c r="E138" s="5" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F138" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G138" s="5" t="inlineStr"/>
-      <c r="H138" s="5" t="inlineStr"/>
-      <c r="I138" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J138" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="K138" s="5" t="inlineStr"/>
-      <c r="L138" s="4" t="inlineStr">
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="inlineStr"/>
+      <c r="H138" s="3" t="inlineStr"/>
+      <c r="I138" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K138" s="3" t="inlineStr"/>
+      <c r="L138" t="inlineStr">
         <is>
           <t>Convective Available Potential Energy</t>
         </is>
       </c>
-      <c r="M138" s="4" t="inlineStr">
+      <c r="M138" t="inlineStr">
         <is>
           <t>atmosphere_convective_available_potential_energy_wrt_surface</t>
         </is>
       </c>
-      <c r="N138" s="4" t="inlineStr">
-        <is>
-          <t>P PB T QVAPOR PH PHB HGT PSFC</t>
-        </is>
-      </c>
-      <c r="O138" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; derived (e.g. wrf-python cape_2d)</t>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>P PB T QVAPOR PH PHB HGT</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_sfc_cape (cape varset; cin li lcl archived as cape_x); surface parcel, Romps 2017 LCL, Bolton 1980 pseudo-adiabat, virtual temperature (RIP/wrf-python EL/LFC)</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="4" t="inlineStr">
+      <c r="A139" t="inlineStr">
         <is>
           <t>li</t>
         </is>
       </c>
-      <c r="B139" s="4" t="inlineStr">
+      <c r="B139" t="inlineStr">
         <is>
           <t>CORDEX-CMIP6</t>
         </is>
       </c>
-      <c r="C139" s="4" t="inlineStr">
+      <c r="C139" t="inlineStr">
         <is>
           <t>TIER 2</t>
         </is>
       </c>
-      <c r="D139" s="4" t="inlineStr">
+      <c r="D139" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="E139" s="5" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F139" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G139" s="5" t="inlineStr"/>
-      <c r="H139" s="5" t="inlineStr"/>
-      <c r="I139" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J139" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="K139" s="5" t="inlineStr"/>
-      <c r="L139" s="4" t="inlineStr">
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="inlineStr"/>
+      <c r="H139" s="3" t="inlineStr"/>
+      <c r="I139" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K139" s="3" t="inlineStr"/>
+      <c r="L139" t="inlineStr">
         <is>
           <t>Lifted Index</t>
         </is>
       </c>
-      <c r="M139" s="4" t="inlineStr">
+      <c r="M139" t="inlineStr">
         <is>
           <t>temperature_difference_between_ambient_air_and_air_lifted_adiabatically_from_the_surface</t>
         </is>
       </c>
-      <c r="N139" s="4" t="inlineStr">
-        <is>
-          <t>P PB T QVAPOR T2 Q2 PSFC</t>
-        </is>
-      </c>
-      <c r="O139" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; derived (lifted index at 500 hPa)</t>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>P PB T QVAPOR PH PHB HGT</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_sfc_cape (cape varset; cin li lcl archived as cape_x); with cape; at 500 hPa</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="4" t="inlineStr">
+      <c r="A140" t="inlineStr">
         <is>
           <t>cin</t>
         </is>
       </c>
-      <c r="B140" s="4" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>CORDEX-CMIP6, FPS-LUCAS</t>
         </is>
       </c>
-      <c r="C140" s="4" t="inlineStr">
+      <c r="C140" t="inlineStr">
         <is>
           <t>TIER 2; LUCAS TIER 1</t>
         </is>
       </c>
-      <c r="D140" s="4" t="inlineStr">
+      <c r="D140" t="inlineStr">
         <is>
           <t>J kg-1</t>
         </is>
       </c>
-      <c r="E140" s="5" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F140" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G140" s="5" t="inlineStr"/>
-      <c r="H140" s="5" t="inlineStr"/>
-      <c r="I140" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J140" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="K140" s="5" t="inlineStr"/>
-      <c r="L140" s="4" t="inlineStr">
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="inlineStr"/>
+      <c r="H140" s="3" t="inlineStr"/>
+      <c r="I140" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K140" s="3" t="inlineStr"/>
+      <c r="L140" t="inlineStr">
         <is>
           <t>Convective Inhibition</t>
         </is>
       </c>
-      <c r="M140" s="4" t="inlineStr">
+      <c r="M140" t="inlineStr">
         <is>
           <t>atmosphere_convective_inhibition_wrt_surface</t>
         </is>
       </c>
-      <c r="N140" s="4" t="inlineStr">
-        <is>
-          <t>P PB T QVAPOR PH PHB HGT PSFC</t>
-        </is>
-      </c>
-      <c r="O140" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; derived (e.g. wrf-python cape_2d)</t>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>P PB T QVAPOR PH PHB HGT</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_sfc_cape (cape varset; cin li lcl archived as cape_x); with cape; 0 where there is no CAPE</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="4" t="inlineStr">
+      <c r="A141" t="inlineStr">
         <is>
           <t>capemax</t>
         </is>
       </c>
-      <c r="B141" s="4" t="inlineStr">
+      <c r="B141" t="inlineStr">
         <is>
           <t>CORDEX-CMIP6</t>
         </is>
       </c>
-      <c r="C141" s="4" t="inlineStr">
+      <c r="C141" t="inlineStr">
         <is>
           <t>TIER 2</t>
         </is>
       </c>
-      <c r="D141" s="4" t="inlineStr">
+      <c r="D141" t="inlineStr">
         <is>
           <t>J kg-1</t>
         </is>
       </c>
-      <c r="E141" s="5" t="inlineStr"/>
-      <c r="F141" s="5" t="inlineStr"/>
-      <c r="G141" s="5" t="inlineStr"/>
-      <c r="H141" s="5" t="inlineStr"/>
-      <c r="I141" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J141" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="K141" s="5" t="inlineStr"/>
-      <c r="L141" s="4" t="inlineStr">
+      <c r="E141" s="3" t="inlineStr"/>
+      <c r="F141" s="3" t="inlineStr"/>
+      <c r="G141" s="3" t="inlineStr"/>
+      <c r="H141" s="3" t="inlineStr"/>
+      <c r="I141" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K141" s="3" t="inlineStr"/>
+      <c r="L141" t="inlineStr">
         <is>
           <t>Daily Maximum Convective Available Potential Energy</t>
         </is>
       </c>
-      <c r="M141" s="4" t="inlineStr">
+      <c r="M141" t="inlineStr">
         <is>
           <t>atmosphere_convective_available_potential_energy_wrt_surface</t>
         </is>
       </c>
-      <c r="N141" s="4" t="inlineStr">
-        <is>
-          <t>P PB T QVAPOR PH PHB HGT PSFC</t>
-        </is>
-      </c>
-      <c r="O141" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; daily maximum of cape</t>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>P PB T QVAPOR PH PHB HGT</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: tools/aggregate.sh, daily maximum of the hourly cape (RCM_sfc_cape, cape varset)</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="4" t="inlineStr">
+      <c r="A142" t="inlineStr">
         <is>
           <t>limax</t>
         </is>
       </c>
-      <c r="B142" s="4" t="inlineStr">
+      <c r="B142" t="inlineStr">
         <is>
           <t>CORDEX-CMIP6</t>
         </is>
       </c>
-      <c r="C142" s="4" t="inlineStr">
+      <c r="C142" t="inlineStr">
         <is>
           <t>TIER 2</t>
         </is>
       </c>
-      <c r="D142" s="4" t="inlineStr">
+      <c r="D142" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="E142" s="5" t="inlineStr"/>
-      <c r="F142" s="5" t="inlineStr"/>
-      <c r="G142" s="5" t="inlineStr"/>
-      <c r="H142" s="5" t="inlineStr"/>
-      <c r="I142" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J142" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="K142" s="5" t="inlineStr"/>
-      <c r="L142" s="4" t="inlineStr">
+      <c r="E142" s="3" t="inlineStr"/>
+      <c r="F142" s="3" t="inlineStr"/>
+      <c r="G142" s="3" t="inlineStr"/>
+      <c r="H142" s="3" t="inlineStr"/>
+      <c r="I142" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K142" s="3" t="inlineStr"/>
+      <c r="L142" t="inlineStr">
         <is>
           <t>Daily Maximum Lifted Index</t>
         </is>
       </c>
-      <c r="M142" s="4" t="inlineStr">
+      <c r="M142" t="inlineStr">
         <is>
           <t>temperature_difference_between_ambient_air_and_air_lifted_adiabatically_from_the_surface</t>
         </is>
       </c>
-      <c r="N142" s="4" t="inlineStr">
-        <is>
-          <t>P PB T QVAPOR T2 Q2 PSFC</t>
-        </is>
-      </c>
-      <c r="O142" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; daily maximum of li</t>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>P PB T QVAPOR PH PHB HGT</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: tools/aggregate.sh, daily maximum of the hourly li (RCM_sfc_cape, cape varset)</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="4" t="inlineStr">
+      <c r="A143" t="inlineStr">
         <is>
           <t>cinmax</t>
         </is>
       </c>
-      <c r="B143" s="4" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>CORDEX-CMIP6</t>
         </is>
       </c>
-      <c r="C143" s="4" t="inlineStr">
+      <c r="C143" t="inlineStr">
         <is>
           <t>TIER 2</t>
         </is>
       </c>
-      <c r="D143" s="4" t="inlineStr">
+      <c r="D143" t="inlineStr">
         <is>
           <t>J kg-1</t>
         </is>
       </c>
-      <c r="E143" s="5" t="inlineStr"/>
-      <c r="F143" s="5" t="inlineStr"/>
-      <c r="G143" s="5" t="inlineStr"/>
-      <c r="H143" s="5" t="inlineStr"/>
-      <c r="I143" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J143" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="K143" s="5" t="inlineStr"/>
-      <c r="L143" s="4" t="inlineStr">
+      <c r="E143" s="3" t="inlineStr"/>
+      <c r="F143" s="3" t="inlineStr"/>
+      <c r="G143" s="3" t="inlineStr"/>
+      <c r="H143" s="3" t="inlineStr"/>
+      <c r="I143" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K143" s="3" t="inlineStr"/>
+      <c r="L143" t="inlineStr">
         <is>
           <t>Daily Maximum Convective Inhibition</t>
         </is>
       </c>
-      <c r="M143" s="4" t="inlineStr">
+      <c r="M143" t="inlineStr">
         <is>
           <t>atmosphere_convective_inhibition_wrt_surface</t>
         </is>
       </c>
-      <c r="N143" s="4" t="inlineStr">
-        <is>
-          <t>P PB T QVAPOR PH PHB HGT PSFC</t>
-        </is>
-      </c>
-      <c r="O143" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; daily maximum of cin</t>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>P PB T QVAPOR PH PHB HGT</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: tools/aggregate.sh, daily maximum of the hourly cin (RCM_sfc_cape, cape varset)</t>
         </is>
       </c>
     </row>

--- a/CORDEX_Cmor_variables.xlsx
+++ b/CORDEX_Cmor_variables.xlsx
@@ -15419,7 +15419,7 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_lsmflx (lsm varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_evspsblsoi (lsm varset)</t>
         </is>
       </c>
     </row>
@@ -15476,7 +15476,7 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_lsmflx (lsm varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_evspsblveg (lsm varset)</t>
         </is>
       </c>
     </row>
@@ -16787,7 +16787,7 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_lsmflx (lsm varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_tran (lsm varset)</t>
         </is>
       </c>
     </row>

--- a/CORDEX_Cmor_variables.xlsx
+++ b/CORDEX_Cmor_variables.xlsx
@@ -15020,7 +15020,7 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_lsm (lsm varset); LUCAS name LAI</t>
+          <t>CORDEX_Cmor: RCM_sfc_lai (lsm varset); LUCAS name LAI</t>
         </is>
       </c>
     </row>
@@ -15077,7 +15077,7 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_lsm (lsm varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_alb (lsm varset)</t>
         </is>
       </c>
     </row>

--- a/CORDEX_Cmor_variables.xlsx
+++ b/CORDEX_Cmor_variables.xlsx
@@ -15310,59 +15310,59 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="4" t="inlineStr">
+      <c r="A225" t="inlineStr">
         <is>
           <t>cVeg</t>
         </is>
       </c>
-      <c r="B225" s="4" t="inlineStr">
+      <c r="B225" t="inlineStr">
         <is>
           <t>FPS-LUCAS</t>
         </is>
       </c>
-      <c r="C225" s="4" t="inlineStr">
+      <c r="C225" t="inlineStr">
         <is>
           <t>TIER 1</t>
         </is>
       </c>
-      <c r="D225" s="4" t="inlineStr">
+      <c r="D225" t="inlineStr">
         <is>
           <t>kg m-2</t>
         </is>
       </c>
-      <c r="E225" s="5" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F225" s="5" t="inlineStr"/>
-      <c r="G225" s="5" t="inlineStr"/>
-      <c r="H225" s="5" t="inlineStr"/>
-      <c r="I225" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J225" s="5" t="inlineStr"/>
-      <c r="K225" s="5" t="inlineStr"/>
-      <c r="L225" s="4" t="inlineStr">
+      <c r="E225" s="3" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F225" s="3" t="inlineStr"/>
+      <c r="G225" s="3" t="inlineStr"/>
+      <c r="H225" s="3" t="inlineStr"/>
+      <c r="I225" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J225" s="3" t="inlineStr"/>
+      <c r="K225" s="3" t="inlineStr"/>
+      <c r="L225" t="inlineStr">
         <is>
           <t>Carbon mass per unit area in vegetation.</t>
         </is>
       </c>
-      <c r="M225" s="4" t="inlineStr">
+      <c r="M225" t="inlineStr">
         <is>
           <t>vegetation_carbon_content</t>
         </is>
       </c>
-      <c r="N225" s="4" t="inlineStr">
-        <is>
-          <t>LFMASS STMASS WOOD</t>
-        </is>
-      </c>
-      <c r="O225" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; Noah-MP with dynamic vegetation (opt_dveg)</t>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>LFMASS RTMASS STMASS WOOD</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_sfc_cVeg (lsm varset); meaningful with Noah-MP dynamic vegetation (opt_dveg) only</t>
         </is>
       </c>
     </row>
@@ -15538,629 +15538,629 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="4" t="inlineStr">
+      <c r="A229" t="inlineStr">
         <is>
           <t>hflsLut</t>
         </is>
       </c>
-      <c r="B229" s="4" t="inlineStr">
+      <c r="B229" t="inlineStr">
         <is>
           <t>FPS-LUCAS</t>
         </is>
       </c>
-      <c r="C229" s="4" t="inlineStr">
+      <c r="C229" t="inlineStr">
         <is>
           <t>TIER 1</t>
         </is>
       </c>
-      <c r="D229" s="4" t="inlineStr">
+      <c r="D229" t="inlineStr">
         <is>
           <t>W m-2</t>
         </is>
       </c>
-      <c r="E229" s="5" t="inlineStr">
+      <c r="E229" s="3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="F229" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G229" s="5" t="inlineStr"/>
-      <c r="H229" s="5" t="inlineStr"/>
-      <c r="I229" s="5" t="inlineStr"/>
-      <c r="J229" s="5" t="inlineStr"/>
-      <c r="K229" s="5" t="inlineStr"/>
-      <c r="L229" s="4" t="inlineStr">
+      <c r="F229" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G229" s="3" t="inlineStr"/>
+      <c r="H229" s="3" t="inlineStr"/>
+      <c r="I229" s="3" t="inlineStr"/>
+      <c r="J229" s="3" t="inlineStr"/>
+      <c r="K229" s="3" t="inlineStr"/>
+      <c r="L229" t="inlineStr">
         <is>
           <t>Latent Heat Flux on Land-Use Tile</t>
         </is>
       </c>
-      <c r="M229" s="4" t="inlineStr">
+      <c r="M229" t="inlineStr">
         <is>
           <t>surface_upward_latent_heat_flux</t>
         </is>
       </c>
-      <c r="N229" s="4" t="inlineStr">
+      <c r="N229" t="inlineStr">
         <is>
           <t>LH</t>
         </is>
       </c>
-      <c r="O229" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; no land-use tiles in WRF: grid-cell value only</t>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_sfc_hfls (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
         </is>
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="4" t="inlineStr">
+      <c r="A230" t="inlineStr">
         <is>
           <t>hfssLut</t>
         </is>
       </c>
-      <c r="B230" s="4" t="inlineStr">
+      <c r="B230" t="inlineStr">
         <is>
           <t>FPS-LUCAS</t>
         </is>
       </c>
-      <c r="C230" s="4" t="inlineStr">
+      <c r="C230" t="inlineStr">
         <is>
           <t>TIER 1</t>
         </is>
       </c>
-      <c r="D230" s="4" t="inlineStr">
+      <c r="D230" t="inlineStr">
         <is>
           <t>W m-2</t>
         </is>
       </c>
-      <c r="E230" s="5" t="inlineStr">
+      <c r="E230" s="3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="F230" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G230" s="5" t="inlineStr"/>
-      <c r="H230" s="5" t="inlineStr"/>
-      <c r="I230" s="5" t="inlineStr"/>
-      <c r="J230" s="5" t="inlineStr"/>
-      <c r="K230" s="5" t="inlineStr"/>
-      <c r="L230" s="4" t="inlineStr">
+      <c r="F230" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G230" s="3" t="inlineStr"/>
+      <c r="H230" s="3" t="inlineStr"/>
+      <c r="I230" s="3" t="inlineStr"/>
+      <c r="J230" s="3" t="inlineStr"/>
+      <c r="K230" s="3" t="inlineStr"/>
+      <c r="L230" t="inlineStr">
         <is>
           <t>Sensible Heat Flux on Land-Use Tile</t>
         </is>
       </c>
-      <c r="M230" s="4" t="inlineStr">
+      <c r="M230" t="inlineStr">
         <is>
           <t>surface_upward_sensible_heat_flux</t>
         </is>
       </c>
-      <c r="N230" s="4" t="inlineStr">
+      <c r="N230" t="inlineStr">
         <is>
           <t>HFX</t>
         </is>
       </c>
-      <c r="O230" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; no land-use tiles in WRF: grid-cell value only</t>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_sfc_hfss (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
         </is>
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="4" t="inlineStr">
+      <c r="A231" t="inlineStr">
         <is>
           <t>hussLut</t>
         </is>
       </c>
-      <c r="B231" s="4" t="inlineStr">
+      <c r="B231" t="inlineStr">
         <is>
           <t>FPS-LUCAS</t>
         </is>
       </c>
-      <c r="C231" s="4" t="inlineStr">
+      <c r="C231" t="inlineStr">
         <is>
           <t>TIER 1</t>
         </is>
       </c>
-      <c r="D231" s="4" t="inlineStr">
+      <c r="D231" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E231" s="5" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F231" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G231" s="5" t="inlineStr"/>
-      <c r="H231" s="5" t="inlineStr"/>
-      <c r="I231" s="5" t="inlineStr"/>
-      <c r="J231" s="5" t="inlineStr"/>
-      <c r="K231" s="5" t="inlineStr"/>
-      <c r="L231" s="4" t="inlineStr">
+      <c r="E231" s="3" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F231" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G231" s="3" t="inlineStr"/>
+      <c r="H231" s="3" t="inlineStr"/>
+      <c r="I231" s="3" t="inlineStr"/>
+      <c r="J231" s="3" t="inlineStr"/>
+      <c r="K231" s="3" t="inlineStr"/>
+      <c r="L231" t="inlineStr">
         <is>
           <t>Normally, the specific humidity should be reported at the 2 meter height</t>
         </is>
       </c>
-      <c r="M231" s="4" t="inlineStr">
+      <c r="M231" t="inlineStr">
         <is>
           <t>specific_humidity</t>
         </is>
       </c>
-      <c r="N231" s="4" t="inlineStr">
+      <c r="N231" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="O231" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; no land-use tiles in WRF (Noah-MP Q2MV/Q2MB: vegetated/bare parts)</t>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_sfc_huss (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
         </is>
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="4" t="inlineStr">
+      <c r="A232" t="inlineStr">
         <is>
           <t>interception</t>
         </is>
       </c>
-      <c r="B232" s="4" t="inlineStr">
+      <c r="B232" t="inlineStr">
         <is>
           <t>FPS-LUCAS</t>
         </is>
       </c>
-      <c r="C232" s="4" t="inlineStr">
+      <c r="C232" t="inlineStr">
         <is>
           <t>TIER 1</t>
         </is>
       </c>
-      <c r="D232" s="4" t="inlineStr">
+      <c r="D232" t="inlineStr">
         <is>
           <t>kg m-2</t>
         </is>
       </c>
-      <c r="E232" s="5" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F232" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G232" s="5" t="inlineStr"/>
-      <c r="H232" s="5" t="inlineStr"/>
-      <c r="I232" s="5" t="inlineStr"/>
-      <c r="J232" s="5" t="inlineStr"/>
-      <c r="K232" s="5" t="inlineStr"/>
-      <c r="L232" s="4" t="inlineStr">
+      <c r="E232" s="3" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F232" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G232" s="3" t="inlineStr"/>
+      <c r="H232" s="3" t="inlineStr"/>
+      <c r="I232" s="3" t="inlineStr"/>
+      <c r="J232" s="3" t="inlineStr"/>
+      <c r="K232" s="3" t="inlineStr"/>
+      <c r="L232" t="inlineStr">
         <is>
           <t>water intercepted</t>
         </is>
       </c>
-      <c r="M232" s="4" t="inlineStr">
+      <c r="M232" t="inlineStr">
         <is>
           <t>canopy_water_amount</t>
         </is>
       </c>
-      <c r="N232" s="4" t="inlineStr">
+      <c r="N232" t="inlineStr">
         <is>
           <t>CANLIQ CANICE</t>
         </is>
       </c>
-      <c r="O232" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; Noah-MP canopy water</t>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_sfc_interception (lsm varset)</t>
         </is>
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="4" t="inlineStr">
+      <c r="A233" t="inlineStr">
         <is>
           <t>irrLut</t>
         </is>
       </c>
-      <c r="B233" s="4" t="inlineStr">
+      <c r="B233" t="inlineStr">
         <is>
           <t>FPS-LUCAS</t>
         </is>
       </c>
-      <c r="C233" s="4" t="inlineStr">
+      <c r="C233" t="inlineStr">
         <is>
           <t>TIER 1</t>
         </is>
       </c>
-      <c r="D233" s="4" t="inlineStr">
+      <c r="D233" t="inlineStr">
         <is>
           <t>kg m-2 s-1</t>
         </is>
       </c>
-      <c r="E233" s="5" t="inlineStr">
+      <c r="E233" s="3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="F233" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G233" s="5" t="inlineStr"/>
-      <c r="H233" s="5" t="inlineStr"/>
-      <c r="I233" s="5" t="inlineStr"/>
-      <c r="J233" s="5" t="inlineStr"/>
-      <c r="K233" s="5" t="inlineStr"/>
-      <c r="L233" s="4" t="inlineStr">
+      <c r="F233" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G233" s="3" t="inlineStr"/>
+      <c r="H233" s="3" t="inlineStr"/>
+      <c r="I233" s="3" t="inlineStr"/>
+      <c r="J233" s="3" t="inlineStr"/>
+      <c r="K233" s="3" t="inlineStr"/>
+      <c r="L233" t="inlineStr">
         <is>
           <t>surface_downward_mass_flux_of_water_due_to_irrigation</t>
         </is>
       </c>
-      <c r="M233" s="4" t="inlineStr">
+      <c r="M233" t="inlineStr">
         <is>
           <t>surface_downward_mass_flux_of_water_due_to_irrigation</t>
         </is>
       </c>
-      <c r="N233" s="4" t="inlineStr">
-        <is>
-          <t>IRWATSI IRWATMI IRWATFI</t>
-        </is>
-      </c>
-      <c r="O233" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; Noah-MP irrigation (opt_irr); no land-use tiles</t>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>IRSIVOL IRMIVOL IRFIVOL</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_sfc_irrLut (irr varset); Noah-MP irrigation (opt_irr); add IRSIVOL IRMIVOL IRFIVOL to wrfout (iofields); no land-use tiles: grid-cell value</t>
         </is>
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="4" t="inlineStr">
+      <c r="A234" t="inlineStr">
         <is>
           <t>laiLut</t>
         </is>
       </c>
-      <c r="B234" s="4" t="inlineStr">
+      <c r="B234" t="inlineStr">
         <is>
           <t>FPS-LUCAS</t>
         </is>
       </c>
-      <c r="C234" s="4" t="inlineStr">
+      <c r="C234" t="inlineStr">
         <is>
           <t>TIER 1</t>
         </is>
       </c>
-      <c r="D234" s="4" t="inlineStr">
+      <c r="D234" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E234" s="5" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F234" s="5" t="inlineStr"/>
-      <c r="G234" s="5" t="inlineStr"/>
-      <c r="H234" s="5" t="inlineStr"/>
-      <c r="I234" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J234" s="5" t="inlineStr"/>
-      <c r="K234" s="5" t="inlineStr"/>
-      <c r="L234" s="4" t="inlineStr">
+      <c r="E234" s="3" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F234" s="3" t="inlineStr"/>
+      <c r="G234" s="3" t="inlineStr"/>
+      <c r="H234" s="3" t="inlineStr"/>
+      <c r="I234" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J234" s="3" t="inlineStr"/>
+      <c r="K234" s="3" t="inlineStr"/>
+      <c r="L234" t="inlineStr">
         <is>
           <t>Leaf Area Index on Land-Use Tile</t>
         </is>
       </c>
-      <c r="M234" s="4" t="inlineStr">
+      <c r="M234" t="inlineStr">
         <is>
           <t>leaf_area_index</t>
         </is>
       </c>
-      <c r="N234" s="4" t="inlineStr">
+      <c r="N234" t="inlineStr">
         <is>
           <t>LAI</t>
         </is>
       </c>
-      <c r="O234" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; no land-use tiles in WRF: grid-cell value only</t>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_sfc_lai (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
         </is>
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="4" t="inlineStr">
+      <c r="A235" t="inlineStr">
         <is>
           <t>landCoverFrac</t>
         </is>
       </c>
-      <c r="B235" s="4" t="inlineStr">
+      <c r="B235" t="inlineStr">
         <is>
           <t>FPS-LUCAS</t>
         </is>
       </c>
-      <c r="C235" s="4" t="inlineStr">
+      <c r="C235" t="inlineStr">
         <is>
           <t>TIER 1</t>
         </is>
       </c>
-      <c r="D235" s="4" t="inlineStr">
+      <c r="D235" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E235" s="5" t="inlineStr"/>
-      <c r="F235" s="5" t="inlineStr"/>
-      <c r="G235" s="5" t="inlineStr"/>
-      <c r="H235" s="5" t="inlineStr"/>
-      <c r="I235" s="5" t="inlineStr">
+      <c r="E235" s="3" t="inlineStr"/>
+      <c r="F235" s="3" t="inlineStr"/>
+      <c r="G235" s="3" t="inlineStr"/>
+      <c r="H235" s="3" t="inlineStr"/>
+      <c r="I235" s="3" t="inlineStr">
         <is>
           <t>x¹</t>
         </is>
       </c>
-      <c r="J235" s="5" t="inlineStr"/>
-      <c r="K235" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="L235" s="4" t="inlineStr">
+      <c r="J235" s="3" t="inlineStr"/>
+      <c r="K235" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
         <is>
           <t>Percentage of Area by Vegetation or Land-Cover Category</t>
         </is>
       </c>
-      <c r="M235" s="4" t="inlineStr">
+      <c r="M235" t="inlineStr">
         <is>
           <t>area_fraction</t>
         </is>
       </c>
-      <c r="N235" s="4" t="inlineStr">
+      <c r="N235" t="inlineStr">
         <is>
           <t>LANDUSEF</t>
         </is>
       </c>
-      <c r="O235" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; one value per land-use class (needs a 3-D fx writer)</t>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_fx_landCoverFrac (fx varset)</t>
         </is>
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="4" t="inlineStr">
+      <c r="A236" t="inlineStr">
         <is>
           <t>mrroLut</t>
         </is>
       </c>
-      <c r="B236" s="4" t="inlineStr">
+      <c r="B236" t="inlineStr">
         <is>
           <t>FPS-LUCAS</t>
         </is>
       </c>
-      <c r="C236" s="4" t="inlineStr">
+      <c r="C236" t="inlineStr">
         <is>
           <t>TIER 1</t>
         </is>
       </c>
-      <c r="D236" s="4" t="inlineStr">
+      <c r="D236" t="inlineStr">
         <is>
           <t>kg m-2 s-1</t>
         </is>
       </c>
-      <c r="E236" s="5" t="inlineStr">
+      <c r="E236" s="3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="F236" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G236" s="5" t="inlineStr"/>
-      <c r="H236" s="5" t="inlineStr"/>
-      <c r="I236" s="5" t="inlineStr"/>
-      <c r="J236" s="5" t="inlineStr"/>
-      <c r="K236" s="5" t="inlineStr"/>
-      <c r="L236" s="4" t="inlineStr">
+      <c r="F236" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G236" s="3" t="inlineStr"/>
+      <c r="H236" s="3" t="inlineStr"/>
+      <c r="I236" s="3" t="inlineStr"/>
+      <c r="J236" s="3" t="inlineStr"/>
+      <c r="K236" s="3" t="inlineStr"/>
+      <c r="L236" t="inlineStr">
         <is>
           <t>Total Runoff on Land-Use Tile</t>
         </is>
       </c>
-      <c r="M236" s="4" t="inlineStr">
+      <c r="M236" t="inlineStr">
         <is>
           <t>runoff_flux</t>
         </is>
       </c>
-      <c r="N236" s="4" t="inlineStr">
-        <is>
-          <t>RUNSF RUNSB</t>
-        </is>
-      </c>
-      <c r="O236" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; no land-use tiles in WRF: grid-cell value only</t>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>RUNSB RUNSF</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_sfc_mrro (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
         </is>
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="4" t="inlineStr">
+      <c r="A237" t="inlineStr">
         <is>
           <t>mrsoLut</t>
         </is>
       </c>
-      <c r="B237" s="4" t="inlineStr">
+      <c r="B237" t="inlineStr">
         <is>
           <t>FPS-LUCAS</t>
         </is>
       </c>
-      <c r="C237" s="4" t="inlineStr">
+      <c r="C237" t="inlineStr">
         <is>
           <t>TIER 1</t>
         </is>
       </c>
-      <c r="D237" s="4" t="inlineStr">
+      <c r="D237" t="inlineStr">
         <is>
           <t>kg m-2</t>
         </is>
       </c>
-      <c r="E237" s="5" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F237" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G237" s="5" t="inlineStr"/>
-      <c r="H237" s="5" t="inlineStr"/>
-      <c r="I237" s="5" t="inlineStr"/>
-      <c r="J237" s="5" t="inlineStr"/>
-      <c r="K237" s="5" t="inlineStr"/>
-      <c r="L237" s="4" t="inlineStr">
+      <c r="E237" s="3" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F237" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G237" s="3" t="inlineStr"/>
+      <c r="H237" s="3" t="inlineStr"/>
+      <c r="I237" s="3" t="inlineStr"/>
+      <c r="J237" s="3" t="inlineStr"/>
+      <c r="K237" s="3" t="inlineStr"/>
+      <c r="L237" t="inlineStr">
         <is>
           <t>Total Soil Moisture on Land-Use Tile</t>
         </is>
       </c>
-      <c r="M237" s="4" t="inlineStr">
+      <c r="M237" t="inlineStr">
         <is>
           <t>mass_content_of_water_in_soil</t>
         </is>
       </c>
-      <c r="N237" s="4" t="inlineStr">
+      <c r="N237" t="inlineStr">
         <is>
           <t>SMOIS</t>
         </is>
       </c>
-      <c r="O237" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; no land-use tiles in WRF: grid-cell value only</t>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_sfc_mrso (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
         </is>
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="4" t="inlineStr">
+      <c r="A238" t="inlineStr">
         <is>
           <t>mrsosLut</t>
         </is>
       </c>
-      <c r="B238" s="4" t="inlineStr">
+      <c r="B238" t="inlineStr">
         <is>
           <t>FPS-LUCAS</t>
         </is>
       </c>
-      <c r="C238" s="4" t="inlineStr">
+      <c r="C238" t="inlineStr">
         <is>
           <t>TIER 1</t>
         </is>
       </c>
-      <c r="D238" s="4" t="inlineStr">
+      <c r="D238" t="inlineStr">
         <is>
           <t>kg m-2</t>
         </is>
       </c>
-      <c r="E238" s="5" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F238" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G238" s="5" t="inlineStr"/>
-      <c r="H238" s="5" t="inlineStr"/>
-      <c r="I238" s="5" t="inlineStr"/>
-      <c r="J238" s="5" t="inlineStr"/>
-      <c r="K238" s="5" t="inlineStr"/>
-      <c r="L238" s="4" t="inlineStr">
+      <c r="E238" s="3" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F238" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G238" s="3" t="inlineStr"/>
+      <c r="H238" s="3" t="inlineStr"/>
+      <c r="I238" s="3" t="inlineStr"/>
+      <c r="J238" s="3" t="inlineStr"/>
+      <c r="K238" s="3" t="inlineStr"/>
+      <c r="L238" t="inlineStr">
         <is>
           <t>the mass of water in all phases in a thin surface layer; integrate over uppermost 10cm</t>
         </is>
       </c>
-      <c r="M238" s="4" t="inlineStr">
+      <c r="M238" t="inlineStr">
         <is>
           <t>mass_content_of_water_in_soil_layer</t>
         </is>
       </c>
-      <c r="N238" s="4" t="inlineStr">
+      <c r="N238" t="inlineStr">
         <is>
           <t>SMOIS</t>
         </is>
       </c>
-      <c r="O238" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; no land-use tiles in WRF: grid-cell value only</t>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_sfc_mrsos (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="4" t="inlineStr">
+      <c r="A239" t="inlineStr">
         <is>
           <t>npp</t>
         </is>
       </c>
-      <c r="B239" s="4" t="inlineStr">
+      <c r="B239" t="inlineStr">
         <is>
           <t>FPS-LUCAS</t>
         </is>
       </c>
-      <c r="C239" s="4" t="inlineStr">
+      <c r="C239" t="inlineStr">
         <is>
           <t>TIER 1</t>
         </is>
       </c>
-      <c r="D239" s="4" t="inlineStr">
+      <c r="D239" t="inlineStr">
         <is>
           <t>kg m-2 s-1</t>
         </is>
       </c>
-      <c r="E239" s="5" t="inlineStr">
+      <c r="E239" s="3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="F239" s="5" t="inlineStr"/>
-      <c r="G239" s="5" t="inlineStr"/>
-      <c r="H239" s="5" t="inlineStr"/>
-      <c r="I239" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J239" s="5" t="inlineStr"/>
-      <c r="K239" s="5" t="inlineStr"/>
-      <c r="L239" s="4" t="inlineStr">
+      <c r="F239" s="3" t="inlineStr"/>
+      <c r="G239" s="3" t="inlineStr"/>
+      <c r="H239" s="3" t="inlineStr"/>
+      <c r="I239" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J239" s="3" t="inlineStr"/>
+      <c r="K239" s="3" t="inlineStr"/>
+      <c r="L239" t="inlineStr">
         <is>
           <t>Net Primary Production on Land as Carbon Mass Flux</t>
         </is>
       </c>
-      <c r="M239" s="4" t="inlineStr">
+      <c r="M239" t="inlineStr">
         <is>
           <t>net_primary_productivity_of_biomass_expressed_as_carbon</t>
         </is>
       </c>
-      <c r="N239" s="4" t="inlineStr">
+      <c r="N239" t="inlineStr">
         <is>
           <t>NPP</t>
         </is>
       </c>
-      <c r="O239" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; Noah-MP with dynamic vegetation (opt_dveg)</t>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_sfc_npp (lsm varset); meaningful with Noah-MP dynamic vegetation (opt_dveg) only</t>
         </is>
       </c>
     </row>
@@ -16222,230 +16222,230 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="4" t="inlineStr">
+      <c r="A241" t="inlineStr">
         <is>
           <t>residualFrac</t>
         </is>
       </c>
-      <c r="B241" s="4" t="inlineStr">
+      <c r="B241" t="inlineStr">
         <is>
           <t>FPS-LUCAS</t>
         </is>
       </c>
-      <c r="C241" s="4" t="inlineStr">
+      <c r="C241" t="inlineStr">
         <is>
           <t>TIER 1</t>
         </is>
       </c>
-      <c r="D241" s="4" t="inlineStr">
+      <c r="D241" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E241" s="5" t="inlineStr"/>
-      <c r="F241" s="5" t="inlineStr"/>
-      <c r="G241" s="5" t="inlineStr"/>
-      <c r="H241" s="5" t="inlineStr"/>
-      <c r="I241" s="5" t="inlineStr">
+      <c r="E241" s="3" t="inlineStr"/>
+      <c r="F241" s="3" t="inlineStr"/>
+      <c r="G241" s="3" t="inlineStr"/>
+      <c r="H241" s="3" t="inlineStr"/>
+      <c r="I241" s="3" t="inlineStr">
         <is>
           <t>x¹</t>
         </is>
       </c>
-      <c r="J241" s="5" t="inlineStr"/>
-      <c r="K241" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="L241" s="4" t="inlineStr">
+      <c r="J241" s="3" t="inlineStr"/>
+      <c r="K241" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
         <is>
           <t>Percentage of Grid Cell That Is Land but neither Vegetation Covered nor Bare Soil</t>
         </is>
       </c>
-      <c r="M241" s="4" t="inlineStr">
+      <c r="M241" t="inlineStr">
         <is>
           <t>area_fraction</t>
         </is>
       </c>
-      <c r="N241" s="4" t="inlineStr">
+      <c r="N241" t="inlineStr">
         <is>
           <t>LANDUSEF</t>
         </is>
       </c>
-      <c r="O241" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; urban + land ice classes; LUCAS name resdiualFrac</t>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_fx_landuse (fx varset) and RCM_sfc_landuse (landuse varset); LUCAS name resdiualFrac</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="4" t="inlineStr">
+      <c r="A242" t="inlineStr">
         <is>
           <t>rlusLut</t>
         </is>
       </c>
-      <c r="B242" s="4" t="inlineStr">
+      <c r="B242" t="inlineStr">
         <is>
           <t>FPS-LUCAS</t>
         </is>
       </c>
-      <c r="C242" s="4" t="inlineStr">
+      <c r="C242" t="inlineStr">
         <is>
           <t>TIER 1</t>
         </is>
       </c>
-      <c r="D242" s="4" t="inlineStr">
+      <c r="D242" t="inlineStr">
         <is>
           <t>W m-2</t>
         </is>
       </c>
-      <c r="E242" s="5" t="inlineStr">
+      <c r="E242" s="3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="F242" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G242" s="5" t="inlineStr"/>
-      <c r="H242" s="5" t="inlineStr"/>
-      <c r="I242" s="5" t="inlineStr"/>
-      <c r="J242" s="5" t="inlineStr"/>
-      <c r="K242" s="5" t="inlineStr"/>
-      <c r="L242" s="4" t="inlineStr">
+      <c r="F242" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G242" s="3" t="inlineStr"/>
+      <c r="H242" s="3" t="inlineStr"/>
+      <c r="I242" s="3" t="inlineStr"/>
+      <c r="J242" s="3" t="inlineStr"/>
+      <c r="K242" s="3" t="inlineStr"/>
+      <c r="L242" t="inlineStr">
         <is>
           <t>Surface Upwelling Longwave on Land-Use Tile</t>
         </is>
       </c>
-      <c r="M242" s="4" t="inlineStr">
+      <c r="M242" t="inlineStr">
         <is>
           <t>surface_upwelling_longwave_flux_in_air</t>
         </is>
       </c>
-      <c r="N242" s="4" t="inlineStr">
+      <c r="N242" t="inlineStr">
         <is>
           <t>ACLWUPB I_ACLWUPB</t>
         </is>
       </c>
-      <c r="O242" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; no land-use tiles in WRF: grid-cell value only</t>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_sfc_rad (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="4" t="inlineStr">
+      <c r="A243" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="B243" s="4" t="inlineStr">
+      <c r="B243" t="inlineStr">
         <is>
           <t>FPS-LUCAS</t>
         </is>
       </c>
-      <c r="C243" s="4" t="inlineStr">
+      <c r="C243" t="inlineStr">
         <is>
           <t>TIER 1</t>
         </is>
       </c>
-      <c r="D243" s="4" t="inlineStr">
+      <c r="D243" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="E243" s="5" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F243" s="5" t="inlineStr"/>
-      <c r="G243" s="5" t="inlineStr"/>
-      <c r="H243" s="5" t="inlineStr"/>
-      <c r="I243" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J243" s="5" t="inlineStr"/>
-      <c r="K243" s="5" t="inlineStr"/>
-      <c r="L243" s="4" t="inlineStr">
+      <c r="E243" s="3" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F243" s="3" t="inlineStr"/>
+      <c r="G243" s="3" t="inlineStr"/>
+      <c r="H243" s="3" t="inlineStr"/>
+      <c r="I243" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J243" s="3" t="inlineStr"/>
+      <c r="K243" s="3" t="inlineStr"/>
+      <c r="L243" t="inlineStr">
         <is>
           <t>Roughness Length</t>
         </is>
       </c>
-      <c r="M243" s="4" t="inlineStr">
+      <c r="M243" t="inlineStr">
         <is>
           <t>roughness_length</t>
         </is>
       </c>
-      <c r="N243" s="4" t="inlineStr">
+      <c r="N243" t="inlineStr">
         <is>
           <t>ZNT</t>
         </is>
       </c>
-      <c r="O243" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready</t>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_sfc_rough (lsm varset)</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="4" t="inlineStr">
+      <c r="A244" t="inlineStr">
         <is>
           <t>rsusLut</t>
         </is>
       </c>
-      <c r="B244" s="4" t="inlineStr">
+      <c r="B244" t="inlineStr">
         <is>
           <t>FPS-LUCAS</t>
         </is>
       </c>
-      <c r="C244" s="4" t="inlineStr">
+      <c r="C244" t="inlineStr">
         <is>
           <t>TIER 1</t>
         </is>
       </c>
-      <c r="D244" s="4" t="inlineStr">
+      <c r="D244" t="inlineStr">
         <is>
           <t>W m-2</t>
         </is>
       </c>
-      <c r="E244" s="5" t="inlineStr">
+      <c r="E244" s="3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="F244" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G244" s="5" t="inlineStr"/>
-      <c r="H244" s="5" t="inlineStr"/>
-      <c r="I244" s="5" t="inlineStr"/>
-      <c r="J244" s="5" t="inlineStr"/>
-      <c r="K244" s="5" t="inlineStr"/>
-      <c r="L244" s="4" t="inlineStr">
+      <c r="F244" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G244" s="3" t="inlineStr"/>
+      <c r="H244" s="3" t="inlineStr"/>
+      <c r="I244" s="3" t="inlineStr"/>
+      <c r="J244" s="3" t="inlineStr"/>
+      <c r="K244" s="3" t="inlineStr"/>
+      <c r="L244" t="inlineStr">
         <is>
           <t>Surface Upwelling Shortwave on Land-Use Tile</t>
         </is>
       </c>
-      <c r="M244" s="4" t="inlineStr">
+      <c r="M244" t="inlineStr">
         <is>
           <t>surface_upwelling_shortwave_flux_in_air</t>
         </is>
       </c>
-      <c r="N244" s="4" t="inlineStr">
+      <c r="N244" t="inlineStr">
         <is>
           <t>ACSWUPB I_ACSWUPB</t>
         </is>
       </c>
-      <c r="O244" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; no land-use tiles in WRF: grid-cell value only</t>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_sfc_rad (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
         </is>
       </c>
     </row>
@@ -16507,230 +16507,230 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="4" t="inlineStr">
+      <c r="A246" t="inlineStr">
         <is>
           <t>sweLut</t>
         </is>
       </c>
-      <c r="B246" s="4" t="inlineStr">
+      <c r="B246" t="inlineStr">
         <is>
           <t>FPS-LUCAS</t>
         </is>
       </c>
-      <c r="C246" s="4" t="inlineStr">
+      <c r="C246" t="inlineStr">
         <is>
           <t>TIER 1</t>
         </is>
       </c>
-      <c r="D246" s="4" t="inlineStr">
+      <c r="D246" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="E246" s="5" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F246" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G246" s="5" t="inlineStr"/>
-      <c r="H246" s="5" t="inlineStr"/>
-      <c r="I246" s="5" t="inlineStr"/>
-      <c r="J246" s="5" t="inlineStr"/>
-      <c r="K246" s="5" t="inlineStr"/>
-      <c r="L246" s="4" t="inlineStr">
+      <c r="E246" s="3" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F246" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G246" s="3" t="inlineStr"/>
+      <c r="H246" s="3" t="inlineStr"/>
+      <c r="I246" s="3" t="inlineStr"/>
+      <c r="J246" s="3" t="inlineStr"/>
+      <c r="K246" s="3" t="inlineStr"/>
+      <c r="L246" t="inlineStr">
         <is>
           <t>Snow Water Equivalent on Land-Use Tile</t>
         </is>
       </c>
-      <c r="M246" s="4" t="inlineStr">
+      <c r="M246" t="inlineStr">
         <is>
           <t>lwe_thickness_of_surface_snow_amount</t>
         </is>
       </c>
-      <c r="N246" s="4" t="inlineStr">
+      <c r="N246" t="inlineStr">
         <is>
           <t>SNOW</t>
         </is>
       </c>
-      <c r="O246" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; SNOW/1000; no land-use tiles in WRF</t>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_sfc_snw (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
         </is>
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="4" t="inlineStr">
+      <c r="A247" t="inlineStr">
         <is>
           <t>tasLut</t>
         </is>
       </c>
-      <c r="B247" s="4" t="inlineStr">
+      <c r="B247" t="inlineStr">
         <is>
           <t>FPS-LUCAS</t>
         </is>
       </c>
-      <c r="C247" s="4" t="inlineStr">
+      <c r="C247" t="inlineStr">
         <is>
           <t>TIER 1</t>
         </is>
       </c>
-      <c r="D247" s="4" t="inlineStr">
+      <c r="D247" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="E247" s="5" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F247" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G247" s="5" t="inlineStr"/>
-      <c r="H247" s="5" t="inlineStr"/>
-      <c r="I247" s="5" t="inlineStr"/>
-      <c r="J247" s="5" t="inlineStr"/>
-      <c r="K247" s="5" t="inlineStr"/>
-      <c r="L247" s="4" t="inlineStr">
+      <c r="E247" s="3" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F247" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G247" s="3" t="inlineStr"/>
+      <c r="H247" s="3" t="inlineStr"/>
+      <c r="I247" s="3" t="inlineStr"/>
+      <c r="J247" s="3" t="inlineStr"/>
+      <c r="K247" s="3" t="inlineStr"/>
+      <c r="L247" t="inlineStr">
         <is>
           <t>Air temperature is the bulk temperature of the air, not the surface (skin) temperature.</t>
         </is>
       </c>
-      <c r="M247" s="4" t="inlineStr">
+      <c r="M247" t="inlineStr">
         <is>
           <t>air_temperature</t>
         </is>
       </c>
-      <c r="N247" s="4" t="inlineStr">
+      <c r="N247" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="O247" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; no land-use tiles in WRF (Noah-MP T2MV/T2MB: vegetated/bare parts)</t>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_sfc_tas (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
         </is>
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="4" t="inlineStr">
+      <c r="A248" t="inlineStr">
         <is>
           <t>tcs</t>
         </is>
       </c>
-      <c r="B248" s="4" t="inlineStr">
+      <c r="B248" t="inlineStr">
         <is>
           <t>FPS-LUCAS</t>
         </is>
       </c>
-      <c r="C248" s="4" t="inlineStr">
+      <c r="C248" t="inlineStr">
         <is>
           <t>TIER 1</t>
         </is>
       </c>
-      <c r="D248" s="4" t="inlineStr">
+      <c r="D248" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="E248" s="5" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F248" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G248" s="5" t="inlineStr"/>
-      <c r="H248" s="5" t="inlineStr"/>
-      <c r="I248" s="5" t="inlineStr"/>
-      <c r="J248" s="5" t="inlineStr"/>
-      <c r="K248" s="5" t="inlineStr"/>
-      <c r="L248" s="4" t="inlineStr">
+      <c r="E248" s="3" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F248" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G248" s="3" t="inlineStr"/>
+      <c r="H248" s="3" t="inlineStr"/>
+      <c r="I248" s="3" t="inlineStr"/>
+      <c r="J248" s="3" t="inlineStr"/>
+      <c r="K248" s="3" t="inlineStr"/>
+      <c r="L248" t="inlineStr">
         <is>
           <t>Vegetation temperature, averaged over all vegetation types</t>
         </is>
       </c>
-      <c r="M248" s="4" t="inlineStr">
+      <c r="M248" t="inlineStr">
         <is>
           <t>canopy_temperature</t>
         </is>
       </c>
-      <c r="N248" s="4" t="inlineStr">
+      <c r="N248" t="inlineStr">
         <is>
           <t>TV</t>
         </is>
       </c>
-      <c r="O248" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; Noah-MP vegetation temperature</t>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_sfc_tcs (lsm varset)</t>
         </is>
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="4" t="inlineStr">
+      <c r="A249" t="inlineStr">
         <is>
           <t>tgs</t>
         </is>
       </c>
-      <c r="B249" s="4" t="inlineStr">
+      <c r="B249" t="inlineStr">
         <is>
           <t>FPS-LUCAS</t>
         </is>
       </c>
-      <c r="C249" s="4" t="inlineStr">
+      <c r="C249" t="inlineStr">
         <is>
           <t>TIER 1</t>
         </is>
       </c>
-      <c r="D249" s="4" t="inlineStr">
+      <c r="D249" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="E249" s="5" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F249" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G249" s="5" t="inlineStr"/>
-      <c r="H249" s="5" t="inlineStr"/>
-      <c r="I249" s="5" t="inlineStr"/>
-      <c r="J249" s="5" t="inlineStr"/>
-      <c r="K249" s="5" t="inlineStr"/>
-      <c r="L249" s="4" t="inlineStr">
+      <c r="E249" s="3" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F249" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G249" s="3" t="inlineStr"/>
+      <c r="H249" s="3" t="inlineStr"/>
+      <c r="I249" s="3" t="inlineStr"/>
+      <c r="J249" s="3" t="inlineStr"/>
+      <c r="K249" s="3" t="inlineStr"/>
+      <c r="L249" t="inlineStr">
         <is>
           <t>Surface bare soil temperature</t>
         </is>
       </c>
-      <c r="M249" s="4" t="inlineStr">
+      <c r="M249" t="inlineStr">
         <is>
           <t>surface_temperature</t>
         </is>
       </c>
-      <c r="N249" s="4" t="inlineStr">
+      <c r="N249" t="inlineStr">
         <is>
           <t>TGB</t>
         </is>
       </c>
-      <c r="O249" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; Noah-MP bare ground temperature</t>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_sfc_tgs (lsm varset)</t>
         </is>
       </c>
     </row>
@@ -16849,230 +16849,230 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="4" t="inlineStr">
+      <c r="A252" t="inlineStr">
         <is>
           <t>treeFracBdlDcd</t>
         </is>
       </c>
-      <c r="B252" s="4" t="inlineStr">
+      <c r="B252" t="inlineStr">
         <is>
           <t>FPS-LUCAS</t>
         </is>
       </c>
-      <c r="C252" s="4" t="inlineStr">
+      <c r="C252" t="inlineStr">
         <is>
           <t>TIER 1</t>
         </is>
       </c>
-      <c r="D252" s="4" t="inlineStr">
+      <c r="D252" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E252" s="5" t="inlineStr"/>
-      <c r="F252" s="5" t="inlineStr"/>
-      <c r="G252" s="5" t="inlineStr"/>
-      <c r="H252" s="5" t="inlineStr"/>
-      <c r="I252" s="5" t="inlineStr">
+      <c r="E252" s="3" t="inlineStr"/>
+      <c r="F252" s="3" t="inlineStr"/>
+      <c r="G252" s="3" t="inlineStr"/>
+      <c r="H252" s="3" t="inlineStr"/>
+      <c r="I252" s="3" t="inlineStr">
         <is>
           <t>x¹</t>
         </is>
       </c>
-      <c r="J252" s="5" t="inlineStr"/>
-      <c r="K252" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="L252" s="4" t="inlineStr">
+      <c r="J252" s="3" t="inlineStr"/>
+      <c r="K252" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
         <is>
           <t>This is the percentage of the entire grid cell that is covered by broadleaf deciduous trees.</t>
         </is>
       </c>
-      <c r="M252" s="4" t="inlineStr">
+      <c r="M252" t="inlineStr">
         <is>
           <t>area_fraction</t>
         </is>
       </c>
-      <c r="N252" s="4" t="inlineStr">
+      <c r="N252" t="inlineStr">
         <is>
           <t>LANDUSEF</t>
         </is>
       </c>
-      <c r="O252" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; MODIS class 4 (deciduous broadleaf forest)</t>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_fx_landuse (fx varset) and RCM_sfc_landuse (landuse varset)</t>
         </is>
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="4" t="inlineStr">
+      <c r="A253" t="inlineStr">
         <is>
           <t>treeFracBdlEvg</t>
         </is>
       </c>
-      <c r="B253" s="4" t="inlineStr">
+      <c r="B253" t="inlineStr">
         <is>
           <t>FPS-LUCAS</t>
         </is>
       </c>
-      <c r="C253" s="4" t="inlineStr">
+      <c r="C253" t="inlineStr">
         <is>
           <t>TIER 1</t>
         </is>
       </c>
-      <c r="D253" s="4" t="inlineStr">
+      <c r="D253" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E253" s="5" t="inlineStr"/>
-      <c r="F253" s="5" t="inlineStr"/>
-      <c r="G253" s="5" t="inlineStr"/>
-      <c r="H253" s="5" t="inlineStr"/>
-      <c r="I253" s="5" t="inlineStr">
+      <c r="E253" s="3" t="inlineStr"/>
+      <c r="F253" s="3" t="inlineStr"/>
+      <c r="G253" s="3" t="inlineStr"/>
+      <c r="H253" s="3" t="inlineStr"/>
+      <c r="I253" s="3" t="inlineStr">
         <is>
           <t>x¹</t>
         </is>
       </c>
-      <c r="J253" s="5" t="inlineStr"/>
-      <c r="K253" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="L253" s="4" t="inlineStr">
+      <c r="J253" s="3" t="inlineStr"/>
+      <c r="K253" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
         <is>
           <t>This is the percentage of the entire grid cell that is covered by broadleaf evergreen trees.</t>
         </is>
       </c>
-      <c r="M253" s="4" t="inlineStr">
+      <c r="M253" t="inlineStr">
         <is>
           <t>area_fraction</t>
         </is>
       </c>
-      <c r="N253" s="4" t="inlineStr">
+      <c r="N253" t="inlineStr">
         <is>
           <t>LANDUSEF</t>
         </is>
       </c>
-      <c r="O253" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; MODIS class 2 (evergreen broadleaf forest)</t>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_fx_landuse (fx varset) and RCM_sfc_landuse (landuse varset)</t>
         </is>
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="4" t="inlineStr">
+      <c r="A254" t="inlineStr">
         <is>
           <t>treeFracNdlDcd</t>
         </is>
       </c>
-      <c r="B254" s="4" t="inlineStr">
+      <c r="B254" t="inlineStr">
         <is>
           <t>FPS-LUCAS</t>
         </is>
       </c>
-      <c r="C254" s="4" t="inlineStr">
+      <c r="C254" t="inlineStr">
         <is>
           <t>TIER 1</t>
         </is>
       </c>
-      <c r="D254" s="4" t="inlineStr">
+      <c r="D254" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E254" s="5" t="inlineStr"/>
-      <c r="F254" s="5" t="inlineStr"/>
-      <c r="G254" s="5" t="inlineStr"/>
-      <c r="H254" s="5" t="inlineStr"/>
-      <c r="I254" s="5" t="inlineStr">
+      <c r="E254" s="3" t="inlineStr"/>
+      <c r="F254" s="3" t="inlineStr"/>
+      <c r="G254" s="3" t="inlineStr"/>
+      <c r="H254" s="3" t="inlineStr"/>
+      <c r="I254" s="3" t="inlineStr">
         <is>
           <t>x¹</t>
         </is>
       </c>
-      <c r="J254" s="5" t="inlineStr"/>
-      <c r="K254" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="L254" s="4" t="inlineStr">
+      <c r="J254" s="3" t="inlineStr"/>
+      <c r="K254" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
         <is>
           <t>This is the percentage of the entire grid cell that is covered by needleleaf deciduous trees.</t>
         </is>
       </c>
-      <c r="M254" s="4" t="inlineStr">
+      <c r="M254" t="inlineStr">
         <is>
           <t>area_fraction</t>
         </is>
       </c>
-      <c r="N254" s="4" t="inlineStr">
+      <c r="N254" t="inlineStr">
         <is>
           <t>LANDUSEF</t>
         </is>
       </c>
-      <c r="O254" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; MODIS class 3 (deciduous needleleaf forest)</t>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_fx_landuse (fx varset) and RCM_sfc_landuse (landuse varset)</t>
         </is>
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="4" t="inlineStr">
+      <c r="A255" t="inlineStr">
         <is>
           <t>tslsiLut</t>
         </is>
       </c>
-      <c r="B255" s="4" t="inlineStr">
+      <c r="B255" t="inlineStr">
         <is>
           <t>FPS-LUCAS</t>
         </is>
       </c>
-      <c r="C255" s="4" t="inlineStr">
+      <c r="C255" t="inlineStr">
         <is>
           <t>TIER 1</t>
         </is>
       </c>
-      <c r="D255" s="4" t="inlineStr">
+      <c r="D255" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="E255" s="5" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F255" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G255" s="5" t="inlineStr"/>
-      <c r="H255" s="5" t="inlineStr"/>
-      <c r="I255" s="5" t="inlineStr"/>
-      <c r="J255" s="5" t="inlineStr"/>
-      <c r="K255" s="5" t="inlineStr"/>
-      <c r="L255" s="4" t="inlineStr">
+      <c r="E255" s="3" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F255" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G255" s="3" t="inlineStr"/>
+      <c r="H255" s="3" t="inlineStr"/>
+      <c r="I255" s="3" t="inlineStr"/>
+      <c r="J255" s="3" t="inlineStr"/>
+      <c r="K255" s="3" t="inlineStr"/>
+      <c r="L255" t="inlineStr">
         <is>
           <t>Surface temperature (i.e. temperature at which long-wave radiation emitted)</t>
         </is>
       </c>
-      <c r="M255" s="4" t="inlineStr">
+      <c r="M255" t="inlineStr">
         <is>
           <t>surface_temperature</t>
         </is>
       </c>
-      <c r="N255" s="4" t="inlineStr">
+      <c r="N255" t="inlineStr">
         <is>
           <t>TSK</t>
         </is>
       </c>
-      <c r="O255" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; no land-use tiles in WRF: grid-cell value only</t>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_sfc_ts (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
         </is>
       </c>
     </row>
@@ -17248,59 +17248,59 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="4" t="inlineStr">
+      <c r="A259" t="inlineStr">
         <is>
           <t>slthick</t>
         </is>
       </c>
-      <c r="B259" s="4" t="inlineStr">
+      <c r="B259" t="inlineStr">
         <is>
           <t>FPS-LUCAS</t>
         </is>
       </c>
-      <c r="C259" s="4" t="inlineStr">
+      <c r="C259" t="inlineStr">
         <is>
           <t>TIER 1</t>
         </is>
       </c>
-      <c r="D259" s="4" t="inlineStr">
+      <c r="D259" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="E259" s="5" t="inlineStr"/>
-      <c r="F259" s="5" t="inlineStr"/>
-      <c r="G259" s="5" t="inlineStr"/>
-      <c r="H259" s="5" t="inlineStr"/>
-      <c r="I259" s="5" t="inlineStr">
+      <c r="E259" s="3" t="inlineStr"/>
+      <c r="F259" s="3" t="inlineStr"/>
+      <c r="G259" s="3" t="inlineStr"/>
+      <c r="H259" s="3" t="inlineStr"/>
+      <c r="I259" s="3" t="inlineStr">
         <is>
           <t>x¹</t>
         </is>
       </c>
-      <c r="J259" s="5" t="inlineStr"/>
-      <c r="K259" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="L259" s="4" t="inlineStr">
+      <c r="J259" s="3" t="inlineStr"/>
+      <c r="K259" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
         <is>
           <t>Thickness of Soil Layers</t>
         </is>
       </c>
-      <c r="M259" s="4" t="inlineStr">
+      <c r="M259" t="inlineStr">
         <is>
           <t>cell_thickness</t>
         </is>
       </c>
-      <c r="N259" s="4" t="inlineStr">
+      <c r="N259" t="inlineStr">
         <is>
           <t>DZS</t>
         </is>
       </c>
-      <c r="O259" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; Noah-MP soil layer thickness</t>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_fx_slthick (fx varset)</t>
         </is>
       </c>
     </row>

--- a/CORDEX_Cmor_variables.xlsx
+++ b/CORDEX_Cmor_variables.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variables" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'variables'!$A$1:$O$260</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'variables'!$A$1:$O$259</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O262"/>
+  <dimension ref="A1:O261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -14911,66 +14911,66 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="4" t="inlineStr">
-        <is>
-          <t>hu</t>
-        </is>
-      </c>
-      <c r="B218" s="4" t="inlineStr">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>lai</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
         <is>
           <t>FPS-LUCAS</t>
         </is>
       </c>
-      <c r="C218" s="4" t="inlineStr">
+      <c r="C218" t="inlineStr">
         <is>
           <t>CORE</t>
         </is>
       </c>
-      <c r="D218" s="4" t="inlineStr">
-        <is>
-          <t>m3/m3</t>
-        </is>
-      </c>
-      <c r="E218" s="5" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F218" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G218" s="5" t="inlineStr"/>
-      <c r="H218" s="5" t="inlineStr"/>
-      <c r="I218" s="5" t="inlineStr"/>
-      <c r="J218" s="5" t="inlineStr"/>
-      <c r="K218" s="5" t="inlineStr"/>
-      <c r="L218" s="4" t="inlineStr">
-        <is>
-          <t>Atmospheric humidity at model levels</t>
-        </is>
-      </c>
-      <c r="M218" s="4" t="inlineStr">
-        <is>
-          <t>specific_humidity</t>
-        </is>
-      </c>
-      <c r="N218" s="4" t="inlineStr">
-        <is>
-          <t>QVAPOR</t>
-        </is>
-      </c>
-      <c r="O218" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; model levels</t>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E218" s="3" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F218" s="3" t="inlineStr"/>
+      <c r="G218" s="3" t="inlineStr"/>
+      <c r="H218" s="3" t="inlineStr"/>
+      <c r="I218" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J218" s="3" t="inlineStr"/>
+      <c r="K218" s="3" t="inlineStr"/>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>leaf area index</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>leaf_area_index</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>LAI</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_sfc_lai (lsm varset); LUCAS name LAI</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>lai</t>
+          <t>alb</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -14980,7 +14980,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>TIER 1</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -15005,143 +15005,143 @@
       <c r="K219" s="3" t="inlineStr"/>
       <c r="L219" t="inlineStr">
         <is>
-          <t>leaf area index</t>
+          <t>Albedo</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>leaf_area_index</t>
+          <t>surface_albedo</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>LAI</t>
+          <t>ALBEDO</t>
         </is>
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_lai (lsm varset); LUCAS name LAI</t>
+          <t>CORDEX_Cmor: RCM_sfc_alb (lsm varset)</t>
         </is>
       </c>
     </row>
     <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>alb</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
+      <c r="A220" s="4" t="inlineStr">
+        <is>
+          <t>albc</t>
+        </is>
+      </c>
+      <c r="B220" s="4" t="inlineStr">
         <is>
           <t>FPS-LUCAS</t>
         </is>
       </c>
-      <c r="C220" t="inlineStr">
+      <c r="C220" s="4" t="inlineStr">
         <is>
           <t>TIER 1</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr">
+      <c r="D220" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E220" s="3" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F220" s="3" t="inlineStr"/>
-      <c r="G220" s="3" t="inlineStr"/>
-      <c r="H220" s="3" t="inlineStr"/>
-      <c r="I220" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J220" s="3" t="inlineStr"/>
-      <c r="K220" s="3" t="inlineStr"/>
-      <c r="L220" t="inlineStr">
-        <is>
-          <t>Albedo</t>
-        </is>
-      </c>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>surface_albedo</t>
-        </is>
-      </c>
-      <c r="N220" t="inlineStr">
-        <is>
-          <t>ALBEDO</t>
-        </is>
-      </c>
-      <c r="O220" t="inlineStr">
-        <is>
-          <t>CORDEX_Cmor: RCM_sfc_alb (lsm varset)</t>
+      <c r="E220" s="5" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F220" s="5" t="inlineStr"/>
+      <c r="G220" s="5" t="inlineStr"/>
+      <c r="H220" s="5" t="inlineStr"/>
+      <c r="I220" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J220" s="5" t="inlineStr"/>
+      <c r="K220" s="5" t="inlineStr"/>
+      <c r="L220" s="4" t="inlineStr">
+        <is>
+          <t>Albedo of the vegetation: fraction of incoming solar radiation which is reflected before reaching the ground.</t>
+        </is>
+      </c>
+      <c r="M220" s="4" t="inlineStr">
+        <is>
+          <t>canopy_albedo</t>
+        </is>
+      </c>
+      <c r="N220" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O220" s="4" t="inlineStr">
+        <is>
+          <t>not produced by CORDEX_Cmor; header ready; no canopy albedo in the WRF output</t>
         </is>
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="4" t="inlineStr">
-        <is>
-          <t>albc</t>
-        </is>
-      </c>
-      <c r="B221" s="4" t="inlineStr">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>baresoilFrac</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
         <is>
           <t>FPS-LUCAS</t>
         </is>
       </c>
-      <c r="C221" s="4" t="inlineStr">
+      <c r="C221" t="inlineStr">
         <is>
           <t>TIER 1</t>
         </is>
       </c>
-      <c r="D221" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E221" s="5" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F221" s="5" t="inlineStr"/>
-      <c r="G221" s="5" t="inlineStr"/>
-      <c r="H221" s="5" t="inlineStr"/>
-      <c r="I221" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J221" s="5" t="inlineStr"/>
-      <c r="K221" s="5" t="inlineStr"/>
-      <c r="L221" s="4" t="inlineStr">
-        <is>
-          <t>Albedo of the vegetation: fraction of incoming solar radiation which is reflected before reaching the ground.</t>
-        </is>
-      </c>
-      <c r="M221" s="4" t="inlineStr">
-        <is>
-          <t>canopy_albedo</t>
-        </is>
-      </c>
-      <c r="N221" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O221" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; no canopy albedo in the WRF output</t>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E221" s="3" t="inlineStr"/>
+      <c r="F221" s="3" t="inlineStr"/>
+      <c r="G221" s="3" t="inlineStr"/>
+      <c r="H221" s="3" t="inlineStr"/>
+      <c r="I221" s="3" t="inlineStr">
+        <is>
+          <t>x¹</t>
+        </is>
+      </c>
+      <c r="J221" s="3" t="inlineStr"/>
+      <c r="K221" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>Bare Soil Percentage Area Coverage</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>area_fraction</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>LANDUSEF</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_fx_landuse (fx varset) and RCM_sfc_landuse (landuse varset); LANDUSEF classes grouped (landuse_field in shared_subs_v2.f90)</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>baresoilFrac</t>
+          <t>cnc</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -15176,7 +15176,7 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>Bare Soil Percentage Area Coverage</t>
+          <t>Percentage of area covered by vegetation.</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
@@ -15191,14 +15191,14 @@
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_fx_landuse (fx varset) and RCM_sfc_landuse (landuse varset); LANDUSEF classes grouped (landuse_field in shared_subs_v2.f90)</t>
+          <t>CORDEX_Cmor: RCM_fx_landuse (fx varset) and RCM_sfc_landuse (landuse varset); LANDUSEF tree+shrub+grass+crop (landuse_field in shared_subs_v2.f90)</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>cnc</t>
+          <t>cropFrac</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -15233,7 +15233,7 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>Percentage of area covered by vegetation.</t>
+          <t>Percentage Crop Cover</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
@@ -15248,14 +15248,14 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_fx_landuse (fx varset) and RCM_sfc_landuse (landuse varset); LANDUSEF tree+shrub+grass+crop (landuse_field in shared_subs_v2.f90)</t>
+          <t>CORDEX_Cmor: RCM_fx_landuse (fx varset) and RCM_sfc_landuse (landuse varset); LANDUSEF classes grouped (landuse_field in shared_subs_v2.f90)</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>cropFrac</t>
+          <t>cVeg</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -15270,49 +15270,49 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E224" s="3" t="inlineStr"/>
+          <t>kg m-2</t>
+        </is>
+      </c>
+      <c r="E224" s="3" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
       <c r="F224" s="3" t="inlineStr"/>
       <c r="G224" s="3" t="inlineStr"/>
       <c r="H224" s="3" t="inlineStr"/>
       <c r="I224" s="3" t="inlineStr">
         <is>
-          <t>x¹</t>
+          <t>x</t>
         </is>
       </c>
       <c r="J224" s="3" t="inlineStr"/>
-      <c r="K224" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="K224" s="3" t="inlineStr"/>
       <c r="L224" t="inlineStr">
         <is>
-          <t>Percentage Crop Cover</t>
+          <t>Carbon mass per unit area in vegetation.</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>area_fraction</t>
+          <t>vegetation_carbon_content</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>LANDUSEF</t>
+          <t>LFMASS RTMASS STMASS WOOD</t>
         </is>
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_fx_landuse (fx varset) and RCM_sfc_landuse (landuse varset); LANDUSEF classes grouped (landuse_field in shared_subs_v2.f90)</t>
+          <t>CORDEX_Cmor: RCM_sfc_cVeg (lsm varset); meaningful with Noah-MP dynamic vegetation (opt_dveg) only</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>cVeg</t>
+          <t>evspsblsoi</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -15327,49 +15327,49 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>kg m-2</t>
+          <t>kg m-2 s-1</t>
         </is>
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F225" s="3" t="inlineStr"/>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F225" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G225" s="3" t="inlineStr"/>
       <c r="H225" s="3" t="inlineStr"/>
-      <c r="I225" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="I225" s="3" t="inlineStr"/>
       <c r="J225" s="3" t="inlineStr"/>
       <c r="K225" s="3" t="inlineStr"/>
       <c r="L225" t="inlineStr">
         <is>
-          <t>Carbon mass per unit area in vegetation.</t>
+          <t>Water evaporation from soil (including sublimation).</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>vegetation_carbon_content</t>
+          <t>water_evaporation_flux_from_soil</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>LFMASS RTMASS STMASS WOOD</t>
+          <t>EDIR</t>
         </is>
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_cVeg (lsm varset); meaningful with Noah-MP dynamic vegetation (opt_dveg) only</t>
+          <t>CORDEX_Cmor: RCM_sfc_evspsblsoi (lsm varset)</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>evspsblsoi</t>
+          <t>evspsblveg</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -15404,29 +15404,29 @@
       <c r="K226" s="3" t="inlineStr"/>
       <c r="L226" t="inlineStr">
         <is>
-          <t>Water evaporation from soil (including sublimation).</t>
+          <t>The canopy evaporation and sublimation (if present in model); may include dew formation as a negative flux.</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>water_evaporation_flux_from_soil</t>
+          <t>water_evaporation_flux_from_canopy</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>EDIR</t>
+          <t>ECAN</t>
         </is>
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_evspsblsoi (lsm varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_evspsblveg (lsm varset)</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>evspsblveg</t>
+          <t>grassFrac</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -15441,49 +15441,49 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>kg m-2 s-1</t>
-        </is>
-      </c>
-      <c r="E227" s="3" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="F227" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E227" s="3" t="inlineStr"/>
+      <c r="F227" s="3" t="inlineStr"/>
       <c r="G227" s="3" t="inlineStr"/>
       <c r="H227" s="3" t="inlineStr"/>
-      <c r="I227" s="3" t="inlineStr"/>
+      <c r="I227" s="3" t="inlineStr">
+        <is>
+          <t>x¹</t>
+        </is>
+      </c>
       <c r="J227" s="3" t="inlineStr"/>
-      <c r="K227" s="3" t="inlineStr"/>
+      <c r="K227" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>The canopy evaporation and sublimation (if present in model); may include dew formation as a negative flux.</t>
+          <t>Natural Grass Area Percentage</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>water_evaporation_flux_from_canopy</t>
+          <t>area_fraction</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>ECAN</t>
+          <t>LANDUSEF</t>
         </is>
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_evspsblveg (lsm varset)</t>
+          <t>CORDEX_Cmor: RCM_fx_landuse (fx varset) and RCM_sfc_landuse (landuse varset); LANDUSEF classes grouped (landuse_field in shared_subs_v2.f90)</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>grassFrac</t>
+          <t>hflsLut</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -15498,49 +15498,49 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E228" s="3" t="inlineStr"/>
-      <c r="F228" s="3" t="inlineStr"/>
+          <t>W m-2</t>
+        </is>
+      </c>
+      <c r="E228" s="3" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F228" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G228" s="3" t="inlineStr"/>
       <c r="H228" s="3" t="inlineStr"/>
-      <c r="I228" s="3" t="inlineStr">
-        <is>
-          <t>x¹</t>
-        </is>
-      </c>
+      <c r="I228" s="3" t="inlineStr"/>
       <c r="J228" s="3" t="inlineStr"/>
-      <c r="K228" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="K228" s="3" t="inlineStr"/>
       <c r="L228" t="inlineStr">
         <is>
-          <t>Natural Grass Area Percentage</t>
+          <t>Latent Heat Flux on Land-Use Tile</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>area_fraction</t>
+          <t>surface_upward_latent_heat_flux</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>LANDUSEF</t>
+          <t>LH</t>
         </is>
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_fx_landuse (fx varset) and RCM_sfc_landuse (landuse varset); LANDUSEF classes grouped (landuse_field in shared_subs_v2.f90)</t>
+          <t>CORDEX_Cmor: RCM_sfc_hfls (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>hflsLut</t>
+          <t>hfssLut</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -15575,29 +15575,29 @@
       <c r="K229" s="3" t="inlineStr"/>
       <c r="L229" t="inlineStr">
         <is>
-          <t>Latent Heat Flux on Land-Use Tile</t>
+          <t>Sensible Heat Flux on Land-Use Tile</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>surface_upward_latent_heat_flux</t>
+          <t>surface_upward_sensible_heat_flux</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>LH</t>
+          <t>HFX</t>
         </is>
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_hfls (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
+          <t>CORDEX_Cmor: RCM_sfc_hfss (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>hfssLut</t>
+          <t>hussLut</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -15612,12 +15612,12 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>W m-2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>i</t>
         </is>
       </c>
       <c r="F230" s="3" t="inlineStr">
@@ -15632,29 +15632,29 @@
       <c r="K230" s="3" t="inlineStr"/>
       <c r="L230" t="inlineStr">
         <is>
-          <t>Sensible Heat Flux on Land-Use Tile</t>
+          <t>Normally, the specific humidity should be reported at the 2 meter height</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>surface_upward_sensible_heat_flux</t>
+          <t>specific_humidity</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>HFX</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_hfss (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
+          <t>CORDEX_Cmor: RCM_sfc_huss (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>hussLut</t>
+          <t>interception</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -15669,7 +15669,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>kg m-2</t>
         </is>
       </c>
       <c r="E231" s="3" t="inlineStr">
@@ -15689,29 +15689,29 @@
       <c r="K231" s="3" t="inlineStr"/>
       <c r="L231" t="inlineStr">
         <is>
-          <t>Normally, the specific humidity should be reported at the 2 meter height</t>
+          <t>water intercepted</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>specific_humidity</t>
+          <t>canopy_water_amount</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>CANLIQ CANICE</t>
         </is>
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_huss (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
+          <t>CORDEX_Cmor: RCM_sfc_interception (lsm varset)</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>interception</t>
+          <t>irrLut</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -15726,12 +15726,12 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>kg m-2</t>
+          <t>kg m-2 s-1</t>
         </is>
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F232" s="3" t="inlineStr">
@@ -15746,29 +15746,29 @@
       <c r="K232" s="3" t="inlineStr"/>
       <c r="L232" t="inlineStr">
         <is>
-          <t>water intercepted</t>
+          <t>surface_downward_mass_flux_of_water_due_to_irrigation</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>canopy_water_amount</t>
+          <t>surface_downward_mass_flux_of_water_due_to_irrigation</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>CANLIQ CANICE</t>
+          <t>IRSIVOL IRMIVOL IRFIVOL</t>
         </is>
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_interception (lsm varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_irrLut (irr varset); Noah-MP irrigation (opt_irr); add IRSIVOL IRMIVOL IRFIVOL to wrfout (iofields); no land-use tiles: grid-cell value</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>irrLut</t>
+          <t>laiLut</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -15783,49 +15783,49 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>kg m-2 s-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E233" s="3" t="inlineStr">
         <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="F233" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F233" s="3" t="inlineStr"/>
       <c r="G233" s="3" t="inlineStr"/>
       <c r="H233" s="3" t="inlineStr"/>
-      <c r="I233" s="3" t="inlineStr"/>
+      <c r="I233" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="J233" s="3" t="inlineStr"/>
       <c r="K233" s="3" t="inlineStr"/>
       <c r="L233" t="inlineStr">
         <is>
-          <t>surface_downward_mass_flux_of_water_due_to_irrigation</t>
+          <t>Leaf Area Index on Land-Use Tile</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>surface_downward_mass_flux_of_water_due_to_irrigation</t>
+          <t>leaf_area_index</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t>IRSIVOL IRMIVOL IRFIVOL</t>
+          <t>LAI</t>
         </is>
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_irrLut (irr varset); Noah-MP irrigation (opt_irr); add IRSIVOL IRMIVOL IRFIVOL to wrfout (iofields); no land-use tiles: grid-cell value</t>
+          <t>CORDEX_Cmor: RCM_sfc_lai (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>laiLut</t>
+          <t>landCoverFrac</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -15840,49 +15840,49 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E234" s="3" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E234" s="3" t="inlineStr"/>
       <c r="F234" s="3" t="inlineStr"/>
       <c r="G234" s="3" t="inlineStr"/>
       <c r="H234" s="3" t="inlineStr"/>
       <c r="I234" s="3" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>x¹</t>
         </is>
       </c>
       <c r="J234" s="3" t="inlineStr"/>
-      <c r="K234" s="3" t="inlineStr"/>
+      <c r="K234" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>Leaf Area Index on Land-Use Tile</t>
+          <t>Percentage of Area by Vegetation or Land-Cover Category</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>leaf_area_index</t>
+          <t>area_fraction</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>LAI</t>
+          <t>LANDUSEF</t>
         </is>
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_lai (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
+          <t>CORDEX_Cmor: RCM_fx_landCoverFrac (fx varset)</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>landCoverFrac</t>
+          <t>mrroLut</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -15897,49 +15897,49 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E235" s="3" t="inlineStr"/>
-      <c r="F235" s="3" t="inlineStr"/>
+          <t>kg m-2 s-1</t>
+        </is>
+      </c>
+      <c r="E235" s="3" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F235" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G235" s="3" t="inlineStr"/>
       <c r="H235" s="3" t="inlineStr"/>
-      <c r="I235" s="3" t="inlineStr">
-        <is>
-          <t>x¹</t>
-        </is>
-      </c>
+      <c r="I235" s="3" t="inlineStr"/>
       <c r="J235" s="3" t="inlineStr"/>
-      <c r="K235" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="K235" s="3" t="inlineStr"/>
       <c r="L235" t="inlineStr">
         <is>
-          <t>Percentage of Area by Vegetation or Land-Cover Category</t>
+          <t>Total Runoff on Land-Use Tile</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>area_fraction</t>
+          <t>runoff_flux</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>LANDUSEF</t>
+          <t>RUNSB RUNSF</t>
         </is>
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_fx_landCoverFrac (fx varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_mrro (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>mrroLut</t>
+          <t>mrsoLut</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -15954,12 +15954,12 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>kg m-2 s-1</t>
+          <t>kg m-2</t>
         </is>
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>i</t>
         </is>
       </c>
       <c r="F236" s="3" t="inlineStr">
@@ -15974,29 +15974,29 @@
       <c r="K236" s="3" t="inlineStr"/>
       <c r="L236" t="inlineStr">
         <is>
-          <t>Total Runoff on Land-Use Tile</t>
+          <t>Total Soil Moisture on Land-Use Tile</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>runoff_flux</t>
+          <t>mass_content_of_water_in_soil</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
         <is>
-          <t>RUNSB RUNSF</t>
+          <t>SMOIS</t>
         </is>
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_mrro (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
+          <t>CORDEX_Cmor: RCM_sfc_mrso (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>mrsoLut</t>
+          <t>mrsosLut</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -16031,12 +16031,12 @@
       <c r="K237" s="3" t="inlineStr"/>
       <c r="L237" t="inlineStr">
         <is>
-          <t>Total Soil Moisture on Land-Use Tile</t>
+          <t>the mass of water in all phases in a thin surface layer; integrate over uppermost 10cm</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>mass_content_of_water_in_soil</t>
+          <t>mass_content_of_water_in_soil_layer</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -16046,14 +16046,14 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_mrso (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
+          <t>CORDEX_Cmor: RCM_sfc_mrsos (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>mrsosLut</t>
+          <t>npp</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -16068,163 +16068,163 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>kg m-2</t>
+          <t>kg m-2 s-1</t>
         </is>
       </c>
       <c r="E238" s="3" t="inlineStr">
         <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F238" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F238" s="3" t="inlineStr"/>
       <c r="G238" s="3" t="inlineStr"/>
       <c r="H238" s="3" t="inlineStr"/>
-      <c r="I238" s="3" t="inlineStr"/>
+      <c r="I238" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="J238" s="3" t="inlineStr"/>
       <c r="K238" s="3" t="inlineStr"/>
       <c r="L238" t="inlineStr">
         <is>
-          <t>the mass of water in all phases in a thin surface layer; integrate over uppermost 10cm</t>
+          <t>Net Primary Production on Land as Carbon Mass Flux</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>mass_content_of_water_in_soil_layer</t>
+          <t>net_primary_productivity_of_biomass_expressed_as_carbon</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
         <is>
-          <t>SMOIS</t>
+          <t>NPP</t>
         </is>
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_mrsos (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
+          <t>CORDEX_Cmor: RCM_sfc_npp (lsm varset); meaningful with Noah-MP dynamic vegetation (opt_dveg) only</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>npp</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
+      <c r="A239" s="4" t="inlineStr">
+        <is>
+          <t>pastureFrac</t>
+        </is>
+      </c>
+      <c r="B239" s="4" t="inlineStr">
         <is>
           <t>FPS-LUCAS</t>
         </is>
       </c>
-      <c r="C239" t="inlineStr">
+      <c r="C239" s="4" t="inlineStr">
         <is>
           <t>TIER 1</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>kg m-2 s-1</t>
-        </is>
-      </c>
-      <c r="E239" s="3" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="F239" s="3" t="inlineStr"/>
-      <c r="G239" s="3" t="inlineStr"/>
-      <c r="H239" s="3" t="inlineStr"/>
-      <c r="I239" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J239" s="3" t="inlineStr"/>
-      <c r="K239" s="3" t="inlineStr"/>
-      <c r="L239" t="inlineStr">
-        <is>
-          <t>Net Primary Production on Land as Carbon Mass Flux</t>
-        </is>
-      </c>
-      <c r="M239" t="inlineStr">
-        <is>
-          <t>net_primary_productivity_of_biomass_expressed_as_carbon</t>
-        </is>
-      </c>
-      <c r="N239" t="inlineStr">
-        <is>
-          <t>NPP</t>
-        </is>
-      </c>
-      <c r="O239" t="inlineStr">
-        <is>
-          <t>CORDEX_Cmor: RCM_sfc_npp (lsm varset); meaningful with Noah-MP dynamic vegetation (opt_dveg) only</t>
+      <c r="D239" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E239" s="5" t="inlineStr"/>
+      <c r="F239" s="5" t="inlineStr"/>
+      <c r="G239" s="5" t="inlineStr"/>
+      <c r="H239" s="5" t="inlineStr"/>
+      <c r="I239" s="5" t="inlineStr">
+        <is>
+          <t>x¹</t>
+        </is>
+      </c>
+      <c r="J239" s="5" t="inlineStr"/>
+      <c r="K239" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L239" s="4" t="inlineStr">
+        <is>
+          <t>Percentage of Land Which Is Anthropogenic Pasture</t>
+        </is>
+      </c>
+      <c r="M239" s="4" t="inlineStr">
+        <is>
+          <t>area_fraction</t>
+        </is>
+      </c>
+      <c r="N239" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O239" s="4" t="inlineStr">
+        <is>
+          <t>not produced by CORDEX_Cmor; header ready; no pasture class in the WRF land-use tables</t>
         </is>
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="4" t="inlineStr">
-        <is>
-          <t>pastureFrac</t>
-        </is>
-      </c>
-      <c r="B240" s="4" t="inlineStr">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>residualFrac</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
         <is>
           <t>FPS-LUCAS</t>
         </is>
       </c>
-      <c r="C240" s="4" t="inlineStr">
+      <c r="C240" t="inlineStr">
         <is>
           <t>TIER 1</t>
         </is>
       </c>
-      <c r="D240" s="4" t="inlineStr">
+      <c r="D240" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E240" s="5" t="inlineStr"/>
-      <c r="F240" s="5" t="inlineStr"/>
-      <c r="G240" s="5" t="inlineStr"/>
-      <c r="H240" s="5" t="inlineStr"/>
-      <c r="I240" s="5" t="inlineStr">
+      <c r="E240" s="3" t="inlineStr"/>
+      <c r="F240" s="3" t="inlineStr"/>
+      <c r="G240" s="3" t="inlineStr"/>
+      <c r="H240" s="3" t="inlineStr"/>
+      <c r="I240" s="3" t="inlineStr">
         <is>
           <t>x¹</t>
         </is>
       </c>
-      <c r="J240" s="5" t="inlineStr"/>
-      <c r="K240" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="L240" s="4" t="inlineStr">
-        <is>
-          <t>Percentage of Land Which Is Anthropogenic Pasture</t>
-        </is>
-      </c>
-      <c r="M240" s="4" t="inlineStr">
+      <c r="J240" s="3" t="inlineStr"/>
+      <c r="K240" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>Percentage of Grid Cell That Is Land but neither Vegetation Covered nor Bare Soil</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
         <is>
           <t>area_fraction</t>
         </is>
       </c>
-      <c r="N240" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O240" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; no pasture class in the WRF land-use tables</t>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>LANDUSEF</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_fx_landuse (fx varset) and RCM_sfc_landuse (landuse varset); LUCAS name resdiualFrac</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>residualFrac</t>
+          <t>rlusLut</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -16239,49 +16239,49 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E241" s="3" t="inlineStr"/>
-      <c r="F241" s="3" t="inlineStr"/>
+          <t>W m-2</t>
+        </is>
+      </c>
+      <c r="E241" s="3" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F241" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G241" s="3" t="inlineStr"/>
       <c r="H241" s="3" t="inlineStr"/>
-      <c r="I241" s="3" t="inlineStr">
-        <is>
-          <t>x¹</t>
-        </is>
-      </c>
+      <c r="I241" s="3" t="inlineStr"/>
       <c r="J241" s="3" t="inlineStr"/>
-      <c r="K241" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="K241" s="3" t="inlineStr"/>
       <c r="L241" t="inlineStr">
         <is>
-          <t>Percentage of Grid Cell That Is Land but neither Vegetation Covered nor Bare Soil</t>
+          <t>Surface Upwelling Longwave on Land-Use Tile</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>area_fraction</t>
+          <t>surface_upwelling_longwave_flux_in_air</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
         <is>
-          <t>LANDUSEF</t>
+          <t>ACLWUPB I_ACLWUPB</t>
         </is>
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_fx_landuse (fx varset) and RCM_sfc_landuse (landuse varset); LUCAS name resdiualFrac</t>
+          <t>CORDEX_Cmor: RCM_sfc_rad (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>rlusLut</t>
+          <t>rough</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -16296,49 +16296,49 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>W m-2</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E242" s="3" t="inlineStr">
         <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="F242" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F242" s="3" t="inlineStr"/>
       <c r="G242" s="3" t="inlineStr"/>
       <c r="H242" s="3" t="inlineStr"/>
-      <c r="I242" s="3" t="inlineStr"/>
+      <c r="I242" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="J242" s="3" t="inlineStr"/>
       <c r="K242" s="3" t="inlineStr"/>
       <c r="L242" t="inlineStr">
         <is>
-          <t>Surface Upwelling Longwave on Land-Use Tile</t>
+          <t>Roughness Length</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>surface_upwelling_longwave_flux_in_air</t>
+          <t>roughness_length</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
         <is>
-          <t>ACLWUPB I_ACLWUPB</t>
+          <t>ZNT</t>
         </is>
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_rad (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
+          <t>CORDEX_Cmor: RCM_sfc_rough (lsm varset)</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>rough</t>
+          <t>rsusLut</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -16353,49 +16353,49 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>W m-2</t>
         </is>
       </c>
       <c r="E243" s="3" t="inlineStr">
         <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F243" s="3" t="inlineStr"/>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F243" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G243" s="3" t="inlineStr"/>
       <c r="H243" s="3" t="inlineStr"/>
-      <c r="I243" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="I243" s="3" t="inlineStr"/>
       <c r="J243" s="3" t="inlineStr"/>
       <c r="K243" s="3" t="inlineStr"/>
       <c r="L243" t="inlineStr">
         <is>
-          <t>Roughness Length</t>
+          <t>Surface Upwelling Shortwave on Land-Use Tile</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>roughness_length</t>
+          <t>surface_upwelling_shortwave_flux_in_air</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
         <is>
-          <t>ZNT</t>
+          <t>ACSWUPB I_ACSWUPB</t>
         </is>
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_rough (lsm varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_rad (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>rsusLut</t>
+          <t>shrubFrac</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -16410,49 +16410,49 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>W m-2</t>
-        </is>
-      </c>
-      <c r="E244" s="3" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="F244" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E244" s="3" t="inlineStr"/>
+      <c r="F244" s="3" t="inlineStr"/>
       <c r="G244" s="3" t="inlineStr"/>
       <c r="H244" s="3" t="inlineStr"/>
-      <c r="I244" s="3" t="inlineStr"/>
+      <c r="I244" s="3" t="inlineStr">
+        <is>
+          <t>x¹</t>
+        </is>
+      </c>
       <c r="J244" s="3" t="inlineStr"/>
-      <c r="K244" s="3" t="inlineStr"/>
+      <c r="K244" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>Surface Upwelling Shortwave on Land-Use Tile</t>
+          <t>Percentage Cover by Shrub</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>surface_upwelling_shortwave_flux_in_air</t>
+          <t>area_fraction</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
         <is>
-          <t>ACSWUPB I_ACSWUPB</t>
+          <t>LANDUSEF</t>
         </is>
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_rad (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
+          <t>CORDEX_Cmor: RCM_fx_landuse (fx varset) and RCM_sfc_landuse (landuse varset); LANDUSEF classes grouped (landuse_field in shared_subs_v2.f90)</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>shrubFrac</t>
+          <t>sweLut</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -16467,49 +16467,49 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E245" s="3" t="inlineStr"/>
-      <c r="F245" s="3" t="inlineStr"/>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E245" s="3" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F245" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G245" s="3" t="inlineStr"/>
       <c r="H245" s="3" t="inlineStr"/>
-      <c r="I245" s="3" t="inlineStr">
-        <is>
-          <t>x¹</t>
-        </is>
-      </c>
+      <c r="I245" s="3" t="inlineStr"/>
       <c r="J245" s="3" t="inlineStr"/>
-      <c r="K245" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="K245" s="3" t="inlineStr"/>
       <c r="L245" t="inlineStr">
         <is>
-          <t>Percentage Cover by Shrub</t>
+          <t>Snow Water Equivalent on Land-Use Tile</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>area_fraction</t>
+          <t>lwe_thickness_of_surface_snow_amount</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
         <is>
-          <t>LANDUSEF</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_fx_landuse (fx varset) and RCM_sfc_landuse (landuse varset); LANDUSEF classes grouped (landuse_field in shared_subs_v2.f90)</t>
+          <t>CORDEX_Cmor: RCM_sfc_snw (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>sweLut</t>
+          <t>tasLut</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -16524,7 +16524,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>K</t>
         </is>
       </c>
       <c r="E246" s="3" t="inlineStr">
@@ -16544,29 +16544,29 @@
       <c r="K246" s="3" t="inlineStr"/>
       <c r="L246" t="inlineStr">
         <is>
-          <t>Snow Water Equivalent on Land-Use Tile</t>
+          <t>Air temperature is the bulk temperature of the air, not the surface (skin) temperature.</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>lwe_thickness_of_surface_snow_amount</t>
+          <t>air_temperature</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_snw (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
+          <t>CORDEX_Cmor: RCM_sfc_tas (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>tasLut</t>
+          <t>tcs</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -16601,29 +16601,29 @@
       <c r="K247" s="3" t="inlineStr"/>
       <c r="L247" t="inlineStr">
         <is>
-          <t>Air temperature is the bulk temperature of the air, not the surface (skin) temperature.</t>
+          <t>Vegetation temperature, averaged over all vegetation types</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>air_temperature</t>
+          <t>canopy_temperature</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>TV</t>
         </is>
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_tas (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
+          <t>CORDEX_Cmor: RCM_sfc_tcs (lsm varset)</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>tcs</t>
+          <t>tgs</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -16658,29 +16658,29 @@
       <c r="K248" s="3" t="inlineStr"/>
       <c r="L248" t="inlineStr">
         <is>
-          <t>Vegetation temperature, averaged over all vegetation types</t>
+          <t>Surface bare soil temperature</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>canopy_temperature</t>
+          <t>surface_temperature</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
         <is>
-          <t>TV</t>
+          <t>TGB</t>
         </is>
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_tcs (lsm varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_tgs (lsm varset)</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>tgs</t>
+          <t>tran</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -16695,12 +16695,12 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>kg m-2 s-1</t>
         </is>
       </c>
       <c r="E249" s="3" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F249" s="3" t="inlineStr">
@@ -16715,29 +16715,29 @@
       <c r="K249" s="3" t="inlineStr"/>
       <c r="L249" t="inlineStr">
         <is>
-          <t>Surface bare soil temperature</t>
+          <t>Transpiration (may include dew formation as a negative flux).</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>surface_temperature</t>
+          <t>transpiration_flux</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
         <is>
-          <t>TGB</t>
+          <t>ETRAN</t>
         </is>
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_tgs (lsm varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_tran (lsm varset)</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>tran</t>
+          <t>treeFrac</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -16752,49 +16752,49 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>kg m-2 s-1</t>
-        </is>
-      </c>
-      <c r="E250" s="3" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="F250" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E250" s="3" t="inlineStr"/>
+      <c r="F250" s="3" t="inlineStr"/>
       <c r="G250" s="3" t="inlineStr"/>
       <c r="H250" s="3" t="inlineStr"/>
-      <c r="I250" s="3" t="inlineStr"/>
+      <c r="I250" s="3" t="inlineStr">
+        <is>
+          <t>x¹</t>
+        </is>
+      </c>
       <c r="J250" s="3" t="inlineStr"/>
-      <c r="K250" s="3" t="inlineStr"/>
+      <c r="K250" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>Transpiration (may include dew formation as a negative flux).</t>
+          <t>Tree Cover Percentage</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>transpiration_flux</t>
+          <t>area_fraction</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
         <is>
-          <t>ETRAN</t>
+          <t>LANDUSEF</t>
         </is>
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_tran (lsm varset)</t>
+          <t>CORDEX_Cmor: RCM_fx_landuse (fx varset) and RCM_sfc_landuse (landuse varset); LANDUSEF classes grouped (landuse_field in shared_subs_v2.f90)</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>treeFrac</t>
+          <t>treeFracBdlDcd</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -16829,7 +16829,7 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>Tree Cover Percentage</t>
+          <t>This is the percentage of the entire grid cell that is covered by broadleaf deciduous trees.</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
@@ -16844,14 +16844,14 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_fx_landuse (fx varset) and RCM_sfc_landuse (landuse varset); LANDUSEF classes grouped (landuse_field in shared_subs_v2.f90)</t>
+          <t>CORDEX_Cmor: RCM_fx_landuse (fx varset) and RCM_sfc_landuse (landuse varset)</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>treeFracBdlDcd</t>
+          <t>treeFracBdlEvg</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -16886,7 +16886,7 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>This is the percentage of the entire grid cell that is covered by broadleaf deciduous trees.</t>
+          <t>This is the percentage of the entire grid cell that is covered by broadleaf evergreen trees.</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
@@ -16908,7 +16908,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>treeFracBdlEvg</t>
+          <t>treeFracNdlDcd</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -16943,7 +16943,7 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>This is the percentage of the entire grid cell that is covered by broadleaf evergreen trees.</t>
+          <t>This is the percentage of the entire grid cell that is covered by needleleaf deciduous trees.</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
@@ -16965,7 +16965,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>treeFracNdlDcd</t>
+          <t>tslsiLut</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -16980,49 +16980,49 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E254" s="3" t="inlineStr"/>
-      <c r="F254" s="3" t="inlineStr"/>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="E254" s="3" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F254" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G254" s="3" t="inlineStr"/>
       <c r="H254" s="3" t="inlineStr"/>
-      <c r="I254" s="3" t="inlineStr">
-        <is>
-          <t>x¹</t>
-        </is>
-      </c>
+      <c r="I254" s="3" t="inlineStr"/>
       <c r="J254" s="3" t="inlineStr"/>
-      <c r="K254" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="K254" s="3" t="inlineStr"/>
       <c r="L254" t="inlineStr">
         <is>
-          <t>This is the percentage of the entire grid cell that is covered by needleleaf deciduous trees.</t>
+          <t>Surface temperature (i.e. temperature at which long-wave radiation emitted)</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>area_fraction</t>
+          <t>surface_temperature</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t>LANDUSEF</t>
+          <t>TSK</t>
         </is>
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_fx_landuse (fx varset) and RCM_sfc_landuse (landuse varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_ts (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>tslsiLut</t>
+          <t>urbanFrac</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -17037,49 +17037,49 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="E255" s="3" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F255" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E255" s="3" t="inlineStr"/>
+      <c r="F255" s="3" t="inlineStr"/>
       <c r="G255" s="3" t="inlineStr"/>
       <c r="H255" s="3" t="inlineStr"/>
-      <c r="I255" s="3" t="inlineStr"/>
+      <c r="I255" s="3" t="inlineStr">
+        <is>
+          <t>x¹</t>
+        </is>
+      </c>
       <c r="J255" s="3" t="inlineStr"/>
-      <c r="K255" s="3" t="inlineStr"/>
+      <c r="K255" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>Surface temperature (i.e. temperature at which long-wave radiation emitted)</t>
+          <t>Urban Percentage Area Coverage</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>surface_temperature</t>
+          <t>area_fraction</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t>TSK</t>
+          <t>LANDUSEF</t>
         </is>
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_ts (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
+          <t>CORDEX_Cmor: RCM_fx_landuse (fx varset) and RCM_sfc_landuse (landuse varset); LANDUSEF urban classes incl. LCZ (landuse_field in shared_subs_v2.f90)</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>urbanFrac</t>
+          <t>vortmen</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -17094,106 +17094,106 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E256" s="3" t="inlineStr"/>
+          <t>s-1</t>
+        </is>
+      </c>
+      <c r="E256" s="3" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
       <c r="F256" s="3" t="inlineStr"/>
-      <c r="G256" s="3" t="inlineStr"/>
+      <c r="G256" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H256" s="3" t="inlineStr"/>
-      <c r="I256" s="3" t="inlineStr">
-        <is>
-          <t>x¹</t>
-        </is>
-      </c>
+      <c r="I256" s="3" t="inlineStr"/>
       <c r="J256" s="3" t="inlineStr"/>
-      <c r="K256" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="K256" s="3" t="inlineStr"/>
       <c r="L256" t="inlineStr">
         <is>
-          <t>Urban Percentage Area Coverage</t>
+          <t>relative vorticity</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>area_fraction</t>
+          <t>atmosphere_relative_vorticity</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
         <is>
-          <t>LANDUSEF</t>
+          <t>U V MAPFAC_U MAPFAC_V MAPFAC_M P PB</t>
         </is>
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_fx_landuse (fx varset) and RCM_sfc_landuse (landuse varset); LANDUSEF urban classes incl. LCZ (landuse_field in shared_subs_v2.f90)</t>
+          <t>CORDEX_Cmor: RCM_plev_vortmen (plev_vortmen0/1 varsets), as vortmen&lt;p&gt; on each pressure level (1000 to 30 hPa); m^2 [d(v/m_v)/dx - d(u/m_u)/dy] as wrf-python; every wp_step hours (grid ini)</t>
         </is>
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="4" t="inlineStr">
-        <is>
-          <t>vortmen</t>
-        </is>
-      </c>
-      <c r="B257" s="4" t="inlineStr">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>wap</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
         <is>
           <t>FPS-LUCAS</t>
         </is>
       </c>
-      <c r="C257" s="4" t="inlineStr">
+      <c r="C257" t="inlineStr">
         <is>
           <t>TIER 1</t>
         </is>
       </c>
-      <c r="D257" s="4" t="inlineStr">
-        <is>
-          <t>s-1</t>
-        </is>
-      </c>
-      <c r="E257" s="5" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F257" s="5" t="inlineStr"/>
-      <c r="G257" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="H257" s="5" t="inlineStr"/>
-      <c r="I257" s="5" t="inlineStr"/>
-      <c r="J257" s="5" t="inlineStr"/>
-      <c r="K257" s="5" t="inlineStr"/>
-      <c r="L257" s="4" t="inlineStr">
-        <is>
-          <t>relative vorticity</t>
-        </is>
-      </c>
-      <c r="M257" s="4" t="inlineStr">
-        <is>
-          <t>atmosphere_relative_vorticity</t>
-        </is>
-      </c>
-      <c r="N257" s="4" t="inlineStr">
-        <is>
-          <t>U V MAPFAC_U MAPFAC_V MAPFAC_M P PB</t>
-        </is>
-      </c>
-      <c r="O257" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; relative vorticity on pressure levels</t>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Pa s-1</t>
+        </is>
+      </c>
+      <c r="E257" s="3" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F257" s="3" t="inlineStr"/>
+      <c r="G257" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H257" s="3" t="inlineStr"/>
+      <c r="I257" s="3" t="inlineStr"/>
+      <c r="J257" s="3" t="inlineStr"/>
+      <c r="K257" s="3" t="inlineStr"/>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>omega</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>lagrangian_tendency_of_air_pressure</t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>W T QVAPOR P PB</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_plev_wap (plev_wap varset), as wap&lt;p&gt; on each pressure level (1000 to 30 hPa); omega = -rho g w; every wp_step hours (grid ini)</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>wap</t>
+          <t>slthick</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -17208,49 +17208,49 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Pa s-1</t>
-        </is>
-      </c>
-      <c r="E258" s="3" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E258" s="3" t="inlineStr"/>
       <c r="F258" s="3" t="inlineStr"/>
-      <c r="G258" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="G258" s="3" t="inlineStr"/>
       <c r="H258" s="3" t="inlineStr"/>
-      <c r="I258" s="3" t="inlineStr"/>
+      <c r="I258" s="3" t="inlineStr">
+        <is>
+          <t>x¹</t>
+        </is>
+      </c>
       <c r="J258" s="3" t="inlineStr"/>
-      <c r="K258" s="3" t="inlineStr"/>
+      <c r="K258" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>omega</t>
+          <t>Thickness of Soil Layers</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>lagrangian_tendency_of_air_pressure</t>
+          <t>cell_thickness</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t>W T QVAPOR P PB</t>
+          <t>DZS</t>
         </is>
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_wap (plev_wap varset), as wap&lt;p&gt; on each pressure level (1000 to 30 hPa); omega = -rho g w; every wp_step hours (grid ini)</t>
+          <t>CORDEX_Cmor: RCM_fx_slthick (fx varset)</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>slthick</t>
+          <t>lcvr</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -17258,18 +17258,18 @@
           <t>FPS-LUCAS</t>
         </is>
       </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>TIER 1</t>
-        </is>
-      </c>
+      <c r="C259" t="inlineStr"/>
       <c r="D259" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E259" s="3" t="inlineStr"/>
-      <c r="F259" s="3" t="inlineStr"/>
+      <c r="F259" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G259" s="3" t="inlineStr"/>
       <c r="H259" s="3" t="inlineStr"/>
       <c r="I259" s="3" t="inlineStr">
@@ -17285,88 +17285,31 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>Thickness of Soil Layers</t>
-        </is>
-      </c>
-      <c r="M259" t="inlineStr">
-        <is>
-          <t>cell_thickness</t>
-        </is>
-      </c>
+          <t>Land Cover Dominant Class</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr"/>
       <c r="N259" t="inlineStr">
         <is>
-          <t>DZS</t>
+          <t>LU_INDEX</t>
         </is>
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_fx_slthick (fx varset)</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>lcvr</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>FPS-LUCAS</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr"/>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E260" s="3" t="inlineStr"/>
-      <c r="F260" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G260" s="3" t="inlineStr"/>
-      <c r="H260" s="3" t="inlineStr"/>
-      <c r="I260" s="3" t="inlineStr">
-        <is>
-          <t>x¹</t>
-        </is>
-      </c>
-      <c r="J260" s="3" t="inlineStr"/>
-      <c r="K260" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="L260" t="inlineStr">
-        <is>
-          <t>Land Cover Dominant Class</t>
-        </is>
-      </c>
-      <c r="M260" t="inlineStr"/>
-      <c r="N260" t="inlineStr">
-        <is>
-          <t>LU_INDEX</t>
-        </is>
-      </c>
-      <c r="O260" t="inlineStr">
-        <is>
           <t>CORDEX_Cmor: RCM_fx_lcvr (fx varset, from geo_em) and RCM_sfc_landuse (landuse varset); LU_INDEX (dominant land-use class); hourly from wrfout; not in the phase 2 workbook list</t>
         </is>
       </c>
     </row>
-    <row r="261"/>
-    <row r="262">
-      <c r="A262" s="6" t="inlineStr">
+    <row r="260"/>
+    <row r="261">
+      <c r="A261" s="6" t="inlineStr">
         <is>
           <t>¹ LUCAS frequency: requested by FPS-LUCAS but not by CORDEX-CMIP6 for this variable; time-invariant (fx) variables are assumed to be also daily variables in LUCAS</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O260"/>
+  <autoFilter ref="A1:O259"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/CORDEX_Cmor_variables.xlsx
+++ b/CORDEX_Cmor_variables.xlsx
@@ -15025,59 +15025,59 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="4" t="inlineStr">
+      <c r="A220" t="inlineStr">
         <is>
           <t>albc</t>
         </is>
       </c>
-      <c r="B220" s="4" t="inlineStr">
+      <c r="B220" t="inlineStr">
         <is>
           <t>FPS-LUCAS</t>
         </is>
       </c>
-      <c r="C220" s="4" t="inlineStr">
+      <c r="C220" t="inlineStr">
         <is>
           <t>TIER 1</t>
         </is>
       </c>
-      <c r="D220" s="4" t="inlineStr">
+      <c r="D220" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E220" s="5" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F220" s="5" t="inlineStr"/>
-      <c r="G220" s="5" t="inlineStr"/>
-      <c r="H220" s="5" t="inlineStr"/>
-      <c r="I220" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J220" s="5" t="inlineStr"/>
-      <c r="K220" s="5" t="inlineStr"/>
-      <c r="L220" s="4" t="inlineStr">
+      <c r="E220" s="3" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F220" s="3" t="inlineStr"/>
+      <c r="G220" s="3" t="inlineStr"/>
+      <c r="H220" s="3" t="inlineStr"/>
+      <c r="I220" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J220" s="3" t="inlineStr"/>
+      <c r="K220" s="3" t="inlineStr"/>
+      <c r="L220" t="inlineStr">
         <is>
           <t>Albedo of the vegetation: fraction of incoming solar radiation which is reflected before reaching the ground.</t>
         </is>
       </c>
-      <c r="M220" s="4" t="inlineStr">
+      <c r="M220" t="inlineStr">
         <is>
           <t>canopy_albedo</t>
         </is>
       </c>
-      <c r="N220" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O220" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; no canopy albedo in the WRF output</t>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>ALBEDO LANDUSEF</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_sfc_albc (lsm varset); ALBEDO x vegetated fraction of the cell (LANDUSEF classes of cnc)</t>
         </is>
       </c>
     </row>

--- a/CORDEX_Cmor_variables.xlsx
+++ b/CORDEX_Cmor_variables.xlsx
@@ -16108,59 +16108,59 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="4" t="inlineStr">
+      <c r="A239" t="inlineStr">
         <is>
           <t>pastureFrac</t>
         </is>
       </c>
-      <c r="B239" s="4" t="inlineStr">
+      <c r="B239" t="inlineStr">
         <is>
           <t>FPS-LUCAS</t>
         </is>
       </c>
-      <c r="C239" s="4" t="inlineStr">
+      <c r="C239" t="inlineStr">
         <is>
           <t>TIER 1</t>
         </is>
       </c>
-      <c r="D239" s="4" t="inlineStr">
+      <c r="D239" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E239" s="5" t="inlineStr"/>
-      <c r="F239" s="5" t="inlineStr"/>
-      <c r="G239" s="5" t="inlineStr"/>
-      <c r="H239" s="5" t="inlineStr"/>
-      <c r="I239" s="5" t="inlineStr">
+      <c r="E239" s="3" t="inlineStr"/>
+      <c r="F239" s="3" t="inlineStr"/>
+      <c r="G239" s="3" t="inlineStr"/>
+      <c r="H239" s="3" t="inlineStr"/>
+      <c r="I239" s="3" t="inlineStr">
         <is>
           <t>x¹</t>
         </is>
       </c>
-      <c r="J239" s="5" t="inlineStr"/>
-      <c r="K239" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="L239" s="4" t="inlineStr">
+      <c r="J239" s="3" t="inlineStr"/>
+      <c r="K239" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
         <is>
           <t>Percentage of Land Which Is Anthropogenic Pasture</t>
         </is>
       </c>
-      <c r="M239" s="4" t="inlineStr">
+      <c r="M239" t="inlineStr">
         <is>
           <t>area_fraction</t>
         </is>
       </c>
-      <c r="N239" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O239" s="4" t="inlineStr">
-        <is>
-          <t>not produced by CORDEX_Cmor; header ready; no pasture class in the WRF land-use tables</t>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>LANDUSEF</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>CORDEX_Cmor: RCM_fx_landuse (fx varset) and RCM_sfc_landuse (landuse varset)</t>
         </is>
       </c>
     </row>

--- a/CORDEX_Cmor_variables.xlsx
+++ b/CORDEX_Cmor_variables.xlsx
@@ -546,7 +546,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4998,7 +4998,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -6114,7 +6114,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -7092,7 +7092,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -7303,7 +7303,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -7514,7 +7514,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -7794,7 +7794,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -8005,7 +8005,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -9776,7 +9776,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>CORDEX-CMIP6, FPS-LUCAS</t>
+          <t>CORDEX-CMIP6</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">

--- a/CORDEX_Cmor_variables.xlsx
+++ b/CORDEX_Cmor_variables.xlsx
@@ -9694,12 +9694,12 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>P PB T QVAPOR PH PHB HGT</t>
+          <t>P PB T QVAPOR PH PHB</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_cape (cape varset; cin li lcl archived as cape_x); surface parcel, Romps 2017 LCL, Bolton 1980 pseudo-adiabat, virtual temperature (RIP/wrf-python EL/LFC)</t>
+          <t>CORDEX_Cmor: RCM_sfc_cape (cape varset; cin li archived as cape_x); surface parcel lifted to the model top, Romps 2017 LCL, Bolton 1980 pseudo-adiabat, virtual temperature (RIP/wrf-python EL/LFC)</t>
         </is>
       </c>
     </row>
@@ -9759,12 +9759,12 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>P PB T QVAPOR PH PHB HGT</t>
+          <t>P PB T QVAPOR PH PHB</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_cape (cape varset; cin li lcl archived as cape_x); with cape; at 500 hPa</t>
+          <t>CORDEX_Cmor: RCM_sfc_cape (cape varset; cin li archived as cape_x); with cape; at 500 hPa</t>
         </is>
       </c>
     </row>
@@ -9824,12 +9824,12 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>P PB T QVAPOR PH PHB HGT</t>
+          <t>P PB T QVAPOR PH PHB</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_cape (cape varset; cin li lcl archived as cape_x); with cape; 0 where there is no CAPE</t>
+          <t>CORDEX_Cmor: RCM_sfc_cape (cape varset; cin li archived as cape_x); with cape; 0 where there is no CAPE</t>
         </is>
       </c>
     </row>
@@ -9881,7 +9881,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>P PB T QVAPOR PH PHB HGT</t>
+          <t>P PB T QVAPOR PH PHB</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>P PB T QVAPOR PH PHB HGT</t>
+          <t>P PB T QVAPOR PH PHB</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
@@ -9995,7 +9995,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>P PB T QVAPOR PH PHB HGT</t>
+          <t>P PB T QVAPOR PH PHB</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">

--- a/CORDEX_Cmor_variables.xlsx
+++ b/CORDEX_Cmor_variables.xlsx
@@ -551,7 +551,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CORE; LUCAS CORE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CORE; LUCAS CORE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CORE; LUCAS CORE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CORE; LUCAS CORE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CORE; LUCAS CORE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CORE; LUCAS CORE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CORE; LUCAS CORE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CORE; LUCAS CORE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CORE; LUCAS CORE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CORE; LUCAS CORE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CORE; LUCAS CORE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CORE; LUCAS CORE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CORE; LUCAS CORE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CORE; LUCAS CORE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CORE; LUCAS CORE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CORE; LUCAS CORE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CORE; LUCAS CORE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TIER 1; LUCAS TIER 1</t>
+          <t>TIER 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TIER 1; LUCAS TIER 1</t>
+          <t>TIER 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">

--- a/CORDEX_Cmor_variables.xlsx
+++ b/CORDEX_Cmor_variables.xlsx
@@ -813,7 +813,11 @@
           <t>x</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H6" s="3" t="inlineStr"/>
       <c r="I6" s="3" t="inlineStr">
         <is>
@@ -1073,7 +1077,11 @@
           <t>x</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H10" s="3" t="inlineStr"/>
       <c r="I10" s="3" t="inlineStr">
         <is>
@@ -1333,7 +1341,11 @@
           <t>x</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H14" s="3" t="inlineStr"/>
       <c r="I14" s="3" t="inlineStr">
         <is>
@@ -1829,7 +1841,11 @@
           <t>x</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr"/>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H22" s="3" t="inlineStr"/>
       <c r="I22" s="3" t="inlineStr">
         <is>
@@ -1891,7 +1907,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>x¹</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr"/>
@@ -2019,11 +2035,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr"/>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F25" s="5" t="inlineStr"/>
       <c r="G25" s="5" t="inlineStr"/>
       <c r="H25" s="5" t="inlineStr"/>
       <c r="I25" s="5" t="inlineStr">
@@ -2031,11 +2043,7 @@
           <t>x</t>
         </is>
       </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="J25" s="5" t="inlineStr"/>
       <c r="K25" s="5" t="inlineStr"/>
       <c r="L25" s="4" t="inlineStr">
         <is>
@@ -2089,7 +2097,11 @@
           <t>x</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr"/>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H26" s="3" t="inlineStr"/>
       <c r="I26" s="3" t="inlineStr">
         <is>
@@ -2151,7 +2163,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>x¹</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr"/>
@@ -2188,7 +2200,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_mrros (soil varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_mrros (soil varset); written every wp_step hours (grid ini)</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2232,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>x¹</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr"/>
@@ -2257,7 +2269,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_mrro (soil varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_mrro (soil varset); written every wp_step hours (grid ini)</t>
         </is>
       </c>
     </row>
@@ -2287,11 +2299,7 @@
           <t>a</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F29" s="3" t="inlineStr"/>
       <c r="G29" s="3" t="inlineStr"/>
       <c r="H29" s="3" t="inlineStr">
         <is>
@@ -2326,7 +2334,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_snm (snw varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_snm (snw varset); written every wp_step hours (grid ini)</t>
         </is>
       </c>
     </row>
@@ -2570,7 +2578,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_sund (snw varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_sund (snw varset); written daily</t>
         </is>
       </c>
     </row>
@@ -2995,7 +3003,11 @@
           <t>x</t>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr"/>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H40" s="3" t="inlineStr"/>
       <c r="I40" s="3" t="inlineStr">
         <is>
@@ -3060,7 +3072,11 @@
           <t>x</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr"/>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H41" s="3" t="inlineStr"/>
       <c r="I41" s="3" t="inlineStr">
         <is>
@@ -3155,7 +3171,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_mrfso (soil varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_mrfso (soil varset); written every wp_step hours (grid ini)</t>
         </is>
       </c>
     </row>
@@ -3317,7 +3333,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>x¹</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr"/>
@@ -3354,7 +3370,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_mrso (soil varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_mrso (soil varset); written every wp_step hours (grid ini)</t>
         </is>
       </c>
     </row>
@@ -3389,7 +3405,11 @@
           <t>x</t>
         </is>
       </c>
-      <c r="G46" s="3" t="inlineStr"/>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H46" s="3" t="inlineStr"/>
       <c r="I46" s="3" t="inlineStr">
         <is>
@@ -3451,7 +3471,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>x¹</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr"/>
@@ -3518,11 +3538,7 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F48" s="3" t="inlineStr"/>
       <c r="G48" s="3" t="inlineStr"/>
       <c r="H48" s="3" t="inlineStr">
         <is>
@@ -3557,7 +3573,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_snw (snw varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_snw (snw varset); written every wp_step hours (grid ini)</t>
         </is>
       </c>
     </row>
@@ -3587,11 +3603,7 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F49" s="3" t="inlineStr"/>
       <c r="G49" s="3" t="inlineStr"/>
       <c r="H49" s="3" t="inlineStr">
         <is>
@@ -3626,7 +3638,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_snc (snw varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_snc (snw varset); written every wp_step hours (grid ini)</t>
         </is>
       </c>
     </row>
@@ -3656,11 +3668,7 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F50" s="3" t="inlineStr"/>
       <c r="G50" s="3" t="inlineStr"/>
       <c r="H50" s="3" t="inlineStr">
         <is>
@@ -3695,7 +3703,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_snd (snw varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_snd (snw varset); written every wp_step hours (grid ini)</t>
         </is>
       </c>
     </row>
@@ -3752,7 +3760,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_siconca (snw varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_siconca (snw varset); written daily</t>
         </is>
       </c>
     </row>
@@ -3789,7 +3797,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>x¹</t>
+          <t>x</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr"/>
@@ -3856,7 +3864,11 @@
           <t>x</t>
         </is>
       </c>
-      <c r="G53" s="3" t="inlineStr"/>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H53" s="3" t="inlineStr"/>
       <c r="I53" s="3" t="inlineStr">
         <is>
@@ -3921,7 +3933,11 @@
           <t>x</t>
         </is>
       </c>
-      <c r="G54" s="3" t="inlineStr"/>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H54" s="3" t="inlineStr"/>
       <c r="I54" s="3" t="inlineStr">
         <is>
@@ -4176,12 +4192,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F58" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G58" s="3" t="inlineStr"/>
+      <c r="F58" s="3" t="inlineStr"/>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -4245,12 +4261,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F59" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G59" s="3" t="inlineStr"/>
+      <c r="F59" s="3" t="inlineStr"/>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -4314,14 +4330,10 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F60" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F60" s="3" t="inlineStr"/>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>x¹</t>
+          <t>x</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
@@ -4387,12 +4399,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F61" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="inlineStr"/>
+      <c r="F61" s="3" t="inlineStr"/>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -4456,12 +4468,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F62" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G62" s="3" t="inlineStr"/>
+      <c r="F62" s="3" t="inlineStr"/>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -4525,14 +4537,10 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F63" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F63" s="3" t="inlineStr"/>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>x¹</t>
+          <t>x</t>
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr">
@@ -4598,12 +4606,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F64" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G64" s="3" t="inlineStr"/>
+      <c r="F64" s="3" t="inlineStr"/>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -4667,12 +4675,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F65" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G65" s="3" t="inlineStr"/>
+      <c r="F65" s="3" t="inlineStr"/>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -4736,14 +4744,10 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F66" s="3" t="inlineStr"/>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>x¹</t>
+          <t>x</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
@@ -4809,12 +4813,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F67" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G67" s="3" t="inlineStr"/>
+      <c r="F67" s="3" t="inlineStr"/>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -4878,12 +4882,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F68" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G68" s="3" t="inlineStr"/>
+      <c r="F68" s="3" t="inlineStr"/>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -4947,12 +4951,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F69" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G69" s="3" t="inlineStr"/>
+      <c r="F69" s="3" t="inlineStr"/>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -5016,14 +5020,10 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F70" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F70" s="3" t="inlineStr"/>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>x¹</t>
+          <t>x</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
@@ -5089,12 +5089,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F71" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G71" s="3" t="inlineStr"/>
+      <c r="F71" s="3" t="inlineStr"/>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -5158,12 +5158,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F72" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G72" s="3" t="inlineStr"/>
+      <c r="F72" s="3" t="inlineStr"/>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -5227,14 +5227,10 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F73" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F73" s="3" t="inlineStr"/>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>x¹</t>
+          <t>x</t>
         </is>
       </c>
       <c r="H73" s="3" t="inlineStr">
@@ -5300,12 +5296,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F74" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G74" s="3" t="inlineStr"/>
+      <c r="F74" s="3" t="inlineStr"/>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -5369,12 +5365,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F75" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G75" s="3" t="inlineStr"/>
+      <c r="F75" s="3" t="inlineStr"/>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -5438,14 +5434,10 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F76" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F76" s="3" t="inlineStr"/>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>x¹</t>
+          <t>x</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
@@ -5511,12 +5503,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F77" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G77" s="3" t="inlineStr"/>
+      <c r="F77" s="3" t="inlineStr"/>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -5580,12 +5572,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F78" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G78" s="3" t="inlineStr"/>
+      <c r="F78" s="3" t="inlineStr"/>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -5649,12 +5641,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F79" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G79" s="3" t="inlineStr"/>
+      <c r="F79" s="3" t="inlineStr"/>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -5718,12 +5710,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F80" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G80" s="3" t="inlineStr"/>
+      <c r="F80" s="3" t="inlineStr"/>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -5787,12 +5779,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F81" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G81" s="3" t="inlineStr"/>
+      <c r="F81" s="3" t="inlineStr"/>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -5856,12 +5848,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F82" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G82" s="3" t="inlineStr"/>
+      <c r="F82" s="3" t="inlineStr"/>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -5925,12 +5917,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F83" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G83" s="3" t="inlineStr"/>
+      <c r="F83" s="3" t="inlineStr"/>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -5994,12 +5986,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F84" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G84" s="3" t="inlineStr"/>
+      <c r="F84" s="3" t="inlineStr"/>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -6063,12 +6055,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F85" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G85" s="3" t="inlineStr"/>
+      <c r="F85" s="3" t="inlineStr"/>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -6132,12 +6124,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F86" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G86" s="3" t="inlineStr"/>
+      <c r="F86" s="3" t="inlineStr"/>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -6201,12 +6193,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F87" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G87" s="3" t="inlineStr"/>
+      <c r="F87" s="3" t="inlineStr"/>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -6270,12 +6262,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F88" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G88" s="3" t="inlineStr"/>
+      <c r="F88" s="3" t="inlineStr"/>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -6339,12 +6331,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F89" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G89" s="3" t="inlineStr"/>
+      <c r="F89" s="3" t="inlineStr"/>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H89" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -6408,14 +6400,10 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F90" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F90" s="3" t="inlineStr"/>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>x¹</t>
+          <t>x</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
@@ -6481,12 +6469,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F91" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G91" s="3" t="inlineStr"/>
+      <c r="F91" s="3" t="inlineStr"/>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -6550,12 +6538,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F92" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G92" s="3" t="inlineStr"/>
+      <c r="F92" s="3" t="inlineStr"/>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -6619,14 +6607,10 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F93" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F93" s="3" t="inlineStr"/>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>x¹</t>
+          <t>x</t>
         </is>
       </c>
       <c r="H93" s="3" t="inlineStr">
@@ -6692,12 +6676,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F94" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G94" s="3" t="inlineStr"/>
+      <c r="F94" s="3" t="inlineStr"/>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -6761,12 +6745,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F95" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G95" s="3" t="inlineStr"/>
+      <c r="F95" s="3" t="inlineStr"/>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -6830,12 +6814,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F96" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G96" s="3" t="inlineStr"/>
+      <c r="F96" s="3" t="inlineStr"/>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -6899,14 +6883,10 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F97" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F97" s="3" t="inlineStr"/>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>x¹</t>
+          <t>x</t>
         </is>
       </c>
       <c r="H97" s="3" t="inlineStr">
@@ -6972,12 +6952,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F98" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G98" s="3" t="inlineStr"/>
+      <c r="F98" s="3" t="inlineStr"/>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -7041,12 +7021,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F99" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G99" s="3" t="inlineStr"/>
+      <c r="F99" s="3" t="inlineStr"/>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -7110,14 +7090,10 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F100" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F100" s="3" t="inlineStr"/>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>x¹</t>
+          <t>x</t>
         </is>
       </c>
       <c r="H100" s="3" t="inlineStr">
@@ -7183,12 +7159,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F101" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G101" s="3" t="inlineStr"/>
+      <c r="F101" s="3" t="inlineStr"/>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H101" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -7252,12 +7228,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F102" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G102" s="3" t="inlineStr"/>
+      <c r="F102" s="3" t="inlineStr"/>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -7321,14 +7297,10 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F103" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F103" s="3" t="inlineStr"/>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>x¹</t>
+          <t>x</t>
         </is>
       </c>
       <c r="H103" s="3" t="inlineStr">
@@ -7394,12 +7366,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F104" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G104" s="3" t="inlineStr"/>
+      <c r="F104" s="3" t="inlineStr"/>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -7463,12 +7435,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F105" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G105" s="3" t="inlineStr"/>
+      <c r="F105" s="3" t="inlineStr"/>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -7532,14 +7504,10 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F106" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F106" s="3" t="inlineStr"/>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>x¹</t>
+          <t>x</t>
         </is>
       </c>
       <c r="H106" s="3" t="inlineStr">
@@ -7605,12 +7573,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F107" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G107" s="3" t="inlineStr"/>
+      <c r="F107" s="3" t="inlineStr"/>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H107" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -7674,12 +7642,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F108" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G108" s="3" t="inlineStr"/>
+      <c r="F108" s="3" t="inlineStr"/>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -7743,12 +7711,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F109" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G109" s="3" t="inlineStr"/>
+      <c r="F109" s="3" t="inlineStr"/>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -7812,14 +7780,10 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F110" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F110" s="3" t="inlineStr"/>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>x¹</t>
+          <t>x</t>
         </is>
       </c>
       <c r="H110" s="3" t="inlineStr">
@@ -7885,12 +7849,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F111" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G111" s="3" t="inlineStr"/>
+      <c r="F111" s="3" t="inlineStr"/>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H111" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -7954,12 +7918,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F112" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G112" s="3" t="inlineStr"/>
+      <c r="F112" s="3" t="inlineStr"/>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -8023,14 +7987,10 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F113" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F113" s="3" t="inlineStr"/>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>x¹</t>
+          <t>x</t>
         </is>
       </c>
       <c r="H113" s="3" t="inlineStr">
@@ -8096,12 +8056,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F114" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G114" s="3" t="inlineStr"/>
+      <c r="F114" s="3" t="inlineStr"/>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -8165,12 +8125,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F115" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G115" s="3" t="inlineStr"/>
+      <c r="F115" s="3" t="inlineStr"/>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H115" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -8234,14 +8194,10 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F116" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F116" s="3" t="inlineStr"/>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>x¹</t>
+          <t>x</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
@@ -8307,12 +8263,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F117" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G117" s="3" t="inlineStr"/>
+      <c r="F117" s="3" t="inlineStr"/>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H117" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -9053,7 +9009,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_cloud (cloud1 varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_cloud (cloud1 varset); written every wp_step hours (grid ini)</t>
         </is>
       </c>
     </row>
@@ -9118,7 +9074,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_cloud (cloud1 varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_cloud (cloud1 varset); written every wp_step hours (grid ini)</t>
         </is>
       </c>
     </row>
@@ -9183,7 +9139,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_cloud (cloud2 varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_cloud (cloud2 varset); written every wp_step hours (grid ini)</t>
         </is>
       </c>
     </row>
@@ -9248,7 +9204,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset); written every wp_step hours (grid ini)</t>
         </is>
       </c>
     </row>
@@ -9313,7 +9269,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset); written every wp_step hours (grid ini)</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9334,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset); written every wp_step hours (grid ini)</t>
         </is>
       </c>
     </row>
@@ -9443,7 +9399,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset); written every wp_step hours (grid ini)</t>
         </is>
       </c>
     </row>
@@ -9508,7 +9464,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset); written every wp_step hours (grid ini)</t>
         </is>
       </c>
     </row>
@@ -9573,7 +9529,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset); written every wp_step hours (grid ini)</t>
         </is>
       </c>
     </row>
@@ -9634,7 +9590,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_z0 (out2 varset); z0 = 10 exp(-k U10/UST), from the 10 m wind and UST (not ZNT)</t>
+          <t>CORDEX_Cmor: RCM_sfc_z0 (out2 varset); written daily; z0 = 10 exp(-k U10/UST), from the 10 m wind and UST (not ZNT)</t>
         </is>
       </c>
     </row>
@@ -9669,7 +9625,11 @@
           <t>x</t>
         </is>
       </c>
-      <c r="G138" s="3" t="inlineStr"/>
+      <c r="G138" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H138" s="3" t="inlineStr"/>
       <c r="I138" s="3" t="inlineStr">
         <is>
@@ -10026,10 +9986,18 @@
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr"/>
-      <c r="F144" s="3" t="inlineStr"/>
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G144" s="3" t="inlineStr"/>
       <c r="H144" s="3" t="inlineStr"/>
-      <c r="I144" s="3" t="inlineStr"/>
+      <c r="I144" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -10083,12 +10051,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F145" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G145" s="3" t="inlineStr"/>
+      <c r="F145" s="3" t="inlineStr"/>
+      <c r="G145" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H145" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -10152,12 +10120,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F146" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G146" s="3" t="inlineStr"/>
+      <c r="F146" s="3" t="inlineStr"/>
+      <c r="G146" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -10221,12 +10189,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F147" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G147" s="3" t="inlineStr"/>
+      <c r="F147" s="3" t="inlineStr"/>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H147" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -10290,12 +10258,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F148" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G148" s="3" t="inlineStr"/>
+      <c r="F148" s="3" t="inlineStr"/>
+      <c r="G148" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -10359,12 +10327,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F149" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G149" s="3" t="inlineStr"/>
+      <c r="F149" s="3" t="inlineStr"/>
+      <c r="G149" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H149" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -10428,12 +10396,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F150" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G150" s="5" t="inlineStr"/>
+      <c r="F150" s="5" t="inlineStr"/>
+      <c r="G150" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H150" s="5" t="inlineStr">
         <is>
           <t>x</t>
@@ -10497,12 +10465,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F151" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G151" s="5" t="inlineStr"/>
+      <c r="F151" s="5" t="inlineStr"/>
+      <c r="G151" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H151" s="5" t="inlineStr">
         <is>
           <t>x</t>
@@ -10566,12 +10534,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F152" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G152" s="3" t="inlineStr"/>
+      <c r="F152" s="3" t="inlineStr"/>
+      <c r="G152" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -10635,12 +10603,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F153" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G153" s="3" t="inlineStr"/>
+      <c r="F153" s="3" t="inlineStr"/>
+      <c r="G153" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H153" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -10704,12 +10672,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F154" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G154" s="3" t="inlineStr"/>
+      <c r="F154" s="3" t="inlineStr"/>
+      <c r="G154" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -10773,12 +10741,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F155" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G155" s="3" t="inlineStr"/>
+      <c r="F155" s="3" t="inlineStr"/>
+      <c r="G155" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H155" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -10842,12 +10810,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F156" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G156" s="3" t="inlineStr"/>
+      <c r="F156" s="3" t="inlineStr"/>
+      <c r="G156" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -10911,12 +10879,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F157" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G157" s="5" t="inlineStr"/>
+      <c r="F157" s="5" t="inlineStr"/>
+      <c r="G157" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H157" s="5" t="inlineStr">
         <is>
           <t>x</t>
@@ -10980,12 +10948,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F158" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G158" s="5" t="inlineStr"/>
+      <c r="F158" s="5" t="inlineStr"/>
+      <c r="G158" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H158" s="5" t="inlineStr">
         <is>
           <t>x</t>
@@ -11049,12 +11017,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F159" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G159" s="3" t="inlineStr"/>
+      <c r="F159" s="3" t="inlineStr"/>
+      <c r="G159" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H159" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -11118,12 +11086,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F160" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G160" s="3" t="inlineStr"/>
+      <c r="F160" s="3" t="inlineStr"/>
+      <c r="G160" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -11187,12 +11155,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F161" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G161" s="3" t="inlineStr"/>
+      <c r="F161" s="3" t="inlineStr"/>
+      <c r="G161" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H161" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -11256,12 +11224,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F162" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G162" s="3" t="inlineStr"/>
+      <c r="F162" s="3" t="inlineStr"/>
+      <c r="G162" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -11325,12 +11293,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F163" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G163" s="3" t="inlineStr"/>
+      <c r="F163" s="3" t="inlineStr"/>
+      <c r="G163" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H163" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -11394,12 +11362,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F164" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G164" s="5" t="inlineStr"/>
+      <c r="F164" s="5" t="inlineStr"/>
+      <c r="G164" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H164" s="5" t="inlineStr">
         <is>
           <t>x</t>
@@ -11463,12 +11431,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F165" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G165" s="5" t="inlineStr"/>
+      <c r="F165" s="5" t="inlineStr"/>
+      <c r="G165" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H165" s="5" t="inlineStr">
         <is>
           <t>x</t>
@@ -11532,12 +11500,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F166" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G166" s="3" t="inlineStr"/>
+      <c r="F166" s="3" t="inlineStr"/>
+      <c r="G166" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -11601,12 +11569,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F167" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G167" s="3" t="inlineStr"/>
+      <c r="F167" s="3" t="inlineStr"/>
+      <c r="G167" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H167" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -11670,12 +11638,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F168" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G168" s="3" t="inlineStr"/>
+      <c r="F168" s="3" t="inlineStr"/>
+      <c r="G168" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -11739,12 +11707,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F169" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G169" s="3" t="inlineStr"/>
+      <c r="F169" s="3" t="inlineStr"/>
+      <c r="G169" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H169" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -11808,12 +11776,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F170" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G170" s="3" t="inlineStr"/>
+      <c r="F170" s="3" t="inlineStr"/>
+      <c r="G170" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -11877,12 +11845,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F171" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G171" s="5" t="inlineStr"/>
+      <c r="F171" s="5" t="inlineStr"/>
+      <c r="G171" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H171" s="5" t="inlineStr">
         <is>
           <t>x</t>
@@ -11946,12 +11914,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F172" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G172" s="5" t="inlineStr"/>
+      <c r="F172" s="5" t="inlineStr"/>
+      <c r="G172" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H172" s="5" t="inlineStr">
         <is>
           <t>x</t>
@@ -12015,12 +11983,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F173" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G173" s="3" t="inlineStr"/>
+      <c r="F173" s="3" t="inlineStr"/>
+      <c r="G173" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H173" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -12084,12 +12052,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F174" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G174" s="3" t="inlineStr"/>
+      <c r="F174" s="3" t="inlineStr"/>
+      <c r="G174" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H174" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -12153,12 +12121,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F175" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G175" s="3" t="inlineStr"/>
+      <c r="F175" s="3" t="inlineStr"/>
+      <c r="G175" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H175" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -12222,12 +12190,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F176" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G176" s="3" t="inlineStr"/>
+      <c r="F176" s="3" t="inlineStr"/>
+      <c r="G176" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H176" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -12291,12 +12259,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F177" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G177" s="3" t="inlineStr"/>
+      <c r="F177" s="3" t="inlineStr"/>
+      <c r="G177" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H177" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -12360,12 +12328,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F178" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G178" s="5" t="inlineStr"/>
+      <c r="F178" s="5" t="inlineStr"/>
+      <c r="G178" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H178" s="5" t="inlineStr">
         <is>
           <t>x</t>
@@ -12429,12 +12397,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F179" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G179" s="5" t="inlineStr"/>
+      <c r="F179" s="5" t="inlineStr"/>
+      <c r="G179" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H179" s="5" t="inlineStr">
         <is>
           <t>x</t>
@@ -12498,12 +12466,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F180" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G180" s="3" t="inlineStr"/>
+      <c r="F180" s="3" t="inlineStr"/>
+      <c r="G180" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H180" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -12567,12 +12535,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F181" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G181" s="3" t="inlineStr"/>
+      <c r="F181" s="3" t="inlineStr"/>
+      <c r="G181" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H181" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -12636,12 +12604,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F182" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G182" s="3" t="inlineStr"/>
+      <c r="F182" s="3" t="inlineStr"/>
+      <c r="G182" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H182" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -12705,12 +12673,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F183" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G183" s="3" t="inlineStr"/>
+      <c r="F183" s="3" t="inlineStr"/>
+      <c r="G183" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H183" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -12774,12 +12742,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F184" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G184" s="3" t="inlineStr"/>
+      <c r="F184" s="3" t="inlineStr"/>
+      <c r="G184" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H184" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -12843,12 +12811,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F185" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G185" s="5" t="inlineStr"/>
+      <c r="F185" s="5" t="inlineStr"/>
+      <c r="G185" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H185" s="5" t="inlineStr">
         <is>
           <t>x</t>
@@ -12912,12 +12880,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F186" s="5" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G186" s="5" t="inlineStr"/>
+      <c r="F186" s="5" t="inlineStr"/>
+      <c r="G186" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H186" s="5" t="inlineStr">
         <is>
           <t>x</t>
@@ -12981,12 +12949,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F187" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G187" s="3" t="inlineStr"/>
+      <c r="F187" s="3" t="inlineStr"/>
+      <c r="G187" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H187" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -13050,12 +13018,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F188" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G188" s="3" t="inlineStr"/>
+      <c r="F188" s="3" t="inlineStr"/>
+      <c r="G188" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H188" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -13119,12 +13087,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F189" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G189" s="3" t="inlineStr"/>
+      <c r="F189" s="3" t="inlineStr"/>
+      <c r="G189" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H189" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -13188,12 +13156,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F190" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G190" s="3" t="inlineStr"/>
+      <c r="F190" s="3" t="inlineStr"/>
+      <c r="G190" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H190" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -13257,12 +13225,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F191" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G191" s="3" t="inlineStr"/>
+      <c r="F191" s="3" t="inlineStr"/>
+      <c r="G191" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H191" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -13326,12 +13294,12 @@
           <t>i</t>
         </is>
       </c>
-      <c r="F192" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G192" s="3" t="inlineStr"/>
+      <c r="F192" s="3" t="inlineStr"/>
+      <c r="G192" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H192" s="3" t="inlineStr">
         <is>
           <t>x</t>
@@ -13806,12 +13774,12 @@
       <c r="G200" s="3" t="inlineStr"/>
       <c r="H200" s="3" t="inlineStr"/>
       <c r="I200" s="3" t="inlineStr"/>
-      <c r="J200" s="3" t="inlineStr"/>
-      <c r="K200" s="3" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="J200" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K200" s="3" t="inlineStr"/>
       <c r="L200" t="inlineStr">
         <is>
           <t>Percentage of the Grid Cell Occupied by City</t>
@@ -13970,7 +13938,11 @@
           <t>x</t>
         </is>
       </c>
-      <c r="G203" s="3" t="inlineStr"/>
+      <c r="G203" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="H203" s="3" t="inlineStr"/>
       <c r="I203" s="3" t="inlineStr">
         <is>
@@ -14963,7 +14935,7 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_lai (lsm varset); LUCAS name LAI</t>
+          <t>CORDEX_Cmor: RCM_sfc_lai (lsm varset); written daily; LUCAS name LAI</t>
         </is>
       </c>
     </row>
@@ -15020,7 +14992,7 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_alb (lsm varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_alb (lsm varset); written daily</t>
         </is>
       </c>
     </row>
@@ -15077,7 +15049,7 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_albc (lsm varset); ALBEDO x vegetated fraction of the cell (LANDUSEF classes of cnc)</t>
+          <t>CORDEX_Cmor: RCM_sfc_albc (lsm varset); written daily; ALBEDO x vegetated fraction of the cell (LANDUSEF classes of cnc)</t>
         </is>
       </c>
     </row>
@@ -15305,7 +15277,7 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_cVeg (lsm varset); meaningful with Noah-MP dynamic vegetation (opt_dveg) only</t>
+          <t>CORDEX_Cmor: RCM_sfc_cVeg (lsm varset); written daily; meaningful with Noah-MP dynamic vegetation (opt_dveg) only</t>
         </is>
       </c>
     </row>
@@ -15818,7 +15790,7 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_lai (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
+          <t>CORDEX_Cmor: RCM_sfc_lai (lut varset); written daily; no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
         </is>
       </c>
     </row>
@@ -16103,7 +16075,7 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_npp (lsm varset); meaningful with Noah-MP dynamic vegetation (opt_dveg) only</t>
+          <t>CORDEX_Cmor: RCM_sfc_npp (lsm varset); written daily; meaningful with Noah-MP dynamic vegetation (opt_dveg) only</t>
         </is>
       </c>
     </row>
@@ -16331,7 +16303,7 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_rough (lsm varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_rough (lsm varset); written daily</t>
         </is>
       </c>
     </row>

--- a/CORDEX_Cmor_variables.xlsx
+++ b/CORDEX_Cmor_variables.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_tas (out1 varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_tas (out1 varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_xtrm (wxtrm varset); wrfxtrm stream</t>
+          <t>CORDEX_Cmor: RCM_sfc_xtrm (wxtrm varset); written daily; wrfxtrm stream</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_xtrm (wxtrm varset); wrfxtrm stream</t>
+          <t>CORDEX_Cmor: RCM_sfc_xtrm (wxtrm varset); written daily; wrfxtrm stream</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_pr (snw varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_pr (snw varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_evspsbl (out1 varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_evspsbl (out1 varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_huss (out1 varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_huss (out1 varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_hurs (out1 varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_hurs (out1 varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_ps (out2 varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_ps (out2 varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_psl (out1 varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_psl (out1 varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_sfcWind (out2 varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_sfcWind (out2 varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_uas (out1 varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_uas (out1 varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_vas (out1 varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_vas (out1 varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_cloud (cloud2 varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_cloud (cloud2 varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_zlev_uava (zlev_uava1 varset)</t>
+          <t>CORDEX_Cmor: RCM_zlev_uava (zlev_uava1 varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_zlev_uava (zlev_uava1 varset)</t>
+          <t>CORDEX_Cmor: RCM_zlev_uava (zlev_uava1 varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_zlev_uava (zlev_uava1 varset)</t>
+          <t>CORDEX_Cmor: RCM_zlev_uava (zlev_uava1 varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_ts (out1 varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_ts (out1 varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_tsl (soil varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_tsl (soil varset); written every wp_step hours (grid ini: 6 CORDEX, 1 LUCAS)</t>
         </is>
       </c>
     </row>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_prc (snw varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_prc (snw varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_prsn (snw varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_prsn (snw varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_mrros (soil varset); written every wp_step hours (grid ini)</t>
+          <t>CORDEX_Cmor: RCM_sfc_mrros (soil varset); written every wp_step hours (grid ini: 6 CORDEX, 1 LUCAS)</t>
         </is>
       </c>
     </row>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_mrro (soil varset); written every wp_step hours (grid ini)</t>
+          <t>CORDEX_Cmor: RCM_sfc_mrro (soil varset); written every wp_step hours (grid ini: 6 CORDEX, 1 LUCAS)</t>
         </is>
       </c>
     </row>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_snm (snw varset); written every wp_step hours (grid ini)</t>
+          <t>CORDEX_Cmor: RCM_sfc_snm (snw varset); written every 6 hours</t>
         </is>
       </c>
     </row>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_tauu (out2 varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_tauu (out2 varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_tauv (out2 varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_tauv (out2 varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_xtrm (wxtrm varset); wrfxtrm stream</t>
+          <t>CORDEX_Cmor: RCM_sfc_xtrm (wxtrm varset); written daily; wrfxtrm stream</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_sund (snw varset); written daily</t>
+          <t>CORDEX_Cmor: RCM_sfc_sund (snw varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset); header uses ACSWDNBC (clear-sky downwelling); WRF also writes SWDDIR (instantaneous direct shortwave)</t>
+          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset); written hourly; header uses ACSWDNBC (clear-sky downwelling); WRF also writes SWDDIR (instantaneous direct shortwave)</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_hfls (out1 varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_hfls (out1 varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_hfss (out1 varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_hfss (out1 varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_mrfso (soil varset); written every wp_step hours (grid ini)</t>
+          <t>CORDEX_Cmor: RCM_sfc_mrfso (soil varset); written every 6 hours</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_mrfsos (soil varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_mrfsos (soil varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_mrsfl (soil varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_mrsfl (soil varset); written every 6 hours</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_mrso (soil varset); written every wp_step hours (grid ini)</t>
+          <t>CORDEX_Cmor: RCM_sfc_mrso (soil varset); written every wp_step hours (grid ini: 6 CORDEX, 1 LUCAS)</t>
         </is>
       </c>
     </row>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_mrsos (soil varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_mrsos (soil varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_mrsol (soil varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_mrsol (soil varset); written every wp_step hours (grid ini: 6 CORDEX, 1 LUCAS)</t>
         </is>
       </c>
     </row>
@@ -3573,7 +3573,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_snw (snw varset); written every wp_step hours (grid ini)</t>
+          <t>CORDEX_Cmor: RCM_sfc_snw (snw varset); written every 6 hours</t>
         </is>
       </c>
     </row>
@@ -3638,7 +3638,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_snc (snw varset); written every wp_step hours (grid ini)</t>
+          <t>CORDEX_Cmor: RCM_sfc_snc (snw varset); written every 6 hours</t>
         </is>
       </c>
     </row>
@@ -3703,7 +3703,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_snd (snw varset); written every wp_step hours (grid ini)</t>
+          <t>CORDEX_Cmor: RCM_sfc_snd (snw varset); written every 6 hours</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_zmla (out1 varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_zmla (out1 varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_prw (wpth2 varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_prw (wpth2 varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_clwvi (wpth3 varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_clwvi (wpth3 varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_clivi (wpth1 varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_clivi (wpth1 varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -4097,7 +4097,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_clgvi (wpth4 varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_clgvi (wpth4 varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_clhvi (wpth4 varset); needs a microphysics with hail (QHAIL)</t>
+          <t>CORDEX_Cmor: RCM_sfc_clhvi (wpth4 varset); written hourly; needs a microphysics with hail (QHAIL)</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_ua (plev_ua varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_ua (plev_ua varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -4300,7 +4300,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_ua (plev_ua varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_ua (plev_ua varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_ua (plev_ua varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_ua (plev_ua varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_ua (plev_ua varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_ua (plev_ua varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -4507,7 +4507,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_ua (plev_ua varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_ua (plev_ua varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_ua (plev_ua varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_ua (plev_ua varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -4645,7 +4645,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_ua (plev_ua varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_ua (plev_ua varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_ua (plev_ua varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_ua (plev_ua varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_ua (plev_ua varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_ua (plev_ua varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_ua (plev_ua varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_ua (plev_ua varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_uava (plev_uava varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_uava (plev_uava varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -4990,7 +4990,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_uava (plev_uava varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_uava (plev_uava varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_uava (plev_uava varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_uava (plev_uava varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -5128,7 +5128,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_uava (plev_uava varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_uava (plev_uava varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_uava (plev_uava varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_uava (plev_uava varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_uava (plev_uava varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_uava (plev_uava varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -5335,7 +5335,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_uava (plev_uava varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_uava (plev_uava varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -5404,7 +5404,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_uava (plev_uava varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_uava (plev_uava varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -5473,7 +5473,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_uava (plev_uava varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_uava (plev_uava varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_uava (plev_uava varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_uava (plev_uava varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_ta (plev_ta varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_ta (plev_ta varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -5680,7 +5680,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_ta (plev_ta varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_ta (plev_ta varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -5749,7 +5749,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_ta (plev_ta varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_ta (plev_ta varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_ta (plev_ta varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_ta (plev_ta varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -5887,7 +5887,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_ta (plev_ta varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_ta (plev_ta varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_ta (plev_ta varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_ta (plev_ta varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -6025,7 +6025,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_ta (plev_ta varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_ta (plev_ta varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -6094,7 +6094,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_ta (plev_ta varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_ta (plev_ta varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_ta (plev_ta varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_ta (plev_ta varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_ta (plev_ta varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_ta (plev_ta varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -6301,7 +6301,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_hus (plev_hus varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_hus (plev_hus varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -6370,7 +6370,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_hus (plev_hus varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_hus (plev_hus varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_hus (plev_hus varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_hus (plev_hus varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_hus (plev_hus varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_hus (plev_hus varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_hus (plev_hus varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_hus (plev_hus varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -6646,7 +6646,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_hus (plev_hus varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_hus (plev_hus varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_hus (plev_hus varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_hus (plev_hus varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_hus (plev_hus varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_hus (plev_hus varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_hus (plev_hus varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_hus (plev_hus varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_hus (plev_hus varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_hus (plev_hus varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_zg (plev_zg varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_zg (plev_zg varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_zg (plev_zg varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_zg (plev_zg varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -7129,7 +7129,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_zg (plev_zg varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_zg (plev_zg varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_zg (plev_zg varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_zg (plev_zg varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -7267,7 +7267,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_zg (plev_zg varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_zg (plev_zg varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_zg (plev_zg varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_zg (plev_zg varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_zg (plev_zg varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_zg (plev_zg varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_zg (plev_zg varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_zg (plev_zg varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_zg (plev_zg varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_zg (plev_zg varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -7612,7 +7612,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_zg (plev_zg varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_zg (plev_zg varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -7681,7 +7681,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_wa (plev_wa varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_wa (plev_wa varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_wa (plev_wa varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_wa (plev_wa varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -7819,7 +7819,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_wa (plev_wa varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_wa (plev_wa varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_wa (plev_wa varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_wa (plev_wa varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -7957,7 +7957,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_wa (plev_wa varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_wa (plev_wa varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_wa (plev_wa varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_wa (plev_wa varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -8095,7 +8095,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_wa (plev_wa varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_wa (plev_wa varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_wa (plev_wa varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_wa (plev_wa varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -8233,7 +8233,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_wa (plev_wa varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_wa (plev_wa varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -8302,7 +8302,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_wa (plev_wa varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_wa (plev_wa varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -8367,7 +8367,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_zlev_ua (zlev_ua0 varset)</t>
+          <t>CORDEX_Cmor: RCM_zlev_ua (zlev_ua0 varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_zlev_ua (zlev_ua0 varset)</t>
+          <t>CORDEX_Cmor: RCM_zlev_ua (zlev_ua0 varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -8497,7 +8497,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_zlev_ua (zlev_ua0 varset)</t>
+          <t>CORDEX_Cmor: RCM_zlev_ua (zlev_ua0 varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_zlev_uava (zlev_uava0 varset)</t>
+          <t>CORDEX_Cmor: RCM_zlev_uava (zlev_uava0 varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -8627,7 +8627,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_zlev_uava (zlev_uava0 varset)</t>
+          <t>CORDEX_Cmor: RCM_zlev_uava (zlev_uava0 varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -8692,7 +8692,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_zlev_uava (zlev_uava0 varset)</t>
+          <t>CORDEX_Cmor: RCM_zlev_uava (zlev_uava0 varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_zlev_ta (zlev_ta varset)</t>
+          <t>CORDEX_Cmor: RCM_zlev_ta (zlev_ta varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_zlev_hus (zlev_hus varset)</t>
+          <t>CORDEX_Cmor: RCM_zlev_hus (zlev_hus varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -8887,7 +8887,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_evspsblpot (out2 varset); FAO-56 Penman-Monteith hourly; net radiation from the accumulated radiation</t>
+          <t>CORDEX_Cmor: RCM_sfc_evspsblpot (out2 varset); written hourly; FAO-56 Penman-Monteith hourly; net radiation from the accumulated radiation</t>
         </is>
       </c>
     </row>
@@ -9009,7 +9009,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_cloud (cloud1 varset); written every wp_step hours (grid ini)</t>
+          <t>CORDEX_Cmor: RCM_sfc_cloud (cloud1 varset); written every 6 hours</t>
         </is>
       </c>
     </row>
@@ -9074,7 +9074,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_cloud (cloud1 varset); written every wp_step hours (grid ini)</t>
+          <t>CORDEX_Cmor: RCM_sfc_cloud (cloud1 varset); written every 6 hours</t>
         </is>
       </c>
     </row>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_cloud (cloud2 varset); written every wp_step hours (grid ini)</t>
+          <t>CORDEX_Cmor: RCM_sfc_cloud (cloud2 varset); written every 6 hours</t>
         </is>
       </c>
     </row>
@@ -9204,7 +9204,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset); written every wp_step hours (grid ini)</t>
+          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset); written every 6 hours</t>
         </is>
       </c>
     </row>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset); written every wp_step hours (grid ini)</t>
+          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset); written every 6 hours</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset); written every wp_step hours (grid ini)</t>
+          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset); written every 6 hours</t>
         </is>
       </c>
     </row>
@@ -9399,7 +9399,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset); written every wp_step hours (grid ini)</t>
+          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset); written every 6 hours</t>
         </is>
       </c>
     </row>
@@ -9464,7 +9464,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset); written every wp_step hours (grid ini)</t>
+          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset); written every 6 hours</t>
         </is>
       </c>
     </row>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset); written every wp_step hours (grid ini)</t>
+          <t>CORDEX_Cmor: RCM_sfc_rad (rad varset); written every 6 hours</t>
         </is>
       </c>
     </row>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_z0 (out2 varset); written daily; z0 = 10 exp(-k U10/UST), from the 10 m wind and UST (not ZNT)</t>
+          <t>CORDEX_Cmor: RCM_sfc_z0 (out2 varset); written hourly; z0 = 10 exp(-k U10/UST), from the 10 m wind and UST (not ZNT)</t>
         </is>
       </c>
     </row>
@@ -10021,7 +10021,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_od550aer (out1 varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_od550aer (out1 varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -10090,7 +10090,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_ua (plev_ua varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_ua (plev_ua varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -10159,7 +10159,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_ua (plev_ua varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_ua (plev_ua varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -10228,7 +10228,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_ua (plev_ua varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_ua (plev_ua varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -10297,7 +10297,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_ua (plev_ua varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_ua (plev_ua varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -10366,7 +10366,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_ua (plev_ua varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_ua (plev_ua varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -10573,7 +10573,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_uava (plev_uava varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_uava (plev_uava varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -10642,7 +10642,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_uava (plev_uava varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_uava (plev_uava varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -10711,7 +10711,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_uava (plev_uava varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_uava (plev_uava varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -10780,7 +10780,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_uava (plev_uava varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_uava (plev_uava varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -10849,7 +10849,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_uava (plev_uava varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_uava (plev_uava varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -11056,7 +11056,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_ta (plev_ta varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_ta (plev_ta varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -11125,7 +11125,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_ta (plev_ta varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_ta (plev_ta varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_ta (plev_ta varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_ta (plev_ta varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -11263,7 +11263,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_ta (plev_ta varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_ta (plev_ta varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_ta (plev_ta varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_ta (plev_ta varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -11539,7 +11539,7 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_hus (plev_hus varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_hus (plev_hus varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -11608,7 +11608,7 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_hus (plev_hus varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_hus (plev_hus varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -11677,7 +11677,7 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_hus (plev_hus varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_hus (plev_hus varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -11746,7 +11746,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_hus (plev_hus varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_hus (plev_hus varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -11815,7 +11815,7 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_hus (plev_hus varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_hus (plev_hus varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -12022,7 +12022,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_zg (plev_zg varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_zg (plev_zg varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -12091,7 +12091,7 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_zg (plev_zg varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_zg (plev_zg varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_zg (plev_zg varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_zg (plev_zg varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -12229,7 +12229,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_zg (plev_zg varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_zg (plev_zg varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -12298,7 +12298,7 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_zg (plev_zg varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_zg (plev_zg varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -12505,7 +12505,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_wa (plev_wa varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_wa (plev_wa varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -12574,7 +12574,7 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_wa (plev_wa varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_wa (plev_wa varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -12643,7 +12643,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_wa (plev_wa varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_wa (plev_wa varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -12712,7 +12712,7 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_wa (plev_wa varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_wa (plev_wa varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -12781,7 +12781,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_wa (plev_wa varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_wa (plev_wa varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -12988,7 +12988,7 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_ua (plev_ua varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_ua (plev_ua varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -13057,7 +13057,7 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_uava (plev_uava varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_uava (plev_uava varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -13126,7 +13126,7 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_ta (plev_ta varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_ta (plev_ta varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -13195,7 +13195,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_hus (plev_hus varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_hus (plev_hus varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -13264,7 +13264,7 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_zg (plev_zg varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_zg (plev_zg varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -13333,7 +13333,7 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_plev_wa (plev_wa varset)</t>
+          <t>CORDEX_Cmor: RCM_plev_wa (plev_wa varset); written every 3 hours</t>
         </is>
       </c>
     </row>
@@ -13398,7 +13398,7 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_zlev_ua (zlev_ua1 varset)</t>
+          <t>CORDEX_Cmor: RCM_zlev_ua (zlev_ua1 varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -13463,7 +13463,7 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_zlev_ua (zlev_ua1 varset)</t>
+          <t>CORDEX_Cmor: RCM_zlev_ua (zlev_ua1 varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -13528,7 +13528,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_zlev_ua (zlev_ua1 varset)</t>
+          <t>CORDEX_Cmor: RCM_zlev_ua (zlev_ua1 varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -13972,7 +13972,7 @@
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_hfso (out2 varset); hourly mean of GRDFLX (positive into the soil)</t>
+          <t>CORDEX_Cmor: RCM_sfc_hfso (out2 varset); written hourly; hourly mean of GRDFLX (positive into the soil)</t>
         </is>
       </c>
     </row>
@@ -14037,7 +14037,7 @@
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_urb (urban varset); urban cells only (FRC_URB2D and LU_INDEX of geo_em)</t>
+          <t>CORDEX_Cmor: RCM_sfc_urb (urban varset); written hourly; urban cells only (FRC_URB2D and LU_INDEX of geo_em)</t>
         </is>
       </c>
     </row>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_urb (urban varset); urban cells only (FRC_URB2D and LU_INDEX of geo_em)</t>
+          <t>CORDEX_Cmor: RCM_sfc_urb (urban varset); written hourly; urban cells only (FRC_URB2D and LU_INDEX of geo_em)</t>
         </is>
       </c>
     </row>
@@ -14167,7 +14167,7 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_urb (urban varset); urban cells only (FRC_URB2D and LU_INDEX of geo_em)</t>
+          <t>CORDEX_Cmor: RCM_sfc_urb (urban varset); written hourly; urban cells only (FRC_URB2D and LU_INDEX of geo_em)</t>
         </is>
       </c>
     </row>
@@ -14232,7 +14232,7 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_tasblue (urban varset); water cells only (LANDMASK = 0)</t>
+          <t>CORDEX_Cmor: RCM_sfc_tasblue (urban varset); written hourly; water cells only (LANDMASK = 0)</t>
         </is>
       </c>
     </row>
@@ -14358,7 +14358,7 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_ts (urban varset); all cells (RCM_sfc_ts with header_tsskin)</t>
+          <t>CORDEX_Cmor: RCM_sfc_ts (urban varset); written hourly; all cells (RCM_sfc_ts with header_tsskin)</t>
         </is>
       </c>
     </row>
@@ -14423,7 +14423,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_urb (urban varset); urban cells only (FRC_URB2D and LU_INDEX of geo_em)</t>
+          <t>CORDEX_Cmor: RCM_sfc_urb (urban varset); written hourly; urban cells only (FRC_URB2D and LU_INDEX of geo_em)</t>
         </is>
       </c>
     </row>
@@ -14488,7 +14488,7 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_urb (urban varset); urban cells only (FRC_URB2D and LU_INDEX of geo_em)</t>
+          <t>CORDEX_Cmor: RCM_sfc_urb (urban varset); written hourly; urban cells only (FRC_URB2D and LU_INDEX of geo_em)</t>
         </is>
       </c>
     </row>
@@ -14553,7 +14553,7 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_urb (urban varset); urban cells only (FRC_URB2D and LU_INDEX of geo_em)</t>
+          <t>CORDEX_Cmor: RCM_sfc_urb (urban varset); written hourly; urban cells only (FRC_URB2D and LU_INDEX of geo_em)</t>
         </is>
       </c>
     </row>
@@ -14618,7 +14618,7 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_tsblue (urban varset); water cells only (LANDMASK = 0)</t>
+          <t>CORDEX_Cmor: RCM_sfc_tsblue (urban varset); written hourly; water cells only (LANDMASK = 0)</t>
         </is>
       </c>
     </row>
@@ -14683,7 +14683,7 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_urb (urban varset); urban cells only (FRC_URB2D and LU_INDEX of geo_em)</t>
+          <t>CORDEX_Cmor: RCM_sfc_urb (urban varset); written hourly; urban cells only (FRC_URB2D and LU_INDEX of geo_em)</t>
         </is>
       </c>
     </row>
@@ -14748,7 +14748,7 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_hurscan (urban varset); urban cells only (FRC_URB2D and LU_INDEX of geo_em)</t>
+          <t>CORDEX_Cmor: RCM_sfc_hurscan (urban varset); written hourly; urban cells only (FRC_URB2D and LU_INDEX of geo_em)</t>
         </is>
       </c>
     </row>
@@ -14813,7 +14813,7 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_husscan (urban varset); q = r/(1+r); urban cells only</t>
+          <t>CORDEX_Cmor: RCM_sfc_husscan (urban varset); written hourly; q = r/(1+r); urban cells only</t>
         </is>
       </c>
     </row>
@@ -14878,7 +14878,7 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_sfcWindcan (urban varset); urban cells only (FRC_URB2D and LU_INDEX of geo_em)</t>
+          <t>CORDEX_Cmor: RCM_sfc_sfcWindcan (urban varset); written hourly; urban cells only (FRC_URB2D and LU_INDEX of geo_em)</t>
         </is>
       </c>
     </row>
@@ -15334,7 +15334,7 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_evspsblsoi (lsm varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_evspsblsoi (lsm varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -15391,7 +15391,7 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_evspsblveg (lsm varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_evspsblveg (lsm varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -15505,7 +15505,7 @@
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_hfls (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
+          <t>CORDEX_Cmor: RCM_sfc_hfls (lut varset); written hourly; no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
         </is>
       </c>
     </row>
@@ -15562,7 +15562,7 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_hfss (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
+          <t>CORDEX_Cmor: RCM_sfc_hfss (lut varset); written hourly; no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
         </is>
       </c>
     </row>
@@ -15619,7 +15619,7 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_huss (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
+          <t>CORDEX_Cmor: RCM_sfc_huss (lut varset); written hourly; no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
         </is>
       </c>
     </row>
@@ -15676,7 +15676,7 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_interception (lsm varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_interception (lsm varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -15733,7 +15733,7 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_irrLut (irr varset); Noah-MP irrigation (opt_irr); add IRSIVOL IRMIVOL IRFIVOL to wrfout (iofields); no land-use tiles: grid-cell value</t>
+          <t>CORDEX_Cmor: RCM_sfc_irrLut (irr varset); written hourly; Noah-MP irrigation (opt_irr); add IRSIVOL IRMIVOL IRFIVOL to wrfout (iofields); no land-use tiles: grid-cell value</t>
         </is>
       </c>
     </row>
@@ -15904,7 +15904,7 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_mrro (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
+          <t>CORDEX_Cmor: RCM_sfc_mrro (lut varset); written hourly; no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
         </is>
       </c>
     </row>
@@ -15961,7 +15961,7 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_mrso (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
+          <t>CORDEX_Cmor: RCM_sfc_mrso (lut varset); written hourly; no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
         </is>
       </c>
     </row>
@@ -16018,7 +16018,7 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_mrsos (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
+          <t>CORDEX_Cmor: RCM_sfc_mrsos (lut varset); written hourly; no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
         </is>
       </c>
     </row>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_rad (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
+          <t>CORDEX_Cmor: RCM_sfc_rad (lut varset); written hourly; no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
         </is>
       </c>
     </row>
@@ -16360,7 +16360,7 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_rad (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
+          <t>CORDEX_Cmor: RCM_sfc_rad (lut varset); written hourly; no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
         </is>
       </c>
     </row>
@@ -16474,7 +16474,7 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_snw (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
+          <t>CORDEX_Cmor: RCM_sfc_snw (lut varset); written hourly; no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
         </is>
       </c>
     </row>
@@ -16531,7 +16531,7 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_tas (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
+          <t>CORDEX_Cmor: RCM_sfc_tas (lut varset); written hourly; no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
         </is>
       </c>
     </row>
@@ -16588,7 +16588,7 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_tcs (lsm varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_tcs (lsm varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -16645,7 +16645,7 @@
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_tgs (lsm varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_tgs (lsm varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -16702,7 +16702,7 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_tran (lsm varset)</t>
+          <t>CORDEX_Cmor: RCM_sfc_tran (lsm varset); written hourly</t>
         </is>
       </c>
     </row>
@@ -16987,7 +16987,7 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_sfc_ts (lut varset); no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
+          <t>CORDEX_Cmor: RCM_sfc_ts (lut varset); written hourly; no land-use tiles in WRF: the grid-cell value, with the Lut header</t>
         </is>
       </c>
     </row>

--- a/CORDEX_Cmor_variables.xlsx
+++ b/CORDEX_Cmor_variables.xlsx
@@ -15106,7 +15106,7 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_fx_landuse (fx varset) and RCM_sfc_landuse (landuse varset); LANDUSEF classes grouped (landuse_field in shared_subs_v2.f90)</t>
+          <t>CORDEX_Cmor: RCM_fx_landuse (fx varset) and RCM_sfc_landuse (landuse varset); LANDUSEF classes grouped (landuse_field in landuse_subs.f90)</t>
         </is>
       </c>
     </row>
@@ -15163,7 +15163,7 @@
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_fx_landuse (fx varset) and RCM_sfc_landuse (landuse varset); LANDUSEF tree+shrub+grass+crop (landuse_field in shared_subs_v2.f90)</t>
+          <t>CORDEX_Cmor: RCM_fx_landuse (fx varset) and RCM_sfc_landuse (landuse varset); LANDUSEF tree+shrub+grass+crop (landuse_field in landuse_subs.f90)</t>
         </is>
       </c>
     </row>
@@ -15220,7 +15220,7 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_fx_landuse (fx varset) and RCM_sfc_landuse (landuse varset); LANDUSEF classes grouped (landuse_field in shared_subs_v2.f90)</t>
+          <t>CORDEX_Cmor: RCM_fx_landuse (fx varset) and RCM_sfc_landuse (landuse varset); LANDUSEF classes grouped (landuse_field in landuse_subs.f90)</t>
         </is>
       </c>
     </row>
@@ -15448,7 +15448,7 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_fx_landuse (fx varset) and RCM_sfc_landuse (landuse varset); LANDUSEF classes grouped (landuse_field in shared_subs_v2.f90)</t>
+          <t>CORDEX_Cmor: RCM_fx_landuse (fx varset) and RCM_sfc_landuse (landuse varset); LANDUSEF classes grouped (landuse_field in landuse_subs.f90)</t>
         </is>
       </c>
     </row>
@@ -16417,7 +16417,7 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_fx_landuse (fx varset) and RCM_sfc_landuse (landuse varset); LANDUSEF classes grouped (landuse_field in shared_subs_v2.f90)</t>
+          <t>CORDEX_Cmor: RCM_fx_landuse (fx varset) and RCM_sfc_landuse (landuse varset); LANDUSEF classes grouped (landuse_field in landuse_subs.f90)</t>
         </is>
       </c>
     </row>
@@ -16759,7 +16759,7 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_fx_landuse (fx varset) and RCM_sfc_landuse (landuse varset); LANDUSEF classes grouped (landuse_field in shared_subs_v2.f90)</t>
+          <t>CORDEX_Cmor: RCM_fx_landuse (fx varset) and RCM_sfc_landuse (landuse varset); LANDUSEF classes grouped (landuse_field in landuse_subs.f90)</t>
         </is>
       </c>
     </row>
@@ -17044,7 +17044,7 @@
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>CORDEX_Cmor: RCM_fx_landuse (fx varset) and RCM_sfc_landuse (landuse varset); LANDUSEF urban classes incl. LCZ (landuse_field in shared_subs_v2.f90)</t>
+          <t>CORDEX_Cmor: RCM_fx_landuse (fx varset) and RCM_sfc_landuse (landuse varset); LANDUSEF urban classes incl. LCZ (landuse_field in landuse_subs.f90)</t>
         </is>
       </c>
     </row>
